--- a/exports/maison-nsaia-stock.xlsx
+++ b/exports/maison-nsaia-stock.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Stock complet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Synthèse" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Paramètres" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Factures" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stock complet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Synthèse" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paramètres" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Factures" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stock complet'!$A$5:$AA$45</definedName>
@@ -22,11 +22,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00 &quot;€&quot;"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
-    <numFmt numFmtId="167" formatCode="#,##0 &quot;art.&quot;"/>
-    <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00 &quot;€&quot;"/>
+    <numFmt numFmtId="165" formatCode="#,##0 &quot;art.&quot;"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="168" formatCode="0.000"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -142,7 +142,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -150,57 +150,81 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="9" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -778,25 +802,25 @@
           <t>Lot de 20 paires de sandales et tongs RELIFE / TOMMY JEANS — neuf</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="54" t="n">
         <v>56.7</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="55">
         <f>$B6+$Y6*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="56">
         <f>$C6/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="55">
         <f>CEILING($D6*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F6" s="8" t="n">
+      <c r="F6" s="57" t="n">
         <v>199</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="57">
         <f>IF($F6="","",$F6-$C6-$M6-$N6)</f>
         <v/>
       </c>
@@ -807,29 +831,29 @@
       <c r="I6" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="55">
         <f>$C6/$I6</f>
         <v/>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="55">
         <f>IF($F6="","",$F6/$I6)</f>
         <v/>
       </c>
-      <c r="L6" s="6">
+      <c r="L6" s="55">
         <f>IF($G6="","",$G6/$I6)</f>
         <v/>
       </c>
-      <c r="M6" s="7">
+      <c r="M6" s="56">
         <f>IF($F6="","",$F6*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N6" s="6" t="n">
+      <c r="N6" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O6" s="11" t="n">
+      <c r="O6" s="58" t="n">
         <v>45</v>
       </c>
-      <c r="P6" s="11" t="n">
+      <c r="P6" s="58" t="n">
         <v>11.7</v>
       </c>
       <c r="Q6" s="12" t="inlineStr">
@@ -867,7 +891,7 @@
       <c r="Y6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z6" s="8">
+      <c r="Z6" s="57">
         <f>IF($G6="","",$G6/$Y6)</f>
         <v/>
       </c>
@@ -882,25 +906,25 @@
           <t>Lot de 2 paires ADIDAS Predator Edge P.48 2/3 — neuves</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="54" t="n">
         <v>37.8</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="55">
         <f>$B7+$Y7*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="56">
         <f>$C7/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="55">
         <f>CEILING($D7*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F7" s="8" t="n">
+      <c r="F7" s="57" t="n">
         <v>178</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="57">
         <f>IF($F7="","",$F7-$C7-$M7-$N7)</f>
         <v/>
       </c>
@@ -911,29 +935,29 @@
       <c r="I7" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="J7" s="6">
+      <c r="J7" s="55">
         <f>$C7/$I7</f>
         <v/>
       </c>
-      <c r="K7" s="6">
+      <c r="K7" s="55">
         <f>IF($F7="","",$F7/$I7)</f>
         <v/>
       </c>
-      <c r="L7" s="6">
+      <c r="L7" s="55">
         <f>IF($G7="","",$G7/$I7)</f>
         <v/>
       </c>
-      <c r="M7" s="7">
+      <c r="M7" s="56">
         <f>IF($F7="","",$F7*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N7" s="6" t="n">
+      <c r="N7" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O7" s="11" t="n">
+      <c r="O7" s="58" t="n">
         <v>30</v>
       </c>
-      <c r="P7" s="11" t="n">
+      <c r="P7" s="58" t="n">
         <v>7.8</v>
       </c>
       <c r="Q7" s="12" t="inlineStr">
@@ -971,7 +995,7 @@
       <c r="Y7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="Z7" s="8">
+      <c r="Z7" s="57">
         <f>IF($G7="","",$G7/$Y7)</f>
         <v/>
       </c>
@@ -986,25 +1010,25 @@
           <t>Demi-bottes FORMA Legacy Waterproof T.45 noir — neuves</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="54" t="n">
         <v>63</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="55">
         <f>$B8+$Y8*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="56">
         <f>$C8/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="55">
         <f>CEILING($D8*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F8" s="8" t="n">
+      <c r="F8" s="57" t="n">
         <v>159</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="57">
         <f>IF($F8="","",$F8-$C8-$M8-$N8)</f>
         <v/>
       </c>
@@ -1015,30 +1039,30 @@
       <c r="I8" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J8" s="6">
+      <c r="J8" s="55">
         <f>$C8/$I8</f>
         <v/>
       </c>
-      <c r="K8" s="6">
+      <c r="K8" s="55">
         <f>IF($F8="","",$F8/$I8)</f>
         <v/>
       </c>
-      <c r="L8" s="6">
+      <c r="L8" s="55">
         <f>IF($G8="","",$G8/$I8)</f>
         <v/>
       </c>
-      <c r="M8" s="7">
+      <c r="M8" s="56">
         <f>IF($F8="","",$F8*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N8" s="6">
+      <c r="N8" s="55">
         <f>IF($F8="","",$F8*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="O8" s="11" t="n">
+      <c r="O8" s="58" t="n">
         <v>50</v>
       </c>
-      <c r="P8" s="11" t="n">
+      <c r="P8" s="58" t="n">
         <v>13</v>
       </c>
       <c r="Q8" s="12" t="inlineStr">
@@ -1076,7 +1100,7 @@
       <c r="Y8" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z8" s="8">
+      <c r="Z8" s="57">
         <f>IF($G8="","",$G8/$Y8)</f>
         <v/>
       </c>
@@ -1091,25 +1115,25 @@
           <t>Lot de 4 gilets de flottaison MRS.ERTHA 3-6 ans — neuf</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="54" t="n">
         <v>37.8</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="55">
         <f>$B9+$Y9*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="56">
         <f>$C9/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="55">
         <f>CEILING($D9*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F9" s="8" t="n">
+      <c r="F9" s="57" t="n">
         <v>136</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="57">
         <f>IF($F9="","",$F9-$C9-$M9-$N9)</f>
         <v/>
       </c>
@@ -1120,29 +1144,29 @@
       <c r="I9" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="J9" s="6">
+      <c r="J9" s="55">
         <f>$C9/$I9</f>
         <v/>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="55">
         <f>IF($F9="","",$F9/$I9)</f>
         <v/>
       </c>
-      <c r="L9" s="6">
+      <c r="L9" s="55">
         <f>IF($G9="","",$G9/$I9)</f>
         <v/>
       </c>
-      <c r="M9" s="7">
+      <c r="M9" s="56">
         <f>IF($F9="","",$F9*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N9" s="6" t="n">
+      <c r="N9" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O9" s="11" t="n">
+      <c r="O9" s="58" t="n">
         <v>30</v>
       </c>
-      <c r="P9" s="11" t="n">
+      <c r="P9" s="58" t="n">
         <v>7.8</v>
       </c>
       <c r="Q9" s="12" t="inlineStr">
@@ -1180,7 +1204,7 @@
       <c r="Y9" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="Z9" s="8">
+      <c r="Z9" s="57">
         <f>IF($G9="","",$G9/$Y9)</f>
         <v/>
       </c>
@@ -1195,25 +1219,25 @@
           <t>Lot de 12 paires de tongs HAVAIANAS fuchsia 35/36 — neuf</t>
         </is>
       </c>
-      <c r="B10" s="14" t="n">
+      <c r="B10" s="59" t="n">
         <v>100.8</v>
       </c>
-      <c r="C10" s="15">
+      <c r="C10" s="60">
         <f>$B10+$Y10*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D10" s="16">
+      <c r="D10" s="61">
         <f>$C10/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E10" s="15">
+      <c r="E10" s="60">
         <f>CEILING($D10*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F10" s="17" t="n">
+      <c r="F10" s="62" t="n">
         <v>208</v>
       </c>
-      <c r="G10" s="17">
+      <c r="G10" s="62">
         <f>IF($F10="","",$F10-$C10-$M10-$N10)</f>
         <v/>
       </c>
@@ -1224,29 +1248,29 @@
       <c r="I10" s="19" t="n">
         <v>12</v>
       </c>
-      <c r="J10" s="15">
+      <c r="J10" s="60">
         <f>$C10/$I10</f>
         <v/>
       </c>
-      <c r="K10" s="15">
+      <c r="K10" s="60">
         <f>IF($F10="","",$F10/$I10)</f>
         <v/>
       </c>
-      <c r="L10" s="15">
+      <c r="L10" s="60">
         <f>IF($G10="","",$G10/$I10)</f>
         <v/>
       </c>
-      <c r="M10" s="16">
+      <c r="M10" s="61">
         <f>IF($F10="","",$F10*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N10" s="15" t="n">
+      <c r="N10" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="O10" s="20" t="n">
+      <c r="O10" s="63" t="n">
         <v>80</v>
       </c>
-      <c r="P10" s="20" t="n">
+      <c r="P10" s="63" t="n">
         <v>20.8</v>
       </c>
       <c r="Q10" s="21" t="inlineStr">
@@ -1288,7 +1312,7 @@
       <c r="Y10" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" s="17">
+      <c r="Z10" s="62">
         <f>IF($G10="","",$G10/$Y10)</f>
         <v/>
       </c>
@@ -1303,25 +1327,25 @@
           <t>ELISABETTA FRANCHI robe asymétrique viscose T.46 IT — neuve</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="54" t="n">
         <v>20.45</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="55">
         <f>$B11+$Y11*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="56">
         <f>$C11/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="55">
         <f>CEILING($D11*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F11" s="8" t="n">
+      <c r="F11" s="57" t="n">
         <v>99</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="57">
         <f>IF($F11="","",$F11-$C11-$M11-$N11)</f>
         <v/>
       </c>
@@ -1332,30 +1356,30 @@
       <c r="I11" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J11" s="6">
+      <c r="J11" s="55">
         <f>$C11/$I11</f>
         <v/>
       </c>
-      <c r="K11" s="6">
+      <c r="K11" s="55">
         <f>IF($F11="","",$F11/$I11)</f>
         <v/>
       </c>
-      <c r="L11" s="6">
+      <c r="L11" s="55">
         <f>IF($G11="","",$G11/$I11)</f>
         <v/>
       </c>
-      <c r="M11" s="7">
+      <c r="M11" s="56">
         <f>IF($F11="","",$F11*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N11" s="6">
+      <c r="N11" s="55">
         <f>IF($F11="","",$F11*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="O11" s="11" t="n">
+      <c r="O11" s="58" t="n">
         <v>16</v>
       </c>
-      <c r="P11" s="11" t="n">
+      <c r="P11" s="58" t="n">
         <v>4.16</v>
       </c>
       <c r="Q11" s="12" t="inlineStr">
@@ -1393,7 +1417,7 @@
       <c r="Y11" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z11" s="8">
+      <c r="Z11" s="57">
         <f>IF($G11="","",$G11/$Y11)</f>
         <v/>
       </c>
@@ -1408,25 +1432,25 @@
           <t>Combinaison de pluie BMW Overall ProRain unisexe XL — neuve</t>
         </is>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="54" t="n">
         <v>68.56999999999999</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="55">
         <f>$B12+$Y12*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="56">
         <f>$C12/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="55">
         <f>CEILING($D12*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F12" s="8" t="n">
+      <c r="F12" s="57" t="n">
         <v>139</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G12" s="57">
         <f>IF($F12="","",$F12-$C12-$M12-$N12)</f>
         <v/>
       </c>
@@ -1437,29 +1461,29 @@
       <c r="I12" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J12" s="6">
+      <c r="J12" s="55">
         <f>$C12/$I12</f>
         <v/>
       </c>
-      <c r="K12" s="6">
+      <c r="K12" s="55">
         <f>IF($F12="","",$F12/$I12)</f>
         <v/>
       </c>
-      <c r="L12" s="6">
+      <c r="L12" s="55">
         <f>IF($G12="","",$G12/$I12)</f>
         <v/>
       </c>
-      <c r="M12" s="7">
+      <c r="M12" s="56">
         <f>IF($F12="","",$F12*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N12" s="6" t="n">
+      <c r="N12" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O12" s="11" t="n">
+      <c r="O12" s="58" t="n">
         <v>60</v>
       </c>
-      <c r="P12" s="11" t="n">
+      <c r="P12" s="58" t="n">
         <v>8.57</v>
       </c>
       <c r="Q12" s="12" t="inlineStr">
@@ -1497,7 +1521,7 @@
       <c r="Y12" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z12" s="8">
+      <c r="Z12" s="57">
         <f>IF($G12="","",$G12/$Y12)</f>
         <v/>
       </c>
@@ -1512,25 +1536,25 @@
           <t>Chaussures HOGAN P.36 — traces d'essayage</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="54" t="n">
         <v>12.6</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="55">
         <f>$B13+$Y13*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="56">
         <f>$C13/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="55">
         <f>CEILING($D13*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F13" s="8" t="n">
+      <c r="F13" s="57" t="n">
         <v>79</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G13" s="57">
         <f>IF($F13="","",$F13-$C13-$M13-$N13)</f>
         <v/>
       </c>
@@ -1541,30 +1565,30 @@
       <c r="I13" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J13" s="6">
+      <c r="J13" s="55">
         <f>$C13/$I13</f>
         <v/>
       </c>
-      <c r="K13" s="6">
+      <c r="K13" s="55">
         <f>IF($F13="","",$F13/$I13)</f>
         <v/>
       </c>
-      <c r="L13" s="6">
+      <c r="L13" s="55">
         <f>IF($G13="","",$G13/$I13)</f>
         <v/>
       </c>
-      <c r="M13" s="7">
+      <c r="M13" s="56">
         <f>IF($F13="","",$F13*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N13" s="6">
+      <c r="N13" s="55">
         <f>IF($F13="","",$F13*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="O13" s="11" t="n">
+      <c r="O13" s="58" t="n">
         <v>10</v>
       </c>
-      <c r="P13" s="11" t="n">
+      <c r="P13" s="58" t="n">
         <v>2.6</v>
       </c>
       <c r="Q13" s="12" t="inlineStr">
@@ -1602,7 +1626,7 @@
       <c r="Y13" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z13" s="8">
+      <c r="Z13" s="57">
         <f>IF($G13="","",$G13/$Y13)</f>
         <v/>
       </c>
@@ -1617,25 +1641,25 @@
           <t>Jupe midi SONIA RYKIEL T.34 — neuve</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B14" s="54" t="n">
         <v>37.8</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="55">
         <f>$B14+$Y14*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="56">
         <f>$C14/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="55">
         <f>CEILING($D14*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F14" s="8" t="n">
+      <c r="F14" s="57" t="n">
         <v>99</v>
       </c>
-      <c r="G14" s="8">
+      <c r="G14" s="57">
         <f>IF($F14="","",$F14-$C14-$M14-$N14)</f>
         <v/>
       </c>
@@ -1646,30 +1670,30 @@
       <c r="I14" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J14" s="6">
+      <c r="J14" s="55">
         <f>$C14/$I14</f>
         <v/>
       </c>
-      <c r="K14" s="6">
+      <c r="K14" s="55">
         <f>IF($F14="","",$F14/$I14)</f>
         <v/>
       </c>
-      <c r="L14" s="6">
+      <c r="L14" s="55">
         <f>IF($G14="","",$G14/$I14)</f>
         <v/>
       </c>
-      <c r="M14" s="7">
+      <c r="M14" s="56">
         <f>IF($F14="","",$F14*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N14" s="6">
+      <c r="N14" s="55">
         <f>IF($F14="","",$F14*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="O14" s="11" t="n">
+      <c r="O14" s="58" t="n">
         <v>30</v>
       </c>
-      <c r="P14" s="11" t="n">
+      <c r="P14" s="58" t="n">
         <v>7.8</v>
       </c>
       <c r="Q14" s="12" t="inlineStr">
@@ -1707,7 +1731,7 @@
       <c r="Y14" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z14" s="8">
+      <c r="Z14" s="57">
         <f>IF($G14="","",$G14/$Y14)</f>
         <v/>
       </c>
@@ -1722,25 +1746,25 @@
           <t>Robe SANDRO T.40 — neuve</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="54" t="n">
         <v>37.8</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="55">
         <f>$B15+$Y15*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="56">
         <f>$C15/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="55">
         <f>CEILING($D15*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F15" s="8" t="n">
+      <c r="F15" s="57" t="n">
         <v>89</v>
       </c>
-      <c r="G15" s="8">
+      <c r="G15" s="57">
         <f>IF($F15="","",$F15-$C15-$M15-$N15)</f>
         <v/>
       </c>
@@ -1751,30 +1775,30 @@
       <c r="I15" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J15" s="6">
+      <c r="J15" s="55">
         <f>$C15/$I15</f>
         <v/>
       </c>
-      <c r="K15" s="6">
+      <c r="K15" s="55">
         <f>IF($F15="","",$F15/$I15)</f>
         <v/>
       </c>
-      <c r="L15" s="6">
+      <c r="L15" s="55">
         <f>IF($G15="","",$G15/$I15)</f>
         <v/>
       </c>
-      <c r="M15" s="7">
+      <c r="M15" s="56">
         <f>IF($F15="","",$F15*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N15" s="6">
+      <c r="N15" s="55">
         <f>IF($F15="","",$F15*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="O15" s="11" t="n">
+      <c r="O15" s="58" t="n">
         <v>30</v>
       </c>
-      <c r="P15" s="11" t="n">
+      <c r="P15" s="58" t="n">
         <v>7.8</v>
       </c>
       <c r="Q15" s="12" t="inlineStr">
@@ -1812,7 +1836,7 @@
       <c r="Y15" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z15" s="8">
+      <c r="Z15" s="57">
         <f>IF($G15="","",$G15/$Y15)</f>
         <v/>
       </c>
@@ -1827,25 +1851,25 @@
           <t>Lot de 6 vêtements femme MORGAN T.40 et L — neuf</t>
         </is>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B16" s="54" t="n">
         <v>37.8</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="55">
         <f>$B16+$Y16*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="56">
         <f>$C16/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E16" s="6">
+      <c r="E16" s="55">
         <f>CEILING($D16*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F16" s="8" t="n">
+      <c r="F16" s="57" t="n">
         <v>98</v>
       </c>
-      <c r="G16" s="8">
+      <c r="G16" s="57">
         <f>IF($F16="","",$F16-$C16-$M16-$N16)</f>
         <v/>
       </c>
@@ -1856,29 +1880,29 @@
       <c r="I16" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="J16" s="6">
+      <c r="J16" s="55">
         <f>$C16/$I16</f>
         <v/>
       </c>
-      <c r="K16" s="6">
+      <c r="K16" s="55">
         <f>IF($F16="","",$F16/$I16)</f>
         <v/>
       </c>
-      <c r="L16" s="6">
+      <c r="L16" s="55">
         <f>IF($G16="","",$G16/$I16)</f>
         <v/>
       </c>
-      <c r="M16" s="7">
+      <c r="M16" s="56">
         <f>IF($F16="","",$F16*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N16" s="6" t="n">
+      <c r="N16" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O16" s="11" t="n">
+      <c r="O16" s="58" t="n">
         <v>30</v>
       </c>
-      <c r="P16" s="11" t="n">
+      <c r="P16" s="58" t="n">
         <v>7.8</v>
       </c>
       <c r="Q16" s="12" t="inlineStr">
@@ -1916,7 +1940,7 @@
       <c r="Y16" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="Z16" s="8">
+      <c r="Z16" s="57">
         <f>IF($G16="","",$G16/$Y16)</f>
         <v/>
       </c>
@@ -1931,25 +1955,25 @@
           <t>ADIDAS Yeezy 700 V3 Mono Safflower T.38 — occasion</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n">
+      <c r="B17" s="54" t="n">
         <v>63</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="55">
         <f>$B17+$Y17*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="56">
         <f>$C17/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E17" s="6">
+      <c r="E17" s="55">
         <f>CEILING($D17*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F17" s="8" t="n">
+      <c r="F17" s="57" t="n">
         <v>105</v>
       </c>
-      <c r="G17" s="8">
+      <c r="G17" s="57">
         <f>IF($F17="","",$F17-$C17-$M17-$N17)</f>
         <v/>
       </c>
@@ -1960,29 +1984,29 @@
       <c r="I17" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J17" s="6">
+      <c r="J17" s="55">
         <f>$C17/$I17</f>
         <v/>
       </c>
-      <c r="K17" s="6">
+      <c r="K17" s="55">
         <f>IF($F17="","",$F17/$I17)</f>
         <v/>
       </c>
-      <c r="L17" s="6">
+      <c r="L17" s="55">
         <f>IF($G17="","",$G17/$I17)</f>
         <v/>
       </c>
-      <c r="M17" s="7">
+      <c r="M17" s="56">
         <f>IF($F17="","",$F17*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N17" s="6" t="n">
+      <c r="N17" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O17" s="11" t="n">
+      <c r="O17" s="58" t="n">
         <v>50</v>
       </c>
-      <c r="P17" s="11" t="n">
+      <c r="P17" s="58" t="n">
         <v>13</v>
       </c>
       <c r="Q17" s="12" t="inlineStr">
@@ -2020,7 +2044,7 @@
       <c r="Y17" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z17" s="8">
+      <c r="Z17" s="57">
         <f>IF($G17="","",$G17/$Y17)</f>
         <v/>
       </c>
@@ -2035,25 +2059,25 @@
           <t>T-shirt BALENCIAGA T.2 — neuf</t>
         </is>
       </c>
-      <c r="B18" s="14" t="n">
+      <c r="B18" s="59" t="n">
         <v>113.4</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="60">
         <f>$B18+$Y18*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D18" s="16">
+      <c r="D18" s="61">
         <f>$C18/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E18" s="15">
+      <c r="E18" s="60">
         <f>CEILING($D18*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F18" s="17" t="n">
+      <c r="F18" s="62" t="n">
         <v>155</v>
       </c>
-      <c r="G18" s="17">
+      <c r="G18" s="62">
         <f>IF($F18="","",$F18-$C18-$M18-$N18)</f>
         <v/>
       </c>
@@ -2064,29 +2088,29 @@
       <c r="I18" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J18" s="15">
+      <c r="J18" s="60">
         <f>$C18/$I18</f>
         <v/>
       </c>
-      <c r="K18" s="15">
+      <c r="K18" s="60">
         <f>IF($F18="","",$F18/$I18)</f>
         <v/>
       </c>
-      <c r="L18" s="15">
+      <c r="L18" s="60">
         <f>IF($G18="","",$G18/$I18)</f>
         <v/>
       </c>
-      <c r="M18" s="16">
+      <c r="M18" s="61">
         <f>IF($F18="","",$F18*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N18" s="15" t="n">
+      <c r="N18" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="O18" s="20" t="n">
+      <c r="O18" s="63" t="n">
         <v>90</v>
       </c>
-      <c r="P18" s="20" t="n">
+      <c r="P18" s="63" t="n">
         <v>23.4</v>
       </c>
       <c r="Q18" s="21" t="inlineStr">
@@ -2128,7 +2152,7 @@
       <c r="Y18" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="Z18" s="17">
+      <c r="Z18" s="62">
         <f>IF($G18="","",$G18/$Y18)</f>
         <v/>
       </c>
@@ -2143,25 +2167,25 @@
           <t>ADIDAS x STELLA McCARTNEY ASMC Ultraboost 21 P.36 — modèle d'exposition</t>
         </is>
       </c>
-      <c r="B19" s="5" t="n">
+      <c r="B19" s="54" t="n">
         <v>37.8</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="55">
         <f>$B19+$Y19*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D19" s="7">
+      <c r="D19" s="56">
         <f>$C19/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="E19" s="6">
+      <c r="E19" s="55">
         <f>CEILING($D19*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F19" s="8" t="n">
+      <c r="F19" s="57" t="n">
         <v>79</v>
       </c>
-      <c r="G19" s="8">
+      <c r="G19" s="57">
         <f>IF($F19="","",$F19-$C19-$M19-$N19)</f>
         <v/>
       </c>
@@ -2172,30 +2196,30 @@
       <c r="I19" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J19" s="6">
+      <c r="J19" s="55">
         <f>$C19/$I19</f>
         <v/>
       </c>
-      <c r="K19" s="6">
+      <c r="K19" s="55">
         <f>IF($F19="","",$F19/$I19)</f>
         <v/>
       </c>
-      <c r="L19" s="6">
+      <c r="L19" s="55">
         <f>IF($G19="","",$G19/$I19)</f>
         <v/>
       </c>
-      <c r="M19" s="7">
+      <c r="M19" s="56">
         <f>IF($F19="","",$F19*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N19" s="6">
+      <c r="N19" s="55">
         <f>IF($F19="","",$F19*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="O19" s="11" t="n">
+      <c r="O19" s="58" t="n">
         <v>30</v>
       </c>
-      <c r="P19" s="11" t="n">
+      <c r="P19" s="58" t="n">
         <v>7.8</v>
       </c>
       <c r="Q19" s="12" t="inlineStr">
@@ -2233,7 +2257,7 @@
       <c r="Y19" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z19" s="8">
+      <c r="Z19" s="57">
         <f>IF($G19="","",$G19/$Y19)</f>
         <v/>
       </c>
@@ -2248,25 +2272,25 @@
           <t>Blazer noir KARL LAGERFELD T.36 FR — neuf avec étiquette</t>
         </is>
       </c>
-      <c r="B20" s="5" t="n">
+      <c r="B20" s="54" t="n">
         <v>50.4</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="55">
         <f>$B20+$Y20*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D20" s="7">
+      <c r="D20" s="56">
         <f>$C20/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="E20" s="6">
+      <c r="E20" s="55">
         <f>CEILING($D20*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F20" s="8" t="n">
+      <c r="F20" s="57" t="n">
         <v>91</v>
       </c>
-      <c r="G20" s="8">
+      <c r="G20" s="57">
         <f>IF($F20="","",$F20-$C20-$M20-$N20)</f>
         <v/>
       </c>
@@ -2277,30 +2301,30 @@
       <c r="I20" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J20" s="6">
+      <c r="J20" s="55">
         <f>$C20/$I20</f>
         <v/>
       </c>
-      <c r="K20" s="6">
+      <c r="K20" s="55">
         <f>IF($F20="","",$F20/$I20)</f>
         <v/>
       </c>
-      <c r="L20" s="6">
+      <c r="L20" s="55">
         <f>IF($G20="","",$G20/$I20)</f>
         <v/>
       </c>
-      <c r="M20" s="7">
+      <c r="M20" s="56">
         <f>IF($F20="","",$F20*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N20" s="6">
+      <c r="N20" s="55">
         <f>IF($F20="","",$F20*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="O20" s="11" t="n">
+      <c r="O20" s="58" t="n">
         <v>40</v>
       </c>
-      <c r="P20" s="11" t="n">
+      <c r="P20" s="58" t="n">
         <v>10.4</v>
       </c>
       <c r="Q20" s="12" t="inlineStr">
@@ -2338,7 +2362,7 @@
       <c r="Y20" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z20" s="8">
+      <c r="Z20" s="57">
         <f>IF($G20="","",$G20/$Y20)</f>
         <v/>
       </c>
@@ -2353,25 +2377,25 @@
           <t>PHILIPP PLEIN SPORT baskets montantes P.40 — neuves</t>
         </is>
       </c>
-      <c r="B21" s="5" t="n">
+      <c r="B21" s="54" t="n">
         <v>57.51</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C21" s="55">
         <f>$B21+$Y21*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D21" s="7">
+      <c r="D21" s="56">
         <f>$C21/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E21" s="6">
+      <c r="E21" s="55">
         <f>CEILING($D21*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F21" s="8" t="n">
+      <c r="F21" s="57" t="n">
         <v>95</v>
       </c>
-      <c r="G21" s="8">
+      <c r="G21" s="57">
         <f>IF($F21="","",$F21-$C21-$M21-$N21)</f>
         <v/>
       </c>
@@ -2382,29 +2406,29 @@
       <c r="I21" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J21" s="6">
+      <c r="J21" s="55">
         <f>$C21/$I21</f>
         <v/>
       </c>
-      <c r="K21" s="6">
+      <c r="K21" s="55">
         <f>IF($F21="","",$F21/$I21)</f>
         <v/>
       </c>
-      <c r="L21" s="6">
+      <c r="L21" s="55">
         <f>IF($G21="","",$G21/$I21)</f>
         <v/>
       </c>
-      <c r="M21" s="7">
+      <c r="M21" s="56">
         <f>IF($F21="","",$F21*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N21" s="6" t="n">
+      <c r="N21" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O21" s="11" t="n">
+      <c r="O21" s="58" t="n">
         <v>45</v>
       </c>
-      <c r="P21" s="11" t="n">
+      <c r="P21" s="58" t="n">
         <v>11.7</v>
       </c>
       <c r="Q21" s="12" t="inlineStr">
@@ -2442,7 +2466,7 @@
       <c r="Y21" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z21" s="8">
+      <c r="Z21" s="57">
         <f>IF($G21="","",$G21/$Y21)</f>
         <v/>
       </c>
@@ -2457,25 +2481,25 @@
           <t>CHIARA FERRAGNI robe bustier courte T.M — neuve</t>
         </is>
       </c>
-      <c r="B22" s="5" t="n">
+      <c r="B22" s="54" t="n">
         <v>31.95</v>
       </c>
-      <c r="C22" s="6">
+      <c r="C22" s="55">
         <f>$B22+$Y22*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D22" s="7">
+      <c r="D22" s="56">
         <f>$C22/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="E22" s="6">
+      <c r="E22" s="55">
         <f>CEILING($D22*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F22" s="8" t="n">
+      <c r="F22" s="57" t="n">
         <v>69</v>
       </c>
-      <c r="G22" s="8">
+      <c r="G22" s="57">
         <f>IF($F22="","",$F22-$C22-$M22-$N22)</f>
         <v/>
       </c>
@@ -2486,30 +2510,30 @@
       <c r="I22" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J22" s="6">
+      <c r="J22" s="55">
         <f>$C22/$I22</f>
         <v/>
       </c>
-      <c r="K22" s="6">
+      <c r="K22" s="55">
         <f>IF($F22="","",$F22/$I22)</f>
         <v/>
       </c>
-      <c r="L22" s="6">
+      <c r="L22" s="55">
         <f>IF($G22="","",$G22/$I22)</f>
         <v/>
       </c>
-      <c r="M22" s="7">
+      <c r="M22" s="56">
         <f>IF($F22="","",$F22*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N22" s="6">
+      <c r="N22" s="55">
         <f>IF($F22="","",$F22*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="O22" s="11" t="n">
+      <c r="O22" s="58" t="n">
         <v>25</v>
       </c>
-      <c r="P22" s="11" t="n">
+      <c r="P22" s="58" t="n">
         <v>6.5</v>
       </c>
       <c r="Q22" s="12" t="inlineStr">
@@ -2547,7 +2571,7 @@
       <c r="Y22" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z22" s="8">
+      <c r="Z22" s="57">
         <f>IF($G22="","",$G22/$Y22)</f>
         <v/>
       </c>
@@ -2562,25 +2586,25 @@
           <t>PIER ANTONIO GASPARI robe droite bleu marine T.42 — neuve</t>
         </is>
       </c>
-      <c r="B23" s="5" t="n">
+      <c r="B23" s="54" t="n">
         <v>25.56</v>
       </c>
-      <c r="C23" s="6">
+      <c r="C23" s="55">
         <f>$B23+$Y23*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D23" s="7">
+      <c r="D23" s="56">
         <f>$C23/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="E23" s="6">
+      <c r="E23" s="55">
         <f>CEILING($D23*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F23" s="8" t="n">
+      <c r="F23" s="57" t="n">
         <v>62</v>
       </c>
-      <c r="G23" s="8">
+      <c r="G23" s="57">
         <f>IF($F23="","",$F23-$C23-$M23-$N23)</f>
         <v/>
       </c>
@@ -2591,30 +2615,30 @@
       <c r="I23" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J23" s="6">
+      <c r="J23" s="55">
         <f>$C23/$I23</f>
         <v/>
       </c>
-      <c r="K23" s="6">
+      <c r="K23" s="55">
         <f>IF($F23="","",$F23/$I23)</f>
         <v/>
       </c>
-      <c r="L23" s="6">
+      <c r="L23" s="55">
         <f>IF($G23="","",$G23/$I23)</f>
         <v/>
       </c>
-      <c r="M23" s="7">
+      <c r="M23" s="56">
         <f>IF($F23="","",$F23*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N23" s="6">
+      <c r="N23" s="55">
         <f>IF($F23="","",$F23*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="O23" s="11" t="n">
+      <c r="O23" s="58" t="n">
         <v>20</v>
       </c>
-      <c r="P23" s="11" t="n">
+      <c r="P23" s="58" t="n">
         <v>5.2</v>
       </c>
       <c r="Q23" s="12" t="inlineStr">
@@ -2652,7 +2676,7 @@
       <c r="Y23" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z23" s="8">
+      <c r="Z23" s="57">
         <f>IF($G23="","",$G23/$Y23)</f>
         <v/>
       </c>
@@ -2667,25 +2691,25 @@
           <t>Lot de 4 toupies BEYBLADE HASBRO</t>
         </is>
       </c>
-      <c r="B24" s="23" t="n">
+      <c r="B24" s="64" t="n">
         <v>19.17</v>
       </c>
-      <c r="C24" s="24">
+      <c r="C24" s="65">
         <f>$B24+$Y24*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D24" s="25">
+      <c r="D24" s="66">
         <f>$C24/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E24" s="24">
+      <c r="E24" s="65">
         <f>CEILING($D24*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F24" s="26" t="n">
+      <c r="F24" s="67" t="n">
         <v>55</v>
       </c>
-      <c r="G24" s="26">
+      <c r="G24" s="67">
         <f>IF($F24="","",$F24-$C24-$M24-$N24)</f>
         <v/>
       </c>
@@ -2696,29 +2720,29 @@
       <c r="I24" s="28" t="n">
         <v>4</v>
       </c>
-      <c r="J24" s="24">
+      <c r="J24" s="65">
         <f>$C24/$I24</f>
         <v/>
       </c>
-      <c r="K24" s="24">
+      <c r="K24" s="65">
         <f>IF($F24="","",$F24/$I24)</f>
         <v/>
       </c>
-      <c r="L24" s="24">
+      <c r="L24" s="65">
         <f>IF($G24="","",$G24/$I24)</f>
         <v/>
       </c>
-      <c r="M24" s="25">
+      <c r="M24" s="66">
         <f>IF($F24="","",$F24*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N24" s="24" t="n">
+      <c r="N24" s="65" t="n">
         <v>0</v>
       </c>
-      <c r="O24" s="29" t="n">
+      <c r="O24" s="68" t="n">
         <v>15</v>
       </c>
-      <c r="P24" s="29" t="n">
+      <c r="P24" s="68" t="n">
         <v>3.9</v>
       </c>
       <c r="Q24" s="30" t="inlineStr">
@@ -2756,7 +2780,7 @@
       <c r="Y24" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="Z24" s="26">
+      <c r="Z24" s="67">
         <f>IF($G24="","",$G24/$Y24)</f>
         <v/>
       </c>
@@ -2766,105 +2790,113 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>Ballerines MASSIMO DUTTI P.41 — traces d'essayage</t>
         </is>
       </c>
-      <c r="B25" s="5" t="n">
+      <c r="B25" s="59" t="n">
         <v>25.2</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C25" s="60">
         <f>$B25+$Y25*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D25" s="7">
+      <c r="D25" s="61">
         <f>$C25/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E25" s="6">
+      <c r="E25" s="60">
         <f>CEILING($D25*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F25" s="8" t="n">
-        <v>61</v>
-      </c>
-      <c r="G25" s="8">
+      <c r="F25" s="62" t="n">
+        <v>50</v>
+      </c>
+      <c r="G25" s="62">
         <f>IF($F25="","",$F25-$C25-$M25-$N25)</f>
         <v/>
       </c>
-      <c r="H25" s="9">
+      <c r="H25" s="18">
         <f>IF($G25="","",$G25/$C25)</f>
         <v/>
       </c>
-      <c r="I25" s="10" t="n">
+      <c r="I25" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J25" s="6">
+      <c r="J25" s="60">
         <f>$C25/$I25</f>
         <v/>
       </c>
-      <c r="K25" s="6">
+      <c r="K25" s="60">
         <f>IF($F25="","",$F25/$I25)</f>
         <v/>
       </c>
-      <c r="L25" s="6">
+      <c r="L25" s="60">
         <f>IF($G25="","",$G25/$I25)</f>
         <v/>
       </c>
-      <c r="M25" s="7">
+      <c r="M25" s="61">
         <f>IF($F25="","",$F25*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N25" s="6" t="n">
+      <c r="N25" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="O25" s="11" t="n">
+      <c r="O25" s="63" t="n">
         <v>20</v>
       </c>
-      <c r="P25" s="11" t="n">
+      <c r="P25" s="63" t="n">
         <v>5.2</v>
       </c>
-      <c r="Q25" s="12" t="inlineStr">
+      <c r="Q25" s="21" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="R25" s="12" t="inlineStr">
+      <c r="R25" s="21" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="S25" s="12" t="inlineStr">
+      <c r="S25" s="21" t="inlineStr">
         <is>
           <t>FB2026-43716</t>
         </is>
       </c>
-      <c r="T25" s="12" t="inlineStr">
+      <c r="T25" s="21" t="inlineStr">
         <is>
           <t>439</t>
         </is>
       </c>
-      <c r="U25" s="4" t="inlineStr">
-        <is>
-          <t>Leboncoin + eBay</t>
-        </is>
-      </c>
-      <c r="V25" s="4" t="inlineStr"/>
-      <c r="W25" s="4" t="inlineStr">
+      <c r="U25" s="13" t="inlineStr">
+        <is>
+          <t>Vinted — non encaissé</t>
+        </is>
+      </c>
+      <c r="V25" s="13" t="inlineStr">
+        <is>
+          <t>VENDUE, en attente</t>
+        </is>
+      </c>
+      <c r="W25" s="13" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="X25" s="4" t="inlineStr"/>
-      <c r="Y25" s="4" t="n">
+      <c r="X25" s="13" t="inlineStr">
+        <is>
+          <t>18/10/2026</t>
+        </is>
+      </c>
+      <c r="Y25" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="Z25" s="8">
+      <c r="Z25" s="62">
         <f>IF($G25="","",$G25/$Y25)</f>
         <v/>
       </c>
-      <c r="AA25" s="4">
+      <c r="AA25" s="13">
         <f>IF($Z25="","",IF($Z25&gt;=25,"atteint",TEXT(25-$Z25,"0.00")&amp;" € manquants"))</f>
         <v/>
       </c>
@@ -2875,25 +2907,25 @@
           <t>GEOX baskets P.35 — neuves</t>
         </is>
       </c>
-      <c r="B26" s="5" t="n">
+      <c r="B26" s="54" t="n">
         <v>21.73</v>
       </c>
-      <c r="C26" s="6">
+      <c r="C26" s="55">
         <f>$B26+$Y26*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D26" s="7">
+      <c r="D26" s="56">
         <f>$C26/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E26" s="6">
+      <c r="E26" s="55">
         <f>CEILING($D26*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F26" s="8" t="n">
+      <c r="F26" s="57" t="n">
         <v>54</v>
       </c>
-      <c r="G26" s="8">
+      <c r="G26" s="57">
         <f>IF($F26="","",$F26-$C26-$M26-$N26)</f>
         <v/>
       </c>
@@ -2904,29 +2936,29 @@
       <c r="I26" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J26" s="6">
+      <c r="J26" s="55">
         <f>$C26/$I26</f>
         <v/>
       </c>
-      <c r="K26" s="6">
+      <c r="K26" s="55">
         <f>IF($F26="","",$F26/$I26)</f>
         <v/>
       </c>
-      <c r="L26" s="6">
+      <c r="L26" s="55">
         <f>IF($G26="","",$G26/$I26)</f>
         <v/>
       </c>
-      <c r="M26" s="7">
+      <c r="M26" s="56">
         <f>IF($F26="","",$F26*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N26" s="6" t="n">
+      <c r="N26" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O26" s="11" t="n">
+      <c r="O26" s="58" t="n">
         <v>17</v>
       </c>
-      <c r="P26" s="11" t="n">
+      <c r="P26" s="58" t="n">
         <v>4.42</v>
       </c>
       <c r="Q26" s="12" t="inlineStr">
@@ -2964,7 +2996,7 @@
       <c r="Y26" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z26" s="8">
+      <c r="Z26" s="57">
         <f>IF($G26="","",$G26/$Y26)</f>
         <v/>
       </c>
@@ -2979,25 +3011,25 @@
           <t>1 booster box Pokémon MEGA Nihil Zero (Munikis Zero) M3 — 30 boosters de 5 cartes — 2 lots de 15 à 49 €, blister à photographier avant ouverture</t>
         </is>
       </c>
-      <c r="B27" s="5" t="n">
+      <c r="B27" s="54" t="n">
         <v>69.23999999999999</v>
       </c>
-      <c r="C27" s="6">
+      <c r="C27" s="55">
         <f>$B27</f>
         <v/>
       </c>
-      <c r="D27" s="7">
+      <c r="D27" s="56">
         <f>$C27/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E27" s="6">
+      <c r="E27" s="55">
         <f>CEILING($D27*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F27" s="8" t="n">
+      <c r="F27" s="57" t="n">
         <v>98</v>
       </c>
-      <c r="G27" s="8">
+      <c r="G27" s="57">
         <f>IF($F27="","",$F27-$C27-$M27-$N27)</f>
         <v/>
       </c>
@@ -3008,23 +3040,23 @@
       <c r="I27" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="J27" s="6">
+      <c r="J27" s="55">
         <f>$C27/$I27</f>
         <v/>
       </c>
-      <c r="K27" s="6">
+      <c r="K27" s="55">
         <f>IF($F27="","",$F27/$I27)</f>
         <v/>
       </c>
-      <c r="L27" s="6">
+      <c r="L27" s="55">
         <f>IF($G27="","",$G27/$I27)</f>
         <v/>
       </c>
-      <c r="M27" s="7">
+      <c r="M27" s="56">
         <f>IF($F27="","",$F27*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N27" s="6" t="n">
+      <c r="N27" s="55" t="n">
         <v>0</v>
       </c>
       <c r="O27" s="31" t="n"/>
@@ -3064,7 +3096,7 @@
       <c r="Y27" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="Z27" s="8">
+      <c r="Z27" s="57">
         <f>IF($G27="","",$G27/$Y27)</f>
         <v/>
       </c>
@@ -3079,25 +3111,25 @@
           <t>Veste en jean ARMANI EXCHANGE T.S — neuve</t>
         </is>
       </c>
-      <c r="B28" s="14" t="n">
+      <c r="B28" s="59" t="n">
         <v>25.2</v>
       </c>
-      <c r="C28" s="15">
+      <c r="C28" s="60">
         <f>$B28+$Y28*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D28" s="16">
+      <c r="D28" s="61">
         <f>$C28/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E28" s="15">
+      <c r="E28" s="60">
         <f>CEILING($D28*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F28" s="17" t="n">
+      <c r="F28" s="62" t="n">
         <v>50</v>
       </c>
-      <c r="G28" s="17">
+      <c r="G28" s="62">
         <f>IF($F28="","",$F28-$C28-$M28-$N28)</f>
         <v/>
       </c>
@@ -3108,29 +3140,29 @@
       <c r="I28" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J28" s="15">
+      <c r="J28" s="60">
         <f>$C28/$I28</f>
         <v/>
       </c>
-      <c r="K28" s="15">
+      <c r="K28" s="60">
         <f>IF($F28="","",$F28/$I28)</f>
         <v/>
       </c>
-      <c r="L28" s="15">
+      <c r="L28" s="60">
         <f>IF($G28="","",$G28/$I28)</f>
         <v/>
       </c>
-      <c r="M28" s="16">
+      <c r="M28" s="61">
         <f>IF($F28="","",$F28*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N28" s="15" t="n">
+      <c r="N28" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="O28" s="20" t="n">
+      <c r="O28" s="63" t="n">
         <v>20</v>
       </c>
-      <c r="P28" s="20" t="n">
+      <c r="P28" s="63" t="n">
         <v>5.2</v>
       </c>
       <c r="Q28" s="21" t="inlineStr">
@@ -3172,7 +3204,7 @@
       <c r="Y28" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="Z28" s="17">
+      <c r="Z28" s="62">
         <f>IF($G28="","",$G28/$Y28)</f>
         <v/>
       </c>
@@ -3187,25 +3219,25 @@
           <t>Short BA&amp;SH Fegor T.34 — neuf</t>
         </is>
       </c>
-      <c r="B29" s="5" t="n">
+      <c r="B29" s="54" t="n">
         <v>50.4</v>
       </c>
-      <c r="C29" s="6">
+      <c r="C29" s="55">
         <f>$B29+$Y29*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D29" s="7">
+      <c r="D29" s="56">
         <f>$C29/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="E29" s="6">
+      <c r="E29" s="55">
         <f>CEILING($D29*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F29" s="8" t="n">
+      <c r="F29" s="57" t="n">
         <v>75</v>
       </c>
-      <c r="G29" s="8">
+      <c r="G29" s="57">
         <f>IF($F29="","",$F29-$C29-$M29-$N29)</f>
         <v/>
       </c>
@@ -3216,30 +3248,30 @@
       <c r="I29" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J29" s="6">
+      <c r="J29" s="55">
         <f>$C29/$I29</f>
         <v/>
       </c>
-      <c r="K29" s="6">
+      <c r="K29" s="55">
         <f>IF($F29="","",$F29/$I29)</f>
         <v/>
       </c>
-      <c r="L29" s="6">
+      <c r="L29" s="55">
         <f>IF($G29="","",$G29/$I29)</f>
         <v/>
       </c>
-      <c r="M29" s="7">
+      <c r="M29" s="56">
         <f>IF($F29="","",$F29*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N29" s="6">
+      <c r="N29" s="55">
         <f>IF($F29="","",$F29*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="O29" s="11" t="n">
+      <c r="O29" s="58" t="n">
         <v>40</v>
       </c>
-      <c r="P29" s="11" t="n">
+      <c r="P29" s="58" t="n">
         <v>10.4</v>
       </c>
       <c r="Q29" s="12" t="inlineStr">
@@ -3277,7 +3309,7 @@
       <c r="Y29" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z29" s="8">
+      <c r="Z29" s="57">
         <f>IF($G29="","",$G29/$Y29)</f>
         <v/>
       </c>
@@ -3292,25 +3324,25 @@
           <t>NEW BALANCE G19064IK Alkaline Green P.38½ — neuves avec boîte</t>
         </is>
       </c>
-      <c r="B30" s="5" t="n">
+      <c r="B30" s="54" t="n">
         <v>75.59999999999999</v>
       </c>
-      <c r="C30" s="6">
+      <c r="C30" s="55">
         <f>$B30+$Y30*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D30" s="7">
+      <c r="D30" s="56">
         <f>$C30/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E30" s="6">
+      <c r="E30" s="55">
         <f>CEILING($D30*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F30" s="8" t="n">
+      <c r="F30" s="57" t="n">
         <v>99</v>
       </c>
-      <c r="G30" s="8">
+      <c r="G30" s="57">
         <f>IF($F30="","",$F30-$C30-$M30-$N30)</f>
         <v/>
       </c>
@@ -3321,29 +3353,29 @@
       <c r="I30" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J30" s="6">
+      <c r="J30" s="55">
         <f>$C30/$I30</f>
         <v/>
       </c>
-      <c r="K30" s="6">
+      <c r="K30" s="55">
         <f>IF($F30="","",$F30/$I30)</f>
         <v/>
       </c>
-      <c r="L30" s="6">
+      <c r="L30" s="55">
         <f>IF($G30="","",$G30/$I30)</f>
         <v/>
       </c>
-      <c r="M30" s="7">
+      <c r="M30" s="56">
         <f>IF($F30="","",$F30*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N30" s="6" t="n">
+      <c r="N30" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O30" s="11" t="n">
+      <c r="O30" s="58" t="n">
         <v>60</v>
       </c>
-      <c r="P30" s="11" t="n">
+      <c r="P30" s="58" t="n">
         <v>15.6</v>
       </c>
       <c r="Q30" s="12" t="inlineStr">
@@ -3381,7 +3413,7 @@
       <c r="Y30" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z30" s="8">
+      <c r="Z30" s="57">
         <f>IF($G30="","",$G30/$Y30)</f>
         <v/>
       </c>
@@ -3396,25 +3428,25 @@
           <t>SALOMON X Ultra 5 Mid GTX P.44 — neuves</t>
         </is>
       </c>
-      <c r="B31" s="14" t="n">
+      <c r="B31" s="59" t="n">
         <v>76.68000000000001</v>
       </c>
-      <c r="C31" s="15">
+      <c r="C31" s="60">
         <f>$B31+$Y31*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D31" s="16">
+      <c r="D31" s="61">
         <f>$C31/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E31" s="15">
+      <c r="E31" s="60">
         <f>CEILING($D31*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F31" s="17" t="n">
+      <c r="F31" s="62" t="n">
         <v>100</v>
       </c>
-      <c r="G31" s="17">
+      <c r="G31" s="62">
         <f>IF($F31="","",$F31-$C31-$M31-$N31)</f>
         <v/>
       </c>
@@ -3425,29 +3457,29 @@
       <c r="I31" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J31" s="15">
+      <c r="J31" s="60">
         <f>$C31/$I31</f>
         <v/>
       </c>
-      <c r="K31" s="15">
+      <c r="K31" s="60">
         <f>IF($F31="","",$F31/$I31)</f>
         <v/>
       </c>
-      <c r="L31" s="15">
+      <c r="L31" s="60">
         <f>IF($G31="","",$G31/$I31)</f>
         <v/>
       </c>
-      <c r="M31" s="16">
+      <c r="M31" s="61">
         <f>IF($F31="","",$F31*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N31" s="15" t="n">
+      <c r="N31" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="O31" s="20" t="n">
+      <c r="O31" s="63" t="n">
         <v>60</v>
       </c>
-      <c r="P31" s="20" t="n">
+      <c r="P31" s="63" t="n">
         <v>15.6</v>
       </c>
       <c r="Q31" s="21" t="inlineStr">
@@ -3489,7 +3521,7 @@
       <c r="Y31" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="Z31" s="17">
+      <c r="Z31" s="62">
         <f>IF($G31="","",$G31/$Y31)</f>
         <v/>
       </c>
@@ -3504,25 +3536,25 @@
           <t>Sac demi-lune nylon noir KARL LAGERFELD JEANS — neuf avec étiquette</t>
         </is>
       </c>
-      <c r="B32" s="14" t="n">
+      <c r="B32" s="59" t="n">
         <v>50.4</v>
       </c>
-      <c r="C32" s="15">
+      <c r="C32" s="60">
         <f>$B32+$Y32*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D32" s="16">
+      <c r="D32" s="61">
         <f>$C32/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E32" s="15">
+      <c r="E32" s="60">
         <f>CEILING($D32*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F32" s="17" t="n">
+      <c r="F32" s="62" t="n">
         <v>70</v>
       </c>
-      <c r="G32" s="17">
+      <c r="G32" s="62">
         <f>IF($F32="","",$F32-$C32-$M32-$N32)</f>
         <v/>
       </c>
@@ -3533,29 +3565,29 @@
       <c r="I32" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J32" s="15">
+      <c r="J32" s="60">
         <f>$C32/$I32</f>
         <v/>
       </c>
-      <c r="K32" s="15">
+      <c r="K32" s="60">
         <f>IF($F32="","",$F32/$I32)</f>
         <v/>
       </c>
-      <c r="L32" s="15">
+      <c r="L32" s="60">
         <f>IF($G32="","",$G32/$I32)</f>
         <v/>
       </c>
-      <c r="M32" s="16">
+      <c r="M32" s="61">
         <f>IF($F32="","",$F32*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N32" s="15" t="n">
+      <c r="N32" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="O32" s="20" t="n">
+      <c r="O32" s="63" t="n">
         <v>40</v>
       </c>
-      <c r="P32" s="20" t="n">
+      <c r="P32" s="63" t="n">
         <v>10.4</v>
       </c>
       <c r="Q32" s="21" t="inlineStr">
@@ -3597,7 +3629,7 @@
       <c r="Y32" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="Z32" s="17">
+      <c r="Z32" s="62">
         <f>IF($G32="","",$G32/$Y32)</f>
         <v/>
       </c>
@@ -3612,25 +3644,25 @@
           <t>EMPORIO ARMANI baskets P.36 — neuves</t>
         </is>
       </c>
-      <c r="B33" s="5" t="n">
+      <c r="B33" s="54" t="n">
         <v>51.12</v>
       </c>
-      <c r="C33" s="6">
+      <c r="C33" s="55">
         <f>$B33+$Y33*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D33" s="7">
+      <c r="D33" s="56">
         <f>$C33/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E33" s="6">
+      <c r="E33" s="55">
         <f>CEILING($D33*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F33" s="8" t="n">
+      <c r="F33" s="57" t="n">
         <v>69</v>
       </c>
-      <c r="G33" s="8">
+      <c r="G33" s="57">
         <f>IF($F33="","",$F33-$C33-$M33-$N33)</f>
         <v/>
       </c>
@@ -3641,29 +3673,29 @@
       <c r="I33" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J33" s="6">
+      <c r="J33" s="55">
         <f>$C33/$I33</f>
         <v/>
       </c>
-      <c r="K33" s="6">
+      <c r="K33" s="55">
         <f>IF($F33="","",$F33/$I33)</f>
         <v/>
       </c>
-      <c r="L33" s="6">
+      <c r="L33" s="55">
         <f>IF($G33="","",$G33/$I33)</f>
         <v/>
       </c>
-      <c r="M33" s="7">
+      <c r="M33" s="56">
         <f>IF($F33="","",$F33*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N33" s="6" t="n">
+      <c r="N33" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O33" s="11" t="n">
+      <c r="O33" s="58" t="n">
         <v>40</v>
       </c>
-      <c r="P33" s="11" t="n">
+      <c r="P33" s="58" t="n">
         <v>10.4</v>
       </c>
       <c r="Q33" s="12" t="inlineStr">
@@ -3701,7 +3733,7 @@
       <c r="Y33" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z33" s="8">
+      <c r="Z33" s="57">
         <f>IF($G33="","",$G33/$Y33)</f>
         <v/>
       </c>
@@ -3716,25 +3748,25 @@
           <t>Lot de 4 toupies BEYBLADE HASBRO</t>
         </is>
       </c>
-      <c r="B34" s="23" t="n">
+      <c r="B34" s="64" t="n">
         <v>38.34</v>
       </c>
-      <c r="C34" s="24">
+      <c r="C34" s="65">
         <f>$B34+$Y34*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D34" s="25">
+      <c r="D34" s="66">
         <f>$C34/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E34" s="24">
+      <c r="E34" s="65">
         <f>CEILING($D34*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F34" s="26" t="n">
+      <c r="F34" s="67" t="n">
         <v>55</v>
       </c>
-      <c r="G34" s="26">
+      <c r="G34" s="67">
         <f>IF($F34="","",$F34-$C34-$M34-$N34)</f>
         <v/>
       </c>
@@ -3745,29 +3777,29 @@
       <c r="I34" s="28" t="n">
         <v>4</v>
       </c>
-      <c r="J34" s="24">
+      <c r="J34" s="65">
         <f>$C34/$I34</f>
         <v/>
       </c>
-      <c r="K34" s="24">
+      <c r="K34" s="65">
         <f>IF($F34="","",$F34/$I34)</f>
         <v/>
       </c>
-      <c r="L34" s="24">
+      <c r="L34" s="65">
         <f>IF($G34="","",$G34/$I34)</f>
         <v/>
       </c>
-      <c r="M34" s="25">
+      <c r="M34" s="66">
         <f>IF($F34="","",$F34*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N34" s="24" t="n">
+      <c r="N34" s="65" t="n">
         <v>0</v>
       </c>
-      <c r="O34" s="29" t="n">
+      <c r="O34" s="68" t="n">
         <v>30</v>
       </c>
-      <c r="P34" s="29" t="n">
+      <c r="P34" s="68" t="n">
         <v>7.8</v>
       </c>
       <c r="Q34" s="30" t="inlineStr">
@@ -3805,7 +3837,7 @@
       <c r="Y34" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="Z34" s="26">
+      <c r="Z34" s="67">
         <f>IF($G34="","",$G34/$Y34)</f>
         <v/>
       </c>
@@ -3820,25 +3852,25 @@
           <t>NEW BALANCE sneakers P.38 — neuves</t>
         </is>
       </c>
-      <c r="B35" s="5" t="n">
+      <c r="B35" s="54" t="n">
         <v>38.34</v>
       </c>
-      <c r="C35" s="6">
+      <c r="C35" s="55">
         <f>$B35+$Y35*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D35" s="7">
+      <c r="D35" s="56">
         <f>$C35/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E35" s="6">
+      <c r="E35" s="55">
         <f>CEILING($D35*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F35" s="8" t="n">
+      <c r="F35" s="57" t="n">
         <v>54</v>
       </c>
-      <c r="G35" s="8">
+      <c r="G35" s="57">
         <f>IF($F35="","",$F35-$C35-$M35-$N35)</f>
         <v/>
       </c>
@@ -3849,29 +3881,29 @@
       <c r="I35" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J35" s="6">
+      <c r="J35" s="55">
         <f>$C35/$I35</f>
         <v/>
       </c>
-      <c r="K35" s="6">
+      <c r="K35" s="55">
         <f>IF($F35="","",$F35/$I35)</f>
         <v/>
       </c>
-      <c r="L35" s="6">
+      <c r="L35" s="55">
         <f>IF($G35="","",$G35/$I35)</f>
         <v/>
       </c>
-      <c r="M35" s="7">
+      <c r="M35" s="56">
         <f>IF($F35="","",$F35*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N35" s="6" t="n">
+      <c r="N35" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O35" s="11" t="n">
+      <c r="O35" s="58" t="n">
         <v>30</v>
       </c>
-      <c r="P35" s="11" t="n">
+      <c r="P35" s="58" t="n">
         <v>7.8</v>
       </c>
       <c r="Q35" s="12" t="inlineStr">
@@ -3909,7 +3941,7 @@
       <c r="Y35" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z35" s="8">
+      <c r="Z35" s="57">
         <f>IF($G35="","",$G35/$Y35)</f>
         <v/>
       </c>
@@ -3924,25 +3956,25 @@
           <t>NEW BALANCE baskets montantes P.44 — neuves</t>
         </is>
       </c>
-      <c r="B36" s="5" t="n">
+      <c r="B36" s="54" t="n">
         <v>51.12</v>
       </c>
-      <c r="C36" s="6">
+      <c r="C36" s="55">
         <f>$B36+$Y36*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D36" s="7">
+      <c r="D36" s="56">
         <f>$C36/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E36" s="6">
+      <c r="E36" s="55">
         <f>CEILING($D36*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F36" s="8" t="n">
+      <c r="F36" s="57" t="n">
         <v>65</v>
       </c>
-      <c r="G36" s="8">
+      <c r="G36" s="57">
         <f>IF($F36="","",$F36-$C36-$M36-$N36)</f>
         <v/>
       </c>
@@ -3953,29 +3985,29 @@
       <c r="I36" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J36" s="6">
+      <c r="J36" s="55">
         <f>$C36/$I36</f>
         <v/>
       </c>
-      <c r="K36" s="6">
+      <c r="K36" s="55">
         <f>IF($F36="","",$F36/$I36)</f>
         <v/>
       </c>
-      <c r="L36" s="6">
+      <c r="L36" s="55">
         <f>IF($G36="","",$G36/$I36)</f>
         <v/>
       </c>
-      <c r="M36" s="7">
+      <c r="M36" s="56">
         <f>IF($F36="","",$F36*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N36" s="6" t="n">
+      <c r="N36" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O36" s="11" t="n">
+      <c r="O36" s="58" t="n">
         <v>40</v>
       </c>
-      <c r="P36" s="11" t="n">
+      <c r="P36" s="58" t="n">
         <v>10.4</v>
       </c>
       <c r="Q36" s="12" t="inlineStr">
@@ -4013,7 +4045,7 @@
       <c r="Y36" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z36" s="8">
+      <c r="Z36" s="57">
         <f>IF($G36="","",$G36/$Y36)</f>
         <v/>
       </c>
@@ -4028,25 +4060,25 @@
           <t>TOMMY JEANS baskets basses P.40 — neuves</t>
         </is>
       </c>
-      <c r="B37" s="5" t="n">
+      <c r="B37" s="54" t="n">
         <v>52.4</v>
       </c>
-      <c r="C37" s="6">
+      <c r="C37" s="55">
         <f>$B37+$Y37*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D37" s="7">
+      <c r="D37" s="56">
         <f>$C37/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E37" s="6">
+      <c r="E37" s="55">
         <f>CEILING($D37*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F37" s="8" t="n">
+      <c r="F37" s="57" t="n">
         <v>65</v>
       </c>
-      <c r="G37" s="8">
+      <c r="G37" s="57">
         <f>IF($F37="","",$F37-$C37-$M37-$N37)</f>
         <v/>
       </c>
@@ -4057,29 +4089,29 @@
       <c r="I37" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J37" s="6">
+      <c r="J37" s="55">
         <f>$C37/$I37</f>
         <v/>
       </c>
-      <c r="K37" s="6">
+      <c r="K37" s="55">
         <f>IF($F37="","",$F37/$I37)</f>
         <v/>
       </c>
-      <c r="L37" s="6">
+      <c r="L37" s="55">
         <f>IF($G37="","",$G37/$I37)</f>
         <v/>
       </c>
-      <c r="M37" s="7">
+      <c r="M37" s="56">
         <f>IF($F37="","",$F37*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N37" s="6" t="n">
+      <c r="N37" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O37" s="11" t="n">
+      <c r="O37" s="58" t="n">
         <v>41</v>
       </c>
-      <c r="P37" s="11" t="n">
+      <c r="P37" s="58" t="n">
         <v>10.66</v>
       </c>
       <c r="Q37" s="12" t="inlineStr">
@@ -4117,7 +4149,7 @@
       <c r="Y37" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z37" s="8">
+      <c r="Z37" s="57">
         <f>IF($G37="","",$G37/$Y37)</f>
         <v/>
       </c>
@@ -4132,25 +4164,25 @@
           <t>LACOSTE sneakers P.42 — neuves</t>
         </is>
       </c>
-      <c r="B38" s="14" t="n">
+      <c r="B38" s="59" t="n">
         <v>57.51</v>
       </c>
-      <c r="C38" s="15">
+      <c r="C38" s="60">
         <f>$B38+$Y38*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D38" s="16">
+      <c r="D38" s="61">
         <f>$C38/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E38" s="15">
+      <c r="E38" s="60">
         <f>CEILING($D38*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F38" s="17" t="n">
+      <c r="F38" s="62" t="n">
         <v>70</v>
       </c>
-      <c r="G38" s="17">
+      <c r="G38" s="62">
         <f>IF($F38="","",$F38-$C38-$M38-$N38)</f>
         <v/>
       </c>
@@ -4161,29 +4193,29 @@
       <c r="I38" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J38" s="15">
+      <c r="J38" s="60">
         <f>$C38/$I38</f>
         <v/>
       </c>
-      <c r="K38" s="15">
+      <c r="K38" s="60">
         <f>IF($F38="","",$F38/$I38)</f>
         <v/>
       </c>
-      <c r="L38" s="15">
+      <c r="L38" s="60">
         <f>IF($G38="","",$G38/$I38)</f>
         <v/>
       </c>
-      <c r="M38" s="16">
+      <c r="M38" s="61">
         <f>IF($F38="","",$F38*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N38" s="15" t="n">
+      <c r="N38" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="O38" s="20" t="n">
+      <c r="O38" s="63" t="n">
         <v>45</v>
       </c>
-      <c r="P38" s="20" t="n">
+      <c r="P38" s="63" t="n">
         <v>11.7</v>
       </c>
       <c r="Q38" s="21" t="inlineStr">
@@ -4225,7 +4257,7 @@
       <c r="Y38" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="Z38" s="17">
+      <c r="Z38" s="62">
         <f>IF($G38="","",$G38/$Y38)</f>
         <v/>
       </c>
@@ -4240,25 +4272,25 @@
           <t>Pompe immergée ROBBY VP550W noir et bleu — produit d'occasion</t>
         </is>
       </c>
-      <c r="B39" s="5" t="n">
+      <c r="B39" s="54" t="n">
         <v>35.9</v>
       </c>
-      <c r="C39" s="6">
+      <c r="C39" s="55">
         <f>$B39</f>
         <v/>
       </c>
-      <c r="D39" s="7">
+      <c r="D39" s="56">
         <f>$C39/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E39" s="6">
+      <c r="E39" s="55">
         <f>CEILING($D39*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F39" s="8" t="n">
+      <c r="F39" s="57" t="n">
         <v>45</v>
       </c>
-      <c r="G39" s="8">
+      <c r="G39" s="57">
         <f>IF($F39="","",$F39-$C39-$M39-$N39)</f>
         <v/>
       </c>
@@ -4269,23 +4301,23 @@
       <c r="I39" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J39" s="6">
+      <c r="J39" s="55">
         <f>$C39/$I39</f>
         <v/>
       </c>
-      <c r="K39" s="6">
+      <c r="K39" s="55">
         <f>IF($F39="","",$F39/$I39)</f>
         <v/>
       </c>
-      <c r="L39" s="6">
+      <c r="L39" s="55">
         <f>IF($G39="","",$G39/$I39)</f>
         <v/>
       </c>
-      <c r="M39" s="7">
+      <c r="M39" s="56">
         <f>IF($F39="","",$F39*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N39" s="6" t="n">
+      <c r="N39" s="55" t="n">
         <v>0</v>
       </c>
       <c r="O39" s="31" t="n"/>
@@ -4325,7 +4357,7 @@
       <c r="Y39" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z39" s="8">
+      <c r="Z39" s="57">
         <f>IF($G39="","",$G39/$Y39)</f>
         <v/>
       </c>
@@ -4340,25 +4372,25 @@
           <t>Pompe immergée ROBBY VP550W noir/gris — comme neuf, SOCLE CASSÉ</t>
         </is>
       </c>
-      <c r="B40" s="5" t="n">
+      <c r="B40" s="54" t="n">
         <v>28.29</v>
       </c>
-      <c r="C40" s="6">
+      <c r="C40" s="55">
         <f>$B40</f>
         <v/>
       </c>
-      <c r="D40" s="7">
+      <c r="D40" s="56">
         <f>$C40/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E40" s="6">
+      <c r="E40" s="55">
         <f>CEILING($D40*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F40" s="8" t="n">
+      <c r="F40" s="57" t="n">
         <v>35</v>
       </c>
-      <c r="G40" s="8">
+      <c r="G40" s="57">
         <f>IF($F40="","",$F40-$C40-$M40-$N40)</f>
         <v/>
       </c>
@@ -4369,23 +4401,23 @@
       <c r="I40" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J40" s="6">
+      <c r="J40" s="55">
         <f>$C40/$I40</f>
         <v/>
       </c>
-      <c r="K40" s="6">
+      <c r="K40" s="55">
         <f>IF($F40="","",$F40/$I40)</f>
         <v/>
       </c>
-      <c r="L40" s="6">
+      <c r="L40" s="55">
         <f>IF($G40="","",$G40/$I40)</f>
         <v/>
       </c>
-      <c r="M40" s="7">
+      <c r="M40" s="56">
         <f>IF($F40="","",$F40*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N40" s="6" t="n">
+      <c r="N40" s="55" t="n">
         <v>0</v>
       </c>
       <c r="O40" s="31" t="n"/>
@@ -4425,7 +4457,7 @@
       <c r="Y40" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z40" s="8">
+      <c r="Z40" s="57">
         <f>IF($G40="","",$G40/$Y40)</f>
         <v/>
       </c>
@@ -4440,25 +4472,25 @@
           <t>2 boosters Pokémon MEGA Storm Emeralda M6 — 5 cartes chacun — set sorti le 31/07/2026, publier vite</t>
         </is>
       </c>
-      <c r="B41" s="5" t="n">
+      <c r="B41" s="54" t="n">
         <v>12.74</v>
       </c>
-      <c r="C41" s="6">
+      <c r="C41" s="55">
         <f>$B41</f>
         <v/>
       </c>
-      <c r="D41" s="7">
+      <c r="D41" s="56">
         <f>$C41/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E41" s="6">
+      <c r="E41" s="55">
         <f>CEILING($D41*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F41" s="8" t="n">
+      <c r="F41" s="57" t="n">
         <v>19</v>
       </c>
-      <c r="G41" s="8">
+      <c r="G41" s="57">
         <f>IF($F41="","",$F41-$C41-$M41-$N41)</f>
         <v/>
       </c>
@@ -4469,23 +4501,23 @@
       <c r="I41" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J41" s="6">
+      <c r="J41" s="55">
         <f>$C41/$I41</f>
         <v/>
       </c>
-      <c r="K41" s="6">
+      <c r="K41" s="55">
         <f>IF($F41="","",$F41/$I41)</f>
         <v/>
       </c>
-      <c r="L41" s="6">
+      <c r="L41" s="55">
         <f>IF($G41="","",$G41/$I41)</f>
         <v/>
       </c>
-      <c r="M41" s="7">
+      <c r="M41" s="56">
         <f>IF($F41="","",$F41*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N41" s="6" t="n">
+      <c r="N41" s="55" t="n">
         <v>0</v>
       </c>
       <c r="O41" s="31" t="n"/>
@@ -4525,7 +4557,7 @@
       <c r="Y41" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z41" s="8">
+      <c r="Z41" s="57">
         <f>IF($G41="","",$G41/$Y41)</f>
         <v/>
       </c>
@@ -4540,23 +4572,23 @@
           <t>1 booster Pokémon High Class Pack MEGA Dream ex M2a — 10 cartes dans le booster</t>
         </is>
       </c>
-      <c r="B42" s="14" t="n">
+      <c r="B42" s="59" t="n">
         <v>12.95</v>
       </c>
-      <c r="C42" s="15">
+      <c r="C42" s="60">
         <f>$B42</f>
         <v/>
       </c>
-      <c r="D42" s="16">
+      <c r="D42" s="61">
         <f>$C42/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E42" s="15">
+      <c r="E42" s="60">
         <f>CEILING($D42*Paramètres!$B$24,1)</f>
         <v/>
       </c>
       <c r="F42" s="32" t="n"/>
-      <c r="G42" s="17">
+      <c r="G42" s="62">
         <f>IF($F42="","",$F42-$C42-$M42-$N42)</f>
         <v/>
       </c>
@@ -4567,23 +4599,23 @@
       <c r="I42" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J42" s="15">
+      <c r="J42" s="60">
         <f>$C42/$I42</f>
         <v/>
       </c>
-      <c r="K42" s="15">
+      <c r="K42" s="60">
         <f>IF($F42="","",$F42/$I42)</f>
         <v/>
       </c>
-      <c r="L42" s="15">
+      <c r="L42" s="60">
         <f>IF($G42="","",$G42/$I42)</f>
         <v/>
       </c>
-      <c r="M42" s="16">
+      <c r="M42" s="61">
         <f>IF($F42="","",$F42*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N42" s="15" t="n">
+      <c r="N42" s="60" t="n">
         <v>0</v>
       </c>
       <c r="O42" s="32" t="n"/>
@@ -4627,7 +4659,7 @@
       <c r="Y42" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="Z42" s="17">
+      <c r="Z42" s="62">
         <f>IF($G42="","",$G42/$Y42)</f>
         <v/>
       </c>
@@ -4642,23 +4674,23 @@
           <t>Pompe immergée ROBBY VP550W bleu et noir — occasion, NE MARCHE QU'EN MODE AUTO</t>
         </is>
       </c>
-      <c r="B43" s="14" t="n">
+      <c r="B43" s="59" t="n">
         <v>19.41</v>
       </c>
-      <c r="C43" s="15">
+      <c r="C43" s="60">
         <f>$B43</f>
         <v/>
       </c>
-      <c r="D43" s="16">
+      <c r="D43" s="61">
         <f>$C43/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E43" s="15">
+      <c r="E43" s="60">
         <f>CEILING($D43*Paramètres!$B$24,1)</f>
         <v/>
       </c>
       <c r="F43" s="32" t="n"/>
-      <c r="G43" s="17">
+      <c r="G43" s="62">
         <f>IF($F43="","",$F43-$C43-$M43-$N43)</f>
         <v/>
       </c>
@@ -4669,23 +4701,23 @@
       <c r="I43" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J43" s="15">
+      <c r="J43" s="60">
         <f>$C43/$I43</f>
         <v/>
       </c>
-      <c r="K43" s="15">
+      <c r="K43" s="60">
         <f>IF($F43="","",$F43/$I43)</f>
         <v/>
       </c>
-      <c r="L43" s="15">
+      <c r="L43" s="60">
         <f>IF($G43="","",$G43/$I43)</f>
         <v/>
       </c>
-      <c r="M43" s="16">
+      <c r="M43" s="61">
         <f>IF($F43="","",$F43*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N43" s="15" t="n">
+      <c r="N43" s="60" t="n">
         <v>0</v>
       </c>
       <c r="O43" s="32" t="n"/>
@@ -4729,7 +4761,7 @@
       <c r="Y43" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="Z43" s="17">
+      <c r="Z43" s="62">
         <f>IF($G43="","",$G43/$Y43)</f>
         <v/>
       </c>
@@ -4744,23 +4776,23 @@
           <t>Baskets NIKE Air Max Moto 2K P.44.5 — neuves</t>
         </is>
       </c>
-      <c r="B44" s="14" t="n">
+      <c r="B44" s="59" t="n">
         <v>50.4</v>
       </c>
-      <c r="C44" s="15">
+      <c r="C44" s="60">
         <f>$B44+$Y44*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D44" s="16">
+      <c r="D44" s="61">
         <f>$C44/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E44" s="15">
+      <c r="E44" s="60">
         <f>CEILING($D44*Paramètres!$B$24,1)</f>
         <v/>
       </c>
       <c r="F44" s="32" t="n"/>
-      <c r="G44" s="17">
+      <c r="G44" s="62">
         <f>IF($F44="","",$F44-$C44-$M44-$N44)</f>
         <v/>
       </c>
@@ -4771,29 +4803,29 @@
       <c r="I44" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J44" s="15">
+      <c r="J44" s="60">
         <f>$C44/$I44</f>
         <v/>
       </c>
-      <c r="K44" s="15">
+      <c r="K44" s="60">
         <f>IF($F44="","",$F44/$I44)</f>
         <v/>
       </c>
-      <c r="L44" s="15">
+      <c r="L44" s="60">
         <f>IF($G44="","",$G44/$I44)</f>
         <v/>
       </c>
-      <c r="M44" s="16">
+      <c r="M44" s="61">
         <f>IF($F44="","",$F44*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N44" s="15" t="n">
+      <c r="N44" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="O44" s="20" t="n">
+      <c r="O44" s="63" t="n">
         <v>40</v>
       </c>
-      <c r="P44" s="20" t="n">
+      <c r="P44" s="63" t="n">
         <v>10.4</v>
       </c>
       <c r="Q44" s="21" t="inlineStr">
@@ -4835,7 +4867,7 @@
       <c r="Y44" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="Z44" s="17">
+      <c r="Z44" s="62">
         <f>IF($G44="","",$G44/$Y44)</f>
         <v/>
       </c>
@@ -4850,23 +4882,23 @@
           <t>Baskets HOKA P.37 1/3 — neuves</t>
         </is>
       </c>
-      <c r="B45" s="14" t="n">
+      <c r="B45" s="59" t="n">
         <v>63</v>
       </c>
-      <c r="C45" s="15">
+      <c r="C45" s="60">
         <f>$B45+$Y45*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D45" s="16">
+      <c r="D45" s="61">
         <f>$C45/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E45" s="15">
+      <c r="E45" s="60">
         <f>CEILING($D45*Paramètres!$B$24,1)</f>
         <v/>
       </c>
       <c r="F45" s="32" t="n"/>
-      <c r="G45" s="17">
+      <c r="G45" s="62">
         <f>IF($F45="","",$F45-$C45-$M45-$N45)</f>
         <v/>
       </c>
@@ -4877,29 +4909,29 @@
       <c r="I45" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J45" s="15">
+      <c r="J45" s="60">
         <f>$C45/$I45</f>
         <v/>
       </c>
-      <c r="K45" s="15">
+      <c r="K45" s="60">
         <f>IF($F45="","",$F45/$I45)</f>
         <v/>
       </c>
-      <c r="L45" s="15">
+      <c r="L45" s="60">
         <f>IF($G45="","",$G45/$I45)</f>
         <v/>
       </c>
-      <c r="M45" s="16">
+      <c r="M45" s="61">
         <f>IF($F45="","",$F45*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N45" s="15" t="n">
+      <c r="N45" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="O45" s="20" t="n">
+      <c r="O45" s="63" t="n">
         <v>50</v>
       </c>
-      <c r="P45" s="20" t="n">
+      <c r="P45" s="63" t="n">
         <v>13</v>
       </c>
       <c r="Q45" s="21" t="inlineStr">
@@ -4941,7 +4973,7 @@
       <c r="Y45" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="Z45" s="17">
+      <c r="Z45" s="62">
         <f>IF($G45="","",$G45/$Y45)</f>
         <v/>
       </c>
@@ -4956,21 +4988,21 @@
           <t>TOTAL — 40 lots</t>
         </is>
       </c>
-      <c r="B46" s="34">
+      <c r="B46" s="69">
         <f>SUM(B6:B45)</f>
         <v/>
       </c>
-      <c r="C46" s="34">
+      <c r="C46" s="69">
         <f>SUM(C6:C45)</f>
         <v/>
       </c>
       <c r="D46" s="35" t="n"/>
       <c r="E46" s="35" t="n"/>
-      <c r="F46" s="34">
+      <c r="F46" s="69">
         <f>SUM(F6:F45)</f>
         <v/>
       </c>
-      <c r="G46" s="34">
+      <c r="G46" s="69">
         <f>SUM(G6:G45)</f>
         <v/>
       </c>
@@ -4978,18 +5010,18 @@
         <f>G46/C46</f>
         <v/>
       </c>
-      <c r="I46" s="37">
+      <c r="I46" s="70">
         <f>SUM(I6:I45)</f>
         <v/>
       </c>
       <c r="J46" s="35" t="n"/>
       <c r="K46" s="35" t="n"/>
       <c r="L46" s="35" t="n"/>
-      <c r="M46" s="34">
+      <c r="M46" s="69">
         <f>SUM(M6:M45)</f>
         <v/>
       </c>
-      <c r="N46" s="34">
+      <c r="N46" s="69">
         <f>SUM(N6:N45)</f>
         <v/>
       </c>
@@ -5004,7 +5036,7 @@
       <c r="W46" s="35" t="n"/>
       <c r="X46" s="35" t="n"/>
       <c r="Y46" s="35" t="n"/>
-      <c r="Z46" s="34">
+      <c r="Z46" s="69">
         <f>G46/SUM(Y6:Y45)</f>
         <v/>
       </c>
@@ -5063,7 +5095,7 @@
           <t>Marchandise ADN</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="55" t="n">
         <v>1637.35</v>
       </c>
     </row>
@@ -5073,7 +5105,7 @@
           <t>Livraison ADN</t>
         </is>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="55">
         <f>Paramètres!B11</f>
         <v/>
       </c>
@@ -5084,7 +5116,7 @@
           <t>Achats hors ADN (pompes, Pokémon)</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="55" t="n">
         <v>178.53</v>
       </c>
     </row>
@@ -5094,7 +5126,7 @@
           <t>TOTAL ENGAGÉ</t>
         </is>
       </c>
-      <c r="B7" s="34">
+      <c r="B7" s="69">
         <f>'Stock complet'!C46</f>
         <v/>
       </c>
@@ -5112,7 +5144,7 @@
           <t>Chiffre d'affaires attendu</t>
         </is>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="57">
         <f>'Stock complet'!F46</f>
         <v/>
       </c>
@@ -5128,7 +5160,7 @@
           <t>− URSSAF + CFP</t>
         </is>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="56">
         <f>-'Stock complet'!M46</f>
         <v/>
       </c>
@@ -5139,7 +5171,7 @@
           <t>− Commission carte</t>
         </is>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="55">
         <f>-'Stock complet'!N46</f>
         <v/>
       </c>
@@ -5149,7 +5181,7 @@
         <f> Marge brute</f>
         <v/>
       </c>
-      <c r="B13" s="34">
+      <c r="B13" s="69">
         <f>'Stock complet'!G46</f>
         <v/>
       </c>
@@ -5160,7 +5192,7 @@
           <t>− Emballage</t>
         </is>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="55">
         <f>-Paramètres!B20*Paramètres!B21</f>
         <v/>
       </c>
@@ -5171,7 +5203,7 @@
           <t>− Frais fixe carte</t>
         </is>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="55">
         <f>-Paramètres!B8*Paramètres!B21</f>
         <v/>
       </c>
@@ -5181,7 +5213,7 @@
         <f> Marge avant impôt</f>
         <v/>
       </c>
-      <c r="B16" s="34">
+      <c r="B16" s="69">
         <f>B13+B14+B15</f>
         <v/>
       </c>
@@ -5192,7 +5224,7 @@
           <t>Base imposable</t>
         </is>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="55">
         <f>B10*(1-Paramètres!B16)</f>
         <v/>
       </c>
@@ -5203,7 +5235,7 @@
           <t>− Impôt estimé</t>
         </is>
       </c>
-      <c r="B18" s="6">
+      <c r="B18" s="55">
         <f>-B17*Paramètres!B17</f>
         <v/>
       </c>
@@ -5213,7 +5245,7 @@
         <f> CE QUI RESTE</f>
         <v/>
       </c>
-      <c r="B19" s="41">
+      <c r="B19" s="71">
         <f>B16+B18</f>
         <v/>
       </c>
@@ -5231,7 +5263,7 @@
           <t>Marge nette / capital engagé</t>
         </is>
       </c>
-      <c r="B22" s="42">
+      <c r="B22" s="72">
         <f>B19/B7</f>
         <v/>
       </c>
@@ -5253,7 +5285,7 @@
           <t>Taux de marge nette sur le CA</t>
         </is>
       </c>
-      <c r="B24" s="42">
+      <c r="B24" s="72">
         <f>B19/B10</f>
         <v/>
       </c>
@@ -5276,7 +5308,7 @@
           <t>Shopify + Claude, aujourd'hui</t>
         </is>
       </c>
-      <c r="B27" s="6">
+      <c r="B27" s="55">
         <f>Paramètres!B30</f>
         <v/>
       </c>
@@ -5292,7 +5324,7 @@
           <t>Shopify + Claude, à partir du 11/11/2026</t>
         </is>
       </c>
-      <c r="B28" s="6">
+      <c r="B28" s="55">
         <f>Paramètres!B31</f>
         <v/>
       </c>
@@ -5308,7 +5340,7 @@
           <t>Soit par an, à partir de novembre</t>
         </is>
       </c>
-      <c r="B29" s="34">
+      <c r="B29" s="69">
         <f>Paramètres!B31*12</f>
         <v/>
       </c>
@@ -5319,7 +5351,7 @@
           <t>CA mensuel nécessaire pour les couvrir</t>
         </is>
       </c>
-      <c r="B30" s="41">
+      <c r="B30" s="71">
         <f>Paramètres!B31/B24</f>
         <v/>
       </c>
@@ -5335,7 +5367,7 @@
           <t>Marge du stock entier</t>
         </is>
       </c>
-      <c r="B31" s="6">
+      <c r="B31" s="55">
         <f>B19</f>
         <v/>
       </c>
@@ -5351,7 +5383,7 @@
           <t>Mois de charges couverts par tout le stock</t>
         </is>
       </c>
-      <c r="B32" s="44">
+      <c r="B32" s="73">
         <f>B19/Paramètres!B31</f>
         <v/>
       </c>
@@ -5479,7 +5511,7 @@
           <t>Cotisations URSSAF (achat-revente BIC)</t>
         </is>
       </c>
-      <c r="B5" s="46" t="n">
+      <c r="B5" s="74" t="n">
         <v>0.123</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -5494,7 +5526,7 @@
           <t>CFP — formation professionnelle</t>
         </is>
       </c>
-      <c r="B6" s="46" t="n">
+      <c r="B6" s="74" t="n">
         <v>0.001</v>
       </c>
     </row>
@@ -5504,7 +5536,7 @@
           <t>Commission carte Shopify Payments</t>
         </is>
       </c>
-      <c r="B7" s="46" t="n">
+      <c r="B7" s="74" t="n">
         <v>0.015</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -5519,7 +5551,7 @@
           <t>Frais fixe par transaction carte</t>
         </is>
       </c>
-      <c r="B8" s="47" t="n">
+      <c r="B8" s="75" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -5536,7 +5568,7 @@
           <t>Total des factures de livraison ADN</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="54" t="n">
         <v>127.8</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -5566,7 +5598,7 @@
           <t>Livraison par unité de vente</t>
         </is>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="55">
         <f>B11/B12</f>
         <v/>
       </c>
@@ -5589,7 +5621,7 @@
           <t>Abattement forfaitaire</t>
         </is>
       </c>
-      <c r="B16" s="46" t="n">
+      <c r="B16" s="74" t="n">
         <v>0.71</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -5604,7 +5636,7 @@
           <t>Tranche marginale du foyer</t>
         </is>
       </c>
-      <c r="B17" s="46" t="n">
+      <c r="B17" s="74" t="n">
         <v>0.11</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -5626,7 +5658,7 @@
           <t>Emballage par colis</t>
         </is>
       </c>
-      <c r="B20" s="47" t="n">
+      <c r="B20" s="75" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5675,7 +5707,7 @@
           <t>Abonnement Shopify — aujourd'hui</t>
         </is>
       </c>
-      <c r="B27" s="47" t="n">
+      <c r="B27" s="75" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -5690,7 +5722,7 @@
           <t>Abonnement Shopify — à partir du 11/11/2026</t>
         </is>
       </c>
-      <c r="B28" s="47" t="n">
+      <c r="B28" s="75" t="n">
         <v>36</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -5705,7 +5737,7 @@
           <t>Abonnement Claude</t>
         </is>
       </c>
-      <c r="B29" s="47" t="n">
+      <c r="B29" s="75" t="n">
         <v>22</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -5720,7 +5752,7 @@
           <t>Total mensuel aujourd'hui</t>
         </is>
       </c>
-      <c r="B30" s="50">
+      <c r="B30" s="76">
         <f>B27+B29</f>
         <v/>
       </c>
@@ -5731,7 +5763,7 @@
           <t>Total mensuel à partir du 11/11/2026</t>
         </is>
       </c>
-      <c r="B31" s="50">
+      <c r="B31" s="76">
         <f>B28+B29</f>
         <v/>
       </c>
@@ -5754,7 +5786,7 @@
           <t>CFE — cotisation foncière des entreprises</t>
         </is>
       </c>
-      <c r="B34" s="47" t="n">
+      <c r="B34" s="75" t="n">
         <v>0</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -5791,7 +5823,7 @@
           <t>Shopify Payments — frais fixe</t>
         </is>
       </c>
-      <c r="B38" s="47" t="n">
+      <c r="B38" s="75" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -5816,7 +5848,7 @@
           <t>PayPal — frais fixe</t>
         </is>
       </c>
-      <c r="B40" s="47" t="n">
+      <c r="B40" s="75" t="n">
         <v>0.35</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -5861,7 +5893,7 @@
           <t>Coefficient de marge — Shopify Payments</t>
         </is>
       </c>
-      <c r="B44" s="52">
+      <c r="B44" s="77">
         <f>1-B5-B6-B37</f>
         <v/>
       </c>
@@ -5877,7 +5909,7 @@
           <t>Coefficient de marge — PayPal</t>
         </is>
       </c>
-      <c r="B45" s="52">
+      <c r="B45" s="77">
         <f>1-B5-B6-B39</f>
         <v/>
       </c>
@@ -5893,7 +5925,7 @@
           <t>Coefficient de marge — hors carte</t>
         </is>
       </c>
-      <c r="B46" s="52">
+      <c r="B46" s="77">
         <f>1-B5-B6</f>
         <v/>
       </c>
@@ -5909,7 +5941,7 @@
           <t>Écart PayPal / Shopify Payments sur une vente à 89 €</t>
         </is>
       </c>
-      <c r="B47" s="6">
+      <c r="B47" s="55">
         <f>89*(B39-B37)+(B40-B38)</f>
         <v/>
       </c>
@@ -6042,16 +6074,16 @@
           <t>Lot de 12 paires de tongs HAVAIANAS fuchsia 35/36 — neuf</t>
         </is>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="G5" s="55" t="n">
         <v>80</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="H5" s="55" t="n">
         <v>20.8</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="I5" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="J5" s="55" t="n">
         <v>100.8</v>
       </c>
     </row>
@@ -6086,16 +6118,16 @@
           <t>Veste en jean ARMANI EXCHANGE T.S — neuve</t>
         </is>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="G6" s="55" t="n">
         <v>20</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="H6" s="55" t="n">
         <v>5.2</v>
       </c>
-      <c r="I6" s="6" t="n">
+      <c r="I6" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="J6" s="55" t="n">
         <v>25.2</v>
       </c>
     </row>
@@ -6130,16 +6162,16 @@
           <t>Lot de 4 gilets de flottaison MRS.ERTHA 3-6 ans — neuf</t>
         </is>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="G7" s="55" t="n">
         <v>30</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="H7" s="55" t="n">
         <v>7.8</v>
       </c>
-      <c r="I7" s="6" t="n">
+      <c r="I7" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="J7" s="55" t="n">
         <v>37.8</v>
       </c>
     </row>
@@ -6174,16 +6206,16 @@
           <t>Robe SANDRO T.40 — neuve</t>
         </is>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="G8" s="55" t="n">
         <v>30</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="H8" s="55" t="n">
         <v>7.8</v>
       </c>
-      <c r="I8" s="6" t="n">
+      <c r="I8" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="J8" s="55" t="n">
         <v>37.8</v>
       </c>
     </row>
@@ -6218,16 +6250,16 @@
           <t>Baskets HOKA P.37 1/3 — neuves</t>
         </is>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="G9" s="55" t="n">
         <v>50</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="H9" s="55" t="n">
         <v>13</v>
       </c>
-      <c r="I9" s="6" t="n">
+      <c r="I9" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="J9" s="55" t="n">
         <v>63</v>
       </c>
     </row>
@@ -6262,16 +6294,16 @@
           <t>Baskets NIKE Air Max Moto 2K P.44.5 — neuves</t>
         </is>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="G10" s="55" t="n">
         <v>40</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="H10" s="55" t="n">
         <v>10.4</v>
       </c>
-      <c r="I10" s="6" t="n">
+      <c r="I10" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="J10" s="55" t="n">
         <v>50.4</v>
       </c>
     </row>
@@ -6306,16 +6338,16 @@
           <t>Chaussures HOGAN P.36 — traces d'essayage</t>
         </is>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="G11" s="55" t="n">
         <v>10</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="H11" s="55" t="n">
         <v>2.6</v>
       </c>
-      <c r="I11" s="6" t="n">
+      <c r="I11" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="J11" s="55" t="n">
         <v>12.6</v>
       </c>
     </row>
@@ -6350,16 +6382,16 @@
           <t>NEW BALANCE G19064IK Alkaline Green P.38½ — neuves avec boîte</t>
         </is>
       </c>
-      <c r="G12" s="6" t="n">
+      <c r="G12" s="55" t="n">
         <v>60</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="H12" s="55" t="n">
         <v>15.6</v>
       </c>
-      <c r="I12" s="6" t="n">
+      <c r="I12" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="J12" s="55" t="n">
         <v>75.59999999999999</v>
       </c>
     </row>
@@ -6394,16 +6426,16 @@
           <t>Lot de 2 paires ADIDAS Predator Edge P.48 2/3 — neuves</t>
         </is>
       </c>
-      <c r="G13" s="6" t="n">
+      <c r="G13" s="55" t="n">
         <v>30</v>
       </c>
-      <c r="H13" s="6" t="n">
+      <c r="H13" s="55" t="n">
         <v>7.8</v>
       </c>
-      <c r="I13" s="6" t="n">
+      <c r="I13" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="6" t="n">
+      <c r="J13" s="55" t="n">
         <v>37.8</v>
       </c>
     </row>
@@ -6438,16 +6470,16 @@
           <t>Short BA&amp;SH Fegor T.34 — neuf</t>
         </is>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="G14" s="55" t="n">
         <v>40</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="H14" s="55" t="n">
         <v>10.4</v>
       </c>
-      <c r="I14" s="6" t="n">
+      <c r="I14" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J14" s="6" t="n">
+      <c r="J14" s="55" t="n">
         <v>50.4</v>
       </c>
     </row>
@@ -6482,16 +6514,16 @@
           <t>Jupe midi SONIA RYKIEL T.34 — neuve</t>
         </is>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="G15" s="55" t="n">
         <v>30</v>
       </c>
-      <c r="H15" s="6" t="n">
+      <c r="H15" s="55" t="n">
         <v>7.8</v>
       </c>
-      <c r="I15" s="6" t="n">
+      <c r="I15" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="J15" s="55" t="n">
         <v>37.8</v>
       </c>
     </row>
@@ -6526,16 +6558,16 @@
           <t>Sac demi-lune nylon noir KARL LAGERFELD JEANS — neuf avec étiquette</t>
         </is>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="G16" s="55" t="n">
         <v>40</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="H16" s="55" t="n">
         <v>10.4</v>
       </c>
-      <c r="I16" s="6" t="n">
+      <c r="I16" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="6" t="n">
+      <c r="J16" s="55" t="n">
         <v>50.4</v>
       </c>
     </row>
@@ -6570,16 +6602,16 @@
           <t>ADIDAS x STELLA McCARTNEY ASMC Ultraboost 21 P.36 — modèle d'exposition</t>
         </is>
       </c>
-      <c r="G17" s="6" t="n">
+      <c r="G17" s="55" t="n">
         <v>30</v>
       </c>
-      <c r="H17" s="6" t="n">
+      <c r="H17" s="55" t="n">
         <v>7.8</v>
       </c>
-      <c r="I17" s="6" t="n">
+      <c r="I17" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J17" s="6" t="n">
+      <c r="J17" s="55" t="n">
         <v>37.8</v>
       </c>
     </row>
@@ -6614,16 +6646,16 @@
           <t>Ballerines MASSIMO DUTTI P.41 — traces d'essayage</t>
         </is>
       </c>
-      <c r="G18" s="6" t="n">
+      <c r="G18" s="55" t="n">
         <v>20</v>
       </c>
-      <c r="H18" s="6" t="n">
+      <c r="H18" s="55" t="n">
         <v>5.2</v>
       </c>
-      <c r="I18" s="6" t="n">
+      <c r="I18" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J18" s="6" t="n">
+      <c r="J18" s="55" t="n">
         <v>25.2</v>
       </c>
     </row>
@@ -6658,16 +6690,16 @@
           <t>NEW BALANCE sneakers P.38 — neuves</t>
         </is>
       </c>
-      <c r="G19" s="6" t="n">
+      <c r="G19" s="55" t="n">
         <v>30</v>
       </c>
-      <c r="H19" s="6" t="n">
+      <c r="H19" s="55" t="n">
         <v>7.8</v>
       </c>
-      <c r="I19" s="6" t="n">
+      <c r="I19" s="55" t="n">
         <v>0.54</v>
       </c>
-      <c r="J19" s="6" t="n">
+      <c r="J19" s="55" t="n">
         <v>38.34</v>
       </c>
     </row>
@@ -6702,16 +6734,16 @@
           <t>LACOSTE sneakers P.42 — neuves</t>
         </is>
       </c>
-      <c r="G20" s="6" t="n">
+      <c r="G20" s="55" t="n">
         <v>45</v>
       </c>
-      <c r="H20" s="6" t="n">
+      <c r="H20" s="55" t="n">
         <v>11.7</v>
       </c>
-      <c r="I20" s="6" t="n">
+      <c r="I20" s="55" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="J20" s="6" t="n">
+      <c r="J20" s="55" t="n">
         <v>57.51</v>
       </c>
     </row>
@@ -6746,16 +6778,16 @@
           <t>EMPORIO ARMANI baskets P.36 — neuves</t>
         </is>
       </c>
-      <c r="G21" s="6" t="n">
+      <c r="G21" s="55" t="n">
         <v>40</v>
       </c>
-      <c r="H21" s="6" t="n">
+      <c r="H21" s="55" t="n">
         <v>10.4</v>
       </c>
-      <c r="I21" s="6" t="n">
+      <c r="I21" s="55" t="n">
         <v>0.72</v>
       </c>
-      <c r="J21" s="6" t="n">
+      <c r="J21" s="55" t="n">
         <v>51.12</v>
       </c>
     </row>
@@ -6790,16 +6822,16 @@
           <t>GEOX baskets P.35 — neuves</t>
         </is>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="G22" s="55" t="n">
         <v>17</v>
       </c>
-      <c r="H22" s="6" t="n">
+      <c r="H22" s="55" t="n">
         <v>4.42</v>
       </c>
-      <c r="I22" s="6" t="n">
+      <c r="I22" s="55" t="n">
         <v>0.31</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="J22" s="55" t="n">
         <v>21.73</v>
       </c>
     </row>
@@ -6834,16 +6866,16 @@
           <t>NEW BALANCE baskets montantes P.44 — neuves</t>
         </is>
       </c>
-      <c r="G23" s="6" t="n">
+      <c r="G23" s="55" t="n">
         <v>40</v>
       </c>
-      <c r="H23" s="6" t="n">
+      <c r="H23" s="55" t="n">
         <v>10.4</v>
       </c>
-      <c r="I23" s="6" t="n">
+      <c r="I23" s="55" t="n">
         <v>0.72</v>
       </c>
-      <c r="J23" s="6" t="n">
+      <c r="J23" s="55" t="n">
         <v>51.12</v>
       </c>
     </row>
@@ -6878,16 +6910,16 @@
           <t>TOMMY JEANS baskets basses P.40 — neuves</t>
         </is>
       </c>
-      <c r="G24" s="6" t="n">
+      <c r="G24" s="55" t="n">
         <v>41</v>
       </c>
-      <c r="H24" s="6" t="n">
+      <c r="H24" s="55" t="n">
         <v>10.66</v>
       </c>
-      <c r="I24" s="6" t="n">
+      <c r="I24" s="55" t="n">
         <v>0.74</v>
       </c>
-      <c r="J24" s="6" t="n">
+      <c r="J24" s="55" t="n">
         <v>52.4</v>
       </c>
     </row>
@@ -6922,16 +6954,16 @@
           <t>PHILIPP PLEIN SPORT baskets montantes P.40 — neuves</t>
         </is>
       </c>
-      <c r="G25" s="6" t="n">
+      <c r="G25" s="55" t="n">
         <v>45</v>
       </c>
-      <c r="H25" s="6" t="n">
+      <c r="H25" s="55" t="n">
         <v>11.7</v>
       </c>
-      <c r="I25" s="6" t="n">
+      <c r="I25" s="55" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="J25" s="6" t="n">
+      <c r="J25" s="55" t="n">
         <v>57.51</v>
       </c>
     </row>
@@ -6966,16 +6998,16 @@
           <t>PIER ANTONIO GASPARI robe droite bleu marine T.42 — neuve</t>
         </is>
       </c>
-      <c r="G26" s="6" t="n">
+      <c r="G26" s="55" t="n">
         <v>20</v>
       </c>
-      <c r="H26" s="6" t="n">
+      <c r="H26" s="55" t="n">
         <v>5.2</v>
       </c>
-      <c r="I26" s="6" t="n">
+      <c r="I26" s="55" t="n">
         <v>0.36</v>
       </c>
-      <c r="J26" s="6" t="n">
+      <c r="J26" s="55" t="n">
         <v>25.56</v>
       </c>
     </row>
@@ -7010,16 +7042,16 @@
           <t>ELISABETTA FRANCHI robe asymétrique viscose T.46 IT — neuve</t>
         </is>
       </c>
-      <c r="G27" s="6" t="n">
+      <c r="G27" s="55" t="n">
         <v>16</v>
       </c>
-      <c r="H27" s="6" t="n">
+      <c r="H27" s="55" t="n">
         <v>4.16</v>
       </c>
-      <c r="I27" s="6" t="n">
+      <c r="I27" s="55" t="n">
         <v>0.29</v>
       </c>
-      <c r="J27" s="6" t="n">
+      <c r="J27" s="55" t="n">
         <v>20.45</v>
       </c>
     </row>
@@ -7054,16 +7086,16 @@
           <t>CHIARA FERRAGNI robe bustier courte T.M — neuve</t>
         </is>
       </c>
-      <c r="G28" s="6" t="n">
+      <c r="G28" s="55" t="n">
         <v>25</v>
       </c>
-      <c r="H28" s="6" t="n">
+      <c r="H28" s="55" t="n">
         <v>6.5</v>
       </c>
-      <c r="I28" s="6" t="n">
+      <c r="I28" s="55" t="n">
         <v>0.45</v>
       </c>
-      <c r="J28" s="6" t="n">
+      <c r="J28" s="55" t="n">
         <v>31.95</v>
       </c>
     </row>
@@ -7098,16 +7130,16 @@
           <t>SALOMON X Ultra 5 Mid GTX P.44 — neuves</t>
         </is>
       </c>
-      <c r="G29" s="6" t="n">
+      <c r="G29" s="55" t="n">
         <v>60</v>
       </c>
-      <c r="H29" s="6" t="n">
+      <c r="H29" s="55" t="n">
         <v>15.6</v>
       </c>
-      <c r="I29" s="6" t="n">
+      <c r="I29" s="55" t="n">
         <v>1.08</v>
       </c>
-      <c r="J29" s="6" t="n">
+      <c r="J29" s="55" t="n">
         <v>76.68000000000001</v>
       </c>
     </row>
@@ -7142,16 +7174,16 @@
           <t>Lot de 4 toupies BEYBLADE HASBRO</t>
         </is>
       </c>
-      <c r="G30" s="6" t="n">
+      <c r="G30" s="55" t="n">
         <v>15</v>
       </c>
-      <c r="H30" s="6" t="n">
+      <c r="H30" s="55" t="n">
         <v>3.9</v>
       </c>
-      <c r="I30" s="6" t="n">
+      <c r="I30" s="55" t="n">
         <v>0.27</v>
       </c>
-      <c r="J30" s="6" t="n">
+      <c r="J30" s="55" t="n">
         <v>19.17</v>
       </c>
     </row>
@@ -7186,16 +7218,16 @@
           <t>Lot de 4 toupies BEYBLADE HASBRO</t>
         </is>
       </c>
-      <c r="G31" s="6" t="n">
+      <c r="G31" s="55" t="n">
         <v>30</v>
       </c>
-      <c r="H31" s="6" t="n">
+      <c r="H31" s="55" t="n">
         <v>7.8</v>
       </c>
-      <c r="I31" s="6" t="n">
+      <c r="I31" s="55" t="n">
         <v>0.54</v>
       </c>
-      <c r="J31" s="6" t="n">
+      <c r="J31" s="55" t="n">
         <v>38.34</v>
       </c>
     </row>
@@ -7230,16 +7262,16 @@
           <t>T-shirt BALENCIAGA T.2 — neuf</t>
         </is>
       </c>
-      <c r="G32" s="6" t="n">
+      <c r="G32" s="55" t="n">
         <v>90</v>
       </c>
-      <c r="H32" s="6" t="n">
+      <c r="H32" s="55" t="n">
         <v>23.4</v>
       </c>
-      <c r="I32" s="6" t="n">
+      <c r="I32" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J32" s="6" t="n">
+      <c r="J32" s="55" t="n">
         <v>113.4</v>
       </c>
     </row>
@@ -7274,16 +7306,16 @@
           <t>Blazer noir KARL LAGERFELD T.36 FR — neuf avec étiquette</t>
         </is>
       </c>
-      <c r="G33" s="6" t="n">
+      <c r="G33" s="55" t="n">
         <v>40</v>
       </c>
-      <c r="H33" s="6" t="n">
+      <c r="H33" s="55" t="n">
         <v>10.4</v>
       </c>
-      <c r="I33" s="6" t="n">
+      <c r="I33" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J33" s="6" t="n">
+      <c r="J33" s="55" t="n">
         <v>50.4</v>
       </c>
     </row>
@@ -7318,16 +7350,16 @@
           <t>ADIDAS Yeezy 700 V3 Mono Safflower T.38 — occasion</t>
         </is>
       </c>
-      <c r="G34" s="6" t="n">
+      <c r="G34" s="55" t="n">
         <v>50</v>
       </c>
-      <c r="H34" s="6" t="n">
+      <c r="H34" s="55" t="n">
         <v>13</v>
       </c>
-      <c r="I34" s="6" t="n">
+      <c r="I34" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J34" s="6" t="n">
+      <c r="J34" s="55" t="n">
         <v>63</v>
       </c>
     </row>
@@ -7362,16 +7394,16 @@
           <t>Lot de 6 vêtements femme MORGAN T.40 et L — neuf</t>
         </is>
       </c>
-      <c r="G35" s="6" t="n">
+      <c r="G35" s="55" t="n">
         <v>30</v>
       </c>
-      <c r="H35" s="6" t="n">
+      <c r="H35" s="55" t="n">
         <v>7.8</v>
       </c>
-      <c r="I35" s="6" t="n">
+      <c r="I35" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J35" s="6" t="n">
+      <c r="J35" s="55" t="n">
         <v>37.8</v>
       </c>
     </row>
@@ -7406,16 +7438,16 @@
           <t>Demi-bottes FORMA Legacy Waterproof T.45 noir — neuves</t>
         </is>
       </c>
-      <c r="G36" s="6" t="n">
+      <c r="G36" s="55" t="n">
         <v>50</v>
       </c>
-      <c r="H36" s="6" t="n">
+      <c r="H36" s="55" t="n">
         <v>13</v>
       </c>
-      <c r="I36" s="6" t="n">
+      <c r="I36" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J36" s="6" t="n">
+      <c r="J36" s="55" t="n">
         <v>63</v>
       </c>
     </row>
@@ -7450,16 +7482,16 @@
           <t>Combinaison de pluie BMW Overall ProRain unisexe XL — neuve</t>
         </is>
       </c>
-      <c r="G37" s="6" t="n">
+      <c r="G37" s="55" t="n">
         <v>60</v>
       </c>
-      <c r="H37" s="6" t="n">
+      <c r="H37" s="55" t="n">
         <v>8.57</v>
       </c>
-      <c r="I37" s="6" t="n">
+      <c r="I37" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J37" s="6" t="n">
+      <c r="J37" s="55" t="n">
         <v>68.56999999999999</v>
       </c>
     </row>
@@ -7494,16 +7526,16 @@
           <t>Lot de 20 paires de sandales et tongs RELIFE / TOMMY JEANS — neuf</t>
         </is>
       </c>
-      <c r="G38" s="6" t="n">
+      <c r="G38" s="55" t="n">
         <v>45</v>
       </c>
-      <c r="H38" s="6" t="n">
+      <c r="H38" s="55" t="n">
         <v>11.7</v>
       </c>
-      <c r="I38" s="6" t="n">
+      <c r="I38" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J38" s="6" t="n">
+      <c r="J38" s="55" t="n">
         <v>56.7</v>
       </c>
     </row>
@@ -7518,19 +7550,19 @@
           <t>TOTAL MARCHANDISE</t>
         </is>
       </c>
-      <c r="G39" s="34">
+      <c r="G39" s="69">
         <f>SUM(G5:G38)</f>
         <v/>
       </c>
-      <c r="H39" s="34">
+      <c r="H39" s="69">
         <f>SUM(H5:H38)</f>
         <v/>
       </c>
-      <c r="I39" s="34">
+      <c r="I39" s="69">
         <f>SUM(I5:I38)</f>
         <v/>
       </c>
-      <c r="J39" s="34">
+      <c r="J39" s="69">
         <f>SUM(J5:J38)</f>
         <v/>
       </c>
@@ -7600,7 +7632,7 @@
           <t>Colissimo Point Relais — assurance et signature</t>
         </is>
       </c>
-      <c r="F43" s="6" t="n">
+      <c r="F43" s="55" t="n">
         <v>19.9</v>
       </c>
     </row>
@@ -7630,7 +7662,7 @@
           <t>Colissimo Point Relais — assurance et signature</t>
         </is>
       </c>
-      <c r="F44" s="6" t="n">
+      <c r="F44" s="55" t="n">
         <v>18.22</v>
       </c>
     </row>
@@ -7660,7 +7692,7 @@
           <t>Colissimo Point Relais — assurance et signature</t>
         </is>
       </c>
-      <c r="F45" s="6" t="n">
+      <c r="F45" s="55" t="n">
         <v>29.94</v>
       </c>
     </row>
@@ -7690,7 +7722,7 @@
           <t>Colissimo Point Relais</t>
         </is>
       </c>
-      <c r="F46" s="6" t="n">
+      <c r="F46" s="55" t="n">
         <v>15.72</v>
       </c>
     </row>
@@ -7720,7 +7752,7 @@
           <t>Colissimo Point Relais — assurance et signature</t>
         </is>
       </c>
-      <c r="F47" s="6" t="n">
+      <c r="F47" s="55" t="n">
         <v>44.02</v>
       </c>
     </row>
@@ -7734,7 +7766,7 @@
           <t>TOTAL LIVRAISON</t>
         </is>
       </c>
-      <c r="F48" s="34">
+      <c r="F48" s="69">
         <f>SUM(F43:F47)</f>
         <v/>
       </c>

--- a/exports/maison-nsaia-stock.xlsx
+++ b/exports/maison-nsaia-stock.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Stock complet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Synthèse" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Paramètres" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Factures" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stock complet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Synthèse" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paramètres" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Factures" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stock complet'!$A$5:$AA$45</definedName>
@@ -22,11 +22,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00 &quot;€&quot;"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
-    <numFmt numFmtId="167" formatCode="#,##0 &quot;art.&quot;"/>
-    <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00 &quot;€&quot;"/>
+    <numFmt numFmtId="165" formatCode="#,##0 &quot;art.&quot;"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="168" formatCode="0.000"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -142,7 +142,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -150,57 +150,81 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="9" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -778,25 +802,25 @@
           <t>Lot de 20 paires de sandales et tongs RELIFE / TOMMY JEANS — neuf</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="54" t="n">
         <v>56.7</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="55">
         <f>$B6+$Y6*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="56">
         <f>$C6/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="55">
         <f>CEILING($D6*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F6" s="8" t="n">
+      <c r="F6" s="57" t="n">
         <v>199</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="57">
         <f>IF($F6="","",$F6-$C6-$M6-$N6)</f>
         <v/>
       </c>
@@ -807,29 +831,29 @@
       <c r="I6" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="55">
         <f>$C6/$I6</f>
         <v/>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="55">
         <f>IF($F6="","",$F6/$I6)</f>
         <v/>
       </c>
-      <c r="L6" s="6">
+      <c r="L6" s="55">
         <f>IF($G6="","",$G6/$I6)</f>
         <v/>
       </c>
-      <c r="M6" s="7">
+      <c r="M6" s="56">
         <f>IF($F6="","",$F6*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N6" s="6" t="n">
+      <c r="N6" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O6" s="11" t="n">
+      <c r="O6" s="58" t="n">
         <v>45</v>
       </c>
-      <c r="P6" s="11" t="n">
+      <c r="P6" s="58" t="n">
         <v>11.7</v>
       </c>
       <c r="Q6" s="12" t="inlineStr">
@@ -867,7 +891,7 @@
       <c r="Y6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z6" s="8">
+      <c r="Z6" s="57">
         <f>IF($G6="","",$G6/$Y6)</f>
         <v/>
       </c>
@@ -882,25 +906,25 @@
           <t>Lot de 2 paires ADIDAS Predator Edge P.48 2/3 — neuves</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="54" t="n">
         <v>37.8</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="55">
         <f>$B7+$Y7*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="56">
         <f>$C7/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="55">
         <f>CEILING($D7*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F7" s="8" t="n">
+      <c r="F7" s="57" t="n">
         <v>178</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="57">
         <f>IF($F7="","",$F7-$C7-$M7-$N7)</f>
         <v/>
       </c>
@@ -911,29 +935,29 @@
       <c r="I7" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="J7" s="6">
+      <c r="J7" s="55">
         <f>$C7/$I7</f>
         <v/>
       </c>
-      <c r="K7" s="6">
+      <c r="K7" s="55">
         <f>IF($F7="","",$F7/$I7)</f>
         <v/>
       </c>
-      <c r="L7" s="6">
+      <c r="L7" s="55">
         <f>IF($G7="","",$G7/$I7)</f>
         <v/>
       </c>
-      <c r="M7" s="7">
+      <c r="M7" s="56">
         <f>IF($F7="","",$F7*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N7" s="6" t="n">
+      <c r="N7" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O7" s="11" t="n">
+      <c r="O7" s="58" t="n">
         <v>30</v>
       </c>
-      <c r="P7" s="11" t="n">
+      <c r="P7" s="58" t="n">
         <v>7.8</v>
       </c>
       <c r="Q7" s="12" t="inlineStr">
@@ -971,7 +995,7 @@
       <c r="Y7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="Z7" s="8">
+      <c r="Z7" s="57">
         <f>IF($G7="","",$G7/$Y7)</f>
         <v/>
       </c>
@@ -986,25 +1010,25 @@
           <t>Demi-bottes FORMA Legacy Waterproof T.45 noir — neuves</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="54" t="n">
         <v>63</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="55">
         <f>$B8+$Y8*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="56">
         <f>$C8/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="55">
         <f>CEILING($D8*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F8" s="8" t="n">
+      <c r="F8" s="57" t="n">
         <v>159</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="57">
         <f>IF($F8="","",$F8-$C8-$M8-$N8)</f>
         <v/>
       </c>
@@ -1015,30 +1039,30 @@
       <c r="I8" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J8" s="6">
+      <c r="J8" s="55">
         <f>$C8/$I8</f>
         <v/>
       </c>
-      <c r="K8" s="6">
+      <c r="K8" s="55">
         <f>IF($F8="","",$F8/$I8)</f>
         <v/>
       </c>
-      <c r="L8" s="6">
+      <c r="L8" s="55">
         <f>IF($G8="","",$G8/$I8)</f>
         <v/>
       </c>
-      <c r="M8" s="7">
+      <c r="M8" s="56">
         <f>IF($F8="","",$F8*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N8" s="6">
+      <c r="N8" s="55">
         <f>IF($F8="","",$F8*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="O8" s="11" t="n">
+      <c r="O8" s="58" t="n">
         <v>50</v>
       </c>
-      <c r="P8" s="11" t="n">
+      <c r="P8" s="58" t="n">
         <v>13</v>
       </c>
       <c r="Q8" s="12" t="inlineStr">
@@ -1076,7 +1100,7 @@
       <c r="Y8" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z8" s="8">
+      <c r="Z8" s="57">
         <f>IF($G8="","",$G8/$Y8)</f>
         <v/>
       </c>
@@ -1091,25 +1115,25 @@
           <t>Lot de 4 gilets de flottaison MRS.ERTHA 3-6 ans — neuf</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="54" t="n">
         <v>37.8</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="55">
         <f>$B9+$Y9*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="56">
         <f>$C9/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="55">
         <f>CEILING($D9*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F9" s="8" t="n">
+      <c r="F9" s="57" t="n">
         <v>136</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="57">
         <f>IF($F9="","",$F9-$C9-$M9-$N9)</f>
         <v/>
       </c>
@@ -1120,29 +1144,29 @@
       <c r="I9" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="J9" s="6">
+      <c r="J9" s="55">
         <f>$C9/$I9</f>
         <v/>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="55">
         <f>IF($F9="","",$F9/$I9)</f>
         <v/>
       </c>
-      <c r="L9" s="6">
+      <c r="L9" s="55">
         <f>IF($G9="","",$G9/$I9)</f>
         <v/>
       </c>
-      <c r="M9" s="7">
+      <c r="M9" s="56">
         <f>IF($F9="","",$F9*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N9" s="6" t="n">
+      <c r="N9" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O9" s="11" t="n">
+      <c r="O9" s="58" t="n">
         <v>30</v>
       </c>
-      <c r="P9" s="11" t="n">
+      <c r="P9" s="58" t="n">
         <v>7.8</v>
       </c>
       <c r="Q9" s="12" t="inlineStr">
@@ -1180,7 +1204,7 @@
       <c r="Y9" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="Z9" s="8">
+      <c r="Z9" s="57">
         <f>IF($G9="","",$G9/$Y9)</f>
         <v/>
       </c>
@@ -1195,25 +1219,25 @@
           <t>Lot de 12 paires de tongs HAVAIANAS fuchsia 35/36 — neuf</t>
         </is>
       </c>
-      <c r="B10" s="14" t="n">
+      <c r="B10" s="59" t="n">
         <v>100.8</v>
       </c>
-      <c r="C10" s="15">
+      <c r="C10" s="60">
         <f>$B10+$Y10*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D10" s="16">
+      <c r="D10" s="61">
         <f>$C10/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E10" s="15">
+      <c r="E10" s="60">
         <f>CEILING($D10*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F10" s="17" t="n">
+      <c r="F10" s="62" t="n">
         <v>208</v>
       </c>
-      <c r="G10" s="17">
+      <c r="G10" s="62">
         <f>IF($F10="","",$F10-$C10-$M10-$N10)</f>
         <v/>
       </c>
@@ -1224,29 +1248,29 @@
       <c r="I10" s="19" t="n">
         <v>12</v>
       </c>
-      <c r="J10" s="15">
+      <c r="J10" s="60">
         <f>$C10/$I10</f>
         <v/>
       </c>
-      <c r="K10" s="15">
+      <c r="K10" s="60">
         <f>IF($F10="","",$F10/$I10)</f>
         <v/>
       </c>
-      <c r="L10" s="15">
+      <c r="L10" s="60">
         <f>IF($G10="","",$G10/$I10)</f>
         <v/>
       </c>
-      <c r="M10" s="16">
+      <c r="M10" s="61">
         <f>IF($F10="","",$F10*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N10" s="15" t="n">
+      <c r="N10" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="O10" s="20" t="n">
+      <c r="O10" s="63" t="n">
         <v>80</v>
       </c>
-      <c r="P10" s="20" t="n">
+      <c r="P10" s="63" t="n">
         <v>20.8</v>
       </c>
       <c r="Q10" s="21" t="inlineStr">
@@ -1288,7 +1312,7 @@
       <c r="Y10" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" s="17">
+      <c r="Z10" s="62">
         <f>IF($G10="","",$G10/$Y10)</f>
         <v/>
       </c>
@@ -1303,25 +1327,25 @@
           <t>ELISABETTA FRANCHI robe asymétrique viscose T.46 IT — neuve</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="54" t="n">
         <v>20.45</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="55">
         <f>$B11+$Y11*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="56">
         <f>$C11/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="55">
         <f>CEILING($D11*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F11" s="8" t="n">
+      <c r="F11" s="57" t="n">
         <v>99</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="57">
         <f>IF($F11="","",$F11-$C11-$M11-$N11)</f>
         <v/>
       </c>
@@ -1332,30 +1356,30 @@
       <c r="I11" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J11" s="6">
+      <c r="J11" s="55">
         <f>$C11/$I11</f>
         <v/>
       </c>
-      <c r="K11" s="6">
+      <c r="K11" s="55">
         <f>IF($F11="","",$F11/$I11)</f>
         <v/>
       </c>
-      <c r="L11" s="6">
+      <c r="L11" s="55">
         <f>IF($G11="","",$G11/$I11)</f>
         <v/>
       </c>
-      <c r="M11" s="7">
+      <c r="M11" s="56">
         <f>IF($F11="","",$F11*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N11" s="6">
+      <c r="N11" s="55">
         <f>IF($F11="","",$F11*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="O11" s="11" t="n">
+      <c r="O11" s="58" t="n">
         <v>16</v>
       </c>
-      <c r="P11" s="11" t="n">
+      <c r="P11" s="58" t="n">
         <v>4.16</v>
       </c>
       <c r="Q11" s="12" t="inlineStr">
@@ -1393,7 +1417,7 @@
       <c r="Y11" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z11" s="8">
+      <c r="Z11" s="57">
         <f>IF($G11="","",$G11/$Y11)</f>
         <v/>
       </c>
@@ -1408,25 +1432,25 @@
           <t>Combinaison de pluie BMW Overall ProRain unisexe XL — neuve</t>
         </is>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="54" t="n">
         <v>68.56999999999999</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="55">
         <f>$B12+$Y12*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="56">
         <f>$C12/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="55">
         <f>CEILING($D12*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F12" s="8" t="n">
+      <c r="F12" s="57" t="n">
         <v>139</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G12" s="57">
         <f>IF($F12="","",$F12-$C12-$M12-$N12)</f>
         <v/>
       </c>
@@ -1437,29 +1461,29 @@
       <c r="I12" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J12" s="6">
+      <c r="J12" s="55">
         <f>$C12/$I12</f>
         <v/>
       </c>
-      <c r="K12" s="6">
+      <c r="K12" s="55">
         <f>IF($F12="","",$F12/$I12)</f>
         <v/>
       </c>
-      <c r="L12" s="6">
+      <c r="L12" s="55">
         <f>IF($G12="","",$G12/$I12)</f>
         <v/>
       </c>
-      <c r="M12" s="7">
+      <c r="M12" s="56">
         <f>IF($F12="","",$F12*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N12" s="6" t="n">
+      <c r="N12" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O12" s="11" t="n">
+      <c r="O12" s="58" t="n">
         <v>60</v>
       </c>
-      <c r="P12" s="11" t="n">
+      <c r="P12" s="58" t="n">
         <v>8.57</v>
       </c>
       <c r="Q12" s="12" t="inlineStr">
@@ -1497,7 +1521,7 @@
       <c r="Y12" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z12" s="8">
+      <c r="Z12" s="57">
         <f>IF($G12="","",$G12/$Y12)</f>
         <v/>
       </c>
@@ -1512,25 +1536,25 @@
           <t>Chaussures HOGAN P.36 — traces d'essayage</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="54" t="n">
         <v>12.6</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="55">
         <f>$B13+$Y13*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="56">
         <f>$C13/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="55">
         <f>CEILING($D13*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F13" s="8" t="n">
+      <c r="F13" s="57" t="n">
         <v>79</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G13" s="57">
         <f>IF($F13="","",$F13-$C13-$M13-$N13)</f>
         <v/>
       </c>
@@ -1541,30 +1565,30 @@
       <c r="I13" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J13" s="6">
+      <c r="J13" s="55">
         <f>$C13/$I13</f>
         <v/>
       </c>
-      <c r="K13" s="6">
+      <c r="K13" s="55">
         <f>IF($F13="","",$F13/$I13)</f>
         <v/>
       </c>
-      <c r="L13" s="6">
+      <c r="L13" s="55">
         <f>IF($G13="","",$G13/$I13)</f>
         <v/>
       </c>
-      <c r="M13" s="7">
+      <c r="M13" s="56">
         <f>IF($F13="","",$F13*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N13" s="6">
+      <c r="N13" s="55">
         <f>IF($F13="","",$F13*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="O13" s="11" t="n">
+      <c r="O13" s="58" t="n">
         <v>10</v>
       </c>
-      <c r="P13" s="11" t="n">
+      <c r="P13" s="58" t="n">
         <v>2.6</v>
       </c>
       <c r="Q13" s="12" t="inlineStr">
@@ -1602,7 +1626,7 @@
       <c r="Y13" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z13" s="8">
+      <c r="Z13" s="57">
         <f>IF($G13="","",$G13/$Y13)</f>
         <v/>
       </c>
@@ -1617,25 +1641,25 @@
           <t>Jupe midi SONIA RYKIEL T.34 — neuve</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B14" s="54" t="n">
         <v>37.8</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="55">
         <f>$B14+$Y14*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="56">
         <f>$C14/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="55">
         <f>CEILING($D14*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F14" s="8" t="n">
+      <c r="F14" s="57" t="n">
         <v>99</v>
       </c>
-      <c r="G14" s="8">
+      <c r="G14" s="57">
         <f>IF($F14="","",$F14-$C14-$M14-$N14)</f>
         <v/>
       </c>
@@ -1646,30 +1670,30 @@
       <c r="I14" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J14" s="6">
+      <c r="J14" s="55">
         <f>$C14/$I14</f>
         <v/>
       </c>
-      <c r="K14" s="6">
+      <c r="K14" s="55">
         <f>IF($F14="","",$F14/$I14)</f>
         <v/>
       </c>
-      <c r="L14" s="6">
+      <c r="L14" s="55">
         <f>IF($G14="","",$G14/$I14)</f>
         <v/>
       </c>
-      <c r="M14" s="7">
+      <c r="M14" s="56">
         <f>IF($F14="","",$F14*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N14" s="6">
+      <c r="N14" s="55">
         <f>IF($F14="","",$F14*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="O14" s="11" t="n">
+      <c r="O14" s="58" t="n">
         <v>30</v>
       </c>
-      <c r="P14" s="11" t="n">
+      <c r="P14" s="58" t="n">
         <v>7.8</v>
       </c>
       <c r="Q14" s="12" t="inlineStr">
@@ -1707,7 +1731,7 @@
       <c r="Y14" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z14" s="8">
+      <c r="Z14" s="57">
         <f>IF($G14="","",$G14/$Y14)</f>
         <v/>
       </c>
@@ -1722,25 +1746,25 @@
           <t>Robe SANDRO T.40 — neuve</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="54" t="n">
         <v>37.8</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="55">
         <f>$B15+$Y15*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="56">
         <f>$C15/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="55">
         <f>CEILING($D15*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F15" s="8" t="n">
+      <c r="F15" s="57" t="n">
         <v>89</v>
       </c>
-      <c r="G15" s="8">
+      <c r="G15" s="57">
         <f>IF($F15="","",$F15-$C15-$M15-$N15)</f>
         <v/>
       </c>
@@ -1751,30 +1775,30 @@
       <c r="I15" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J15" s="6">
+      <c r="J15" s="55">
         <f>$C15/$I15</f>
         <v/>
       </c>
-      <c r="K15" s="6">
+      <c r="K15" s="55">
         <f>IF($F15="","",$F15/$I15)</f>
         <v/>
       </c>
-      <c r="L15" s="6">
+      <c r="L15" s="55">
         <f>IF($G15="","",$G15/$I15)</f>
         <v/>
       </c>
-      <c r="M15" s="7">
+      <c r="M15" s="56">
         <f>IF($F15="","",$F15*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N15" s="6">
+      <c r="N15" s="55">
         <f>IF($F15="","",$F15*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="O15" s="11" t="n">
+      <c r="O15" s="58" t="n">
         <v>30</v>
       </c>
-      <c r="P15" s="11" t="n">
+      <c r="P15" s="58" t="n">
         <v>7.8</v>
       </c>
       <c r="Q15" s="12" t="inlineStr">
@@ -1812,7 +1836,7 @@
       <c r="Y15" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z15" s="8">
+      <c r="Z15" s="57">
         <f>IF($G15="","",$G15/$Y15)</f>
         <v/>
       </c>
@@ -1827,25 +1851,25 @@
           <t>Lot de 6 vêtements femme MORGAN T.40 et L — neuf</t>
         </is>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B16" s="54" t="n">
         <v>37.8</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="55">
         <f>$B16+$Y16*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="56">
         <f>$C16/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E16" s="6">
+      <c r="E16" s="55">
         <f>CEILING($D16*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F16" s="8" t="n">
+      <c r="F16" s="57" t="n">
         <v>98</v>
       </c>
-      <c r="G16" s="8">
+      <c r="G16" s="57">
         <f>IF($F16="","",$F16-$C16-$M16-$N16)</f>
         <v/>
       </c>
@@ -1856,29 +1880,29 @@
       <c r="I16" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="J16" s="6">
+      <c r="J16" s="55">
         <f>$C16/$I16</f>
         <v/>
       </c>
-      <c r="K16" s="6">
+      <c r="K16" s="55">
         <f>IF($F16="","",$F16/$I16)</f>
         <v/>
       </c>
-      <c r="L16" s="6">
+      <c r="L16" s="55">
         <f>IF($G16="","",$G16/$I16)</f>
         <v/>
       </c>
-      <c r="M16" s="7">
+      <c r="M16" s="56">
         <f>IF($F16="","",$F16*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N16" s="6" t="n">
+      <c r="N16" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O16" s="11" t="n">
+      <c r="O16" s="58" t="n">
         <v>30</v>
       </c>
-      <c r="P16" s="11" t="n">
+      <c r="P16" s="58" t="n">
         <v>7.8</v>
       </c>
       <c r="Q16" s="12" t="inlineStr">
@@ -1916,7 +1940,7 @@
       <c r="Y16" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="Z16" s="8">
+      <c r="Z16" s="57">
         <f>IF($G16="","",$G16/$Y16)</f>
         <v/>
       </c>
@@ -1931,25 +1955,25 @@
           <t>ADIDAS Yeezy 700 V3 Mono Safflower T.38 — occasion</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n">
+      <c r="B17" s="54" t="n">
         <v>63</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="55">
         <f>$B17+$Y17*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="56">
         <f>$C17/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E17" s="6">
+      <c r="E17" s="55">
         <f>CEILING($D17*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F17" s="8" t="n">
+      <c r="F17" s="57" t="n">
         <v>105</v>
       </c>
-      <c r="G17" s="8">
+      <c r="G17" s="57">
         <f>IF($F17="","",$F17-$C17-$M17-$N17)</f>
         <v/>
       </c>
@@ -1960,29 +1984,29 @@
       <c r="I17" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J17" s="6">
+      <c r="J17" s="55">
         <f>$C17/$I17</f>
         <v/>
       </c>
-      <c r="K17" s="6">
+      <c r="K17" s="55">
         <f>IF($F17="","",$F17/$I17)</f>
         <v/>
       </c>
-      <c r="L17" s="6">
+      <c r="L17" s="55">
         <f>IF($G17="","",$G17/$I17)</f>
         <v/>
       </c>
-      <c r="M17" s="7">
+      <c r="M17" s="56">
         <f>IF($F17="","",$F17*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N17" s="6" t="n">
+      <c r="N17" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O17" s="11" t="n">
+      <c r="O17" s="58" t="n">
         <v>50</v>
       </c>
-      <c r="P17" s="11" t="n">
+      <c r="P17" s="58" t="n">
         <v>13</v>
       </c>
       <c r="Q17" s="12" t="inlineStr">
@@ -2020,7 +2044,7 @@
       <c r="Y17" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z17" s="8">
+      <c r="Z17" s="57">
         <f>IF($G17="","",$G17/$Y17)</f>
         <v/>
       </c>
@@ -2035,25 +2059,25 @@
           <t>T-shirt BALENCIAGA T.2 — neuf</t>
         </is>
       </c>
-      <c r="B18" s="14" t="n">
+      <c r="B18" s="59" t="n">
         <v>113.4</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="60">
         <f>$B18+$Y18*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D18" s="16">
+      <c r="D18" s="61">
         <f>$C18/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E18" s="15">
+      <c r="E18" s="60">
         <f>CEILING($D18*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F18" s="17" t="n">
+      <c r="F18" s="62" t="n">
         <v>155</v>
       </c>
-      <c r="G18" s="17">
+      <c r="G18" s="62">
         <f>IF($F18="","",$F18-$C18-$M18-$N18)</f>
         <v/>
       </c>
@@ -2064,29 +2088,29 @@
       <c r="I18" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J18" s="15">
+      <c r="J18" s="60">
         <f>$C18/$I18</f>
         <v/>
       </c>
-      <c r="K18" s="15">
+      <c r="K18" s="60">
         <f>IF($F18="","",$F18/$I18)</f>
         <v/>
       </c>
-      <c r="L18" s="15">
+      <c r="L18" s="60">
         <f>IF($G18="","",$G18/$I18)</f>
         <v/>
       </c>
-      <c r="M18" s="16">
+      <c r="M18" s="61">
         <f>IF($F18="","",$F18*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N18" s="15" t="n">
+      <c r="N18" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="O18" s="20" t="n">
+      <c r="O18" s="63" t="n">
         <v>90</v>
       </c>
-      <c r="P18" s="20" t="n">
+      <c r="P18" s="63" t="n">
         <v>23.4</v>
       </c>
       <c r="Q18" s="21" t="inlineStr">
@@ -2128,7 +2152,7 @@
       <c r="Y18" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="Z18" s="17">
+      <c r="Z18" s="62">
         <f>IF($G18="","",$G18/$Y18)</f>
         <v/>
       </c>
@@ -2143,25 +2167,25 @@
           <t>ADIDAS x STELLA McCARTNEY ASMC Ultraboost 21 P.36 — modèle d'exposition</t>
         </is>
       </c>
-      <c r="B19" s="5" t="n">
+      <c r="B19" s="54" t="n">
         <v>37.8</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="55">
         <f>$B19+$Y19*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D19" s="7">
+      <c r="D19" s="56">
         <f>$C19/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="E19" s="6">
+      <c r="E19" s="55">
         <f>CEILING($D19*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F19" s="8" t="n">
+      <c r="F19" s="57" t="n">
         <v>79</v>
       </c>
-      <c r="G19" s="8">
+      <c r="G19" s="57">
         <f>IF($F19="","",$F19-$C19-$M19-$N19)</f>
         <v/>
       </c>
@@ -2172,30 +2196,30 @@
       <c r="I19" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J19" s="6">
+      <c r="J19" s="55">
         <f>$C19/$I19</f>
         <v/>
       </c>
-      <c r="K19" s="6">
+      <c r="K19" s="55">
         <f>IF($F19="","",$F19/$I19)</f>
         <v/>
       </c>
-      <c r="L19" s="6">
+      <c r="L19" s="55">
         <f>IF($G19="","",$G19/$I19)</f>
         <v/>
       </c>
-      <c r="M19" s="7">
+      <c r="M19" s="56">
         <f>IF($F19="","",$F19*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N19" s="6">
+      <c r="N19" s="55">
         <f>IF($F19="","",$F19*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="O19" s="11" t="n">
+      <c r="O19" s="58" t="n">
         <v>30</v>
       </c>
-      <c r="P19" s="11" t="n">
+      <c r="P19" s="58" t="n">
         <v>7.8</v>
       </c>
       <c r="Q19" s="12" t="inlineStr">
@@ -2233,7 +2257,7 @@
       <c r="Y19" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z19" s="8">
+      <c r="Z19" s="57">
         <f>IF($G19="","",$G19/$Y19)</f>
         <v/>
       </c>
@@ -2248,25 +2272,25 @@
           <t>Blazer noir KARL LAGERFELD T.36 FR — neuf avec étiquette</t>
         </is>
       </c>
-      <c r="B20" s="5" t="n">
+      <c r="B20" s="54" t="n">
         <v>50.4</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="55">
         <f>$B20+$Y20*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D20" s="7">
+      <c r="D20" s="56">
         <f>$C20/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="E20" s="6">
+      <c r="E20" s="55">
         <f>CEILING($D20*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F20" s="8" t="n">
+      <c r="F20" s="57" t="n">
         <v>91</v>
       </c>
-      <c r="G20" s="8">
+      <c r="G20" s="57">
         <f>IF($F20="","",$F20-$C20-$M20-$N20)</f>
         <v/>
       </c>
@@ -2277,30 +2301,30 @@
       <c r="I20" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J20" s="6">
+      <c r="J20" s="55">
         <f>$C20/$I20</f>
         <v/>
       </c>
-      <c r="K20" s="6">
+      <c r="K20" s="55">
         <f>IF($F20="","",$F20/$I20)</f>
         <v/>
       </c>
-      <c r="L20" s="6">
+      <c r="L20" s="55">
         <f>IF($G20="","",$G20/$I20)</f>
         <v/>
       </c>
-      <c r="M20" s="7">
+      <c r="M20" s="56">
         <f>IF($F20="","",$F20*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N20" s="6">
+      <c r="N20" s="55">
         <f>IF($F20="","",$F20*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="O20" s="11" t="n">
+      <c r="O20" s="58" t="n">
         <v>40</v>
       </c>
-      <c r="P20" s="11" t="n">
+      <c r="P20" s="58" t="n">
         <v>10.4</v>
       </c>
       <c r="Q20" s="12" t="inlineStr">
@@ -2338,7 +2362,7 @@
       <c r="Y20" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z20" s="8">
+      <c r="Z20" s="57">
         <f>IF($G20="","",$G20/$Y20)</f>
         <v/>
       </c>
@@ -2353,25 +2377,25 @@
           <t>PHILIPP PLEIN SPORT baskets montantes P.40 — neuves</t>
         </is>
       </c>
-      <c r="B21" s="5" t="n">
+      <c r="B21" s="54" t="n">
         <v>57.51</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C21" s="55">
         <f>$B21+$Y21*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D21" s="7">
+      <c r="D21" s="56">
         <f>$C21/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E21" s="6">
+      <c r="E21" s="55">
         <f>CEILING($D21*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F21" s="8" t="n">
+      <c r="F21" s="57" t="n">
         <v>95</v>
       </c>
-      <c r="G21" s="8">
+      <c r="G21" s="57">
         <f>IF($F21="","",$F21-$C21-$M21-$N21)</f>
         <v/>
       </c>
@@ -2382,29 +2406,29 @@
       <c r="I21" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J21" s="6">
+      <c r="J21" s="55">
         <f>$C21/$I21</f>
         <v/>
       </c>
-      <c r="K21" s="6">
+      <c r="K21" s="55">
         <f>IF($F21="","",$F21/$I21)</f>
         <v/>
       </c>
-      <c r="L21" s="6">
+      <c r="L21" s="55">
         <f>IF($G21="","",$G21/$I21)</f>
         <v/>
       </c>
-      <c r="M21" s="7">
+      <c r="M21" s="56">
         <f>IF($F21="","",$F21*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N21" s="6" t="n">
+      <c r="N21" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O21" s="11" t="n">
+      <c r="O21" s="58" t="n">
         <v>45</v>
       </c>
-      <c r="P21" s="11" t="n">
+      <c r="P21" s="58" t="n">
         <v>11.7</v>
       </c>
       <c r="Q21" s="12" t="inlineStr">
@@ -2442,7 +2466,7 @@
       <c r="Y21" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z21" s="8">
+      <c r="Z21" s="57">
         <f>IF($G21="","",$G21/$Y21)</f>
         <v/>
       </c>
@@ -2457,25 +2481,25 @@
           <t>CHIARA FERRAGNI robe bustier courte T.M — neuve</t>
         </is>
       </c>
-      <c r="B22" s="5" t="n">
+      <c r="B22" s="54" t="n">
         <v>31.95</v>
       </c>
-      <c r="C22" s="6">
+      <c r="C22" s="55">
         <f>$B22+$Y22*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D22" s="7">
+      <c r="D22" s="56">
         <f>$C22/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="E22" s="6">
+      <c r="E22" s="55">
         <f>CEILING($D22*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F22" s="8" t="n">
+      <c r="F22" s="57" t="n">
         <v>69</v>
       </c>
-      <c r="G22" s="8">
+      <c r="G22" s="57">
         <f>IF($F22="","",$F22-$C22-$M22-$N22)</f>
         <v/>
       </c>
@@ -2486,30 +2510,30 @@
       <c r="I22" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J22" s="6">
+      <c r="J22" s="55">
         <f>$C22/$I22</f>
         <v/>
       </c>
-      <c r="K22" s="6">
+      <c r="K22" s="55">
         <f>IF($F22="","",$F22/$I22)</f>
         <v/>
       </c>
-      <c r="L22" s="6">
+      <c r="L22" s="55">
         <f>IF($G22="","",$G22/$I22)</f>
         <v/>
       </c>
-      <c r="M22" s="7">
+      <c r="M22" s="56">
         <f>IF($F22="","",$F22*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N22" s="6">
+      <c r="N22" s="55">
         <f>IF($F22="","",$F22*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="O22" s="11" t="n">
+      <c r="O22" s="58" t="n">
         <v>25</v>
       </c>
-      <c r="P22" s="11" t="n">
+      <c r="P22" s="58" t="n">
         <v>6.5</v>
       </c>
       <c r="Q22" s="12" t="inlineStr">
@@ -2547,7 +2571,7 @@
       <c r="Y22" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z22" s="8">
+      <c r="Z22" s="57">
         <f>IF($G22="","",$G22/$Y22)</f>
         <v/>
       </c>
@@ -2562,25 +2586,25 @@
           <t>PIER ANTONIO GASPARI robe droite bleu marine T.42 — neuve</t>
         </is>
       </c>
-      <c r="B23" s="5" t="n">
+      <c r="B23" s="54" t="n">
         <v>25.56</v>
       </c>
-      <c r="C23" s="6">
+      <c r="C23" s="55">
         <f>$B23+$Y23*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D23" s="7">
+      <c r="D23" s="56">
         <f>$C23/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="E23" s="6">
+      <c r="E23" s="55">
         <f>CEILING($D23*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F23" s="8" t="n">
+      <c r="F23" s="57" t="n">
         <v>62</v>
       </c>
-      <c r="G23" s="8">
+      <c r="G23" s="57">
         <f>IF($F23="","",$F23-$C23-$M23-$N23)</f>
         <v/>
       </c>
@@ -2591,30 +2615,30 @@
       <c r="I23" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J23" s="6">
+      <c r="J23" s="55">
         <f>$C23/$I23</f>
         <v/>
       </c>
-      <c r="K23" s="6">
+      <c r="K23" s="55">
         <f>IF($F23="","",$F23/$I23)</f>
         <v/>
       </c>
-      <c r="L23" s="6">
+      <c r="L23" s="55">
         <f>IF($G23="","",$G23/$I23)</f>
         <v/>
       </c>
-      <c r="M23" s="7">
+      <c r="M23" s="56">
         <f>IF($F23="","",$F23*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N23" s="6">
+      <c r="N23" s="55">
         <f>IF($F23="","",$F23*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="O23" s="11" t="n">
+      <c r="O23" s="58" t="n">
         <v>20</v>
       </c>
-      <c r="P23" s="11" t="n">
+      <c r="P23" s="58" t="n">
         <v>5.2</v>
       </c>
       <c r="Q23" s="12" t="inlineStr">
@@ -2652,7 +2676,7 @@
       <c r="Y23" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z23" s="8">
+      <c r="Z23" s="57">
         <f>IF($G23="","",$G23/$Y23)</f>
         <v/>
       </c>
@@ -2667,25 +2691,25 @@
           <t>Lot de 4 toupies BEYBLADE HASBRO</t>
         </is>
       </c>
-      <c r="B24" s="23" t="n">
+      <c r="B24" s="64" t="n">
         <v>19.17</v>
       </c>
-      <c r="C24" s="24">
+      <c r="C24" s="65">
         <f>$B24+$Y24*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D24" s="25">
+      <c r="D24" s="66">
         <f>$C24/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E24" s="24">
+      <c r="E24" s="65">
         <f>CEILING($D24*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F24" s="26" t="n">
+      <c r="F24" s="67" t="n">
         <v>55</v>
       </c>
-      <c r="G24" s="26">
+      <c r="G24" s="67">
         <f>IF($F24="","",$F24-$C24-$M24-$N24)</f>
         <v/>
       </c>
@@ -2696,29 +2720,29 @@
       <c r="I24" s="28" t="n">
         <v>4</v>
       </c>
-      <c r="J24" s="24">
+      <c r="J24" s="65">
         <f>$C24/$I24</f>
         <v/>
       </c>
-      <c r="K24" s="24">
+      <c r="K24" s="65">
         <f>IF($F24="","",$F24/$I24)</f>
         <v/>
       </c>
-      <c r="L24" s="24">
+      <c r="L24" s="65">
         <f>IF($G24="","",$G24/$I24)</f>
         <v/>
       </c>
-      <c r="M24" s="25">
+      <c r="M24" s="66">
         <f>IF($F24="","",$F24*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N24" s="24" t="n">
+      <c r="N24" s="65" t="n">
         <v>0</v>
       </c>
-      <c r="O24" s="29" t="n">
+      <c r="O24" s="68" t="n">
         <v>15</v>
       </c>
-      <c r="P24" s="29" t="n">
+      <c r="P24" s="68" t="n">
         <v>3.9</v>
       </c>
       <c r="Q24" s="30" t="inlineStr">
@@ -2756,7 +2780,7 @@
       <c r="Y24" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="Z24" s="26">
+      <c r="Z24" s="67">
         <f>IF($G24="","",$G24/$Y24)</f>
         <v/>
       </c>
@@ -2766,105 +2790,109 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>Ballerines MASSIMO DUTTI P.41 — traces d'essayage</t>
         </is>
       </c>
-      <c r="B25" s="5" t="n">
+      <c r="B25" s="59" t="n">
         <v>25.2</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C25" s="60">
         <f>$B25+$Y25*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D25" s="7">
+      <c r="D25" s="61">
         <f>$C25/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E25" s="6">
+      <c r="E25" s="60">
         <f>CEILING($D25*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F25" s="8" t="n">
-        <v>61</v>
-      </c>
-      <c r="G25" s="8">
+      <c r="F25" s="62" t="n">
+        <v>50</v>
+      </c>
+      <c r="G25" s="62">
         <f>IF($F25="","",$F25-$C25-$M25-$N25)</f>
         <v/>
       </c>
-      <c r="H25" s="9">
+      <c r="H25" s="18">
         <f>IF($G25="","",$G25/$C25)</f>
         <v/>
       </c>
-      <c r="I25" s="10" t="n">
+      <c r="I25" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J25" s="6">
+      <c r="J25" s="60">
         <f>$C25/$I25</f>
         <v/>
       </c>
-      <c r="K25" s="6">
+      <c r="K25" s="60">
         <f>IF($F25="","",$F25/$I25)</f>
         <v/>
       </c>
-      <c r="L25" s="6">
+      <c r="L25" s="60">
         <f>IF($G25="","",$G25/$I25)</f>
         <v/>
       </c>
-      <c r="M25" s="7">
+      <c r="M25" s="61">
         <f>IF($F25="","",$F25*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N25" s="6" t="n">
+      <c r="N25" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="O25" s="11" t="n">
+      <c r="O25" s="63" t="n">
         <v>20</v>
       </c>
-      <c r="P25" s="11" t="n">
+      <c r="P25" s="63" t="n">
         <v>5.2</v>
       </c>
-      <c r="Q25" s="12" t="inlineStr">
+      <c r="Q25" s="21" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="R25" s="12" t="inlineStr">
+      <c r="R25" s="21" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="S25" s="12" t="inlineStr">
+      <c r="S25" s="21" t="inlineStr">
         <is>
           <t>FB2026-43716</t>
         </is>
       </c>
-      <c r="T25" s="12" t="inlineStr">
+      <c r="T25" s="21" t="inlineStr">
         <is>
           <t>439</t>
         </is>
       </c>
-      <c r="U25" s="4" t="inlineStr">
-        <is>
-          <t>Leboncoin + eBay</t>
-        </is>
-      </c>
-      <c r="V25" s="4" t="inlineStr"/>
-      <c r="W25" s="4" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="X25" s="4" t="inlineStr"/>
-      <c r="Y25" s="4" t="n">
+      <c r="U25" s="13" t="inlineStr">
+        <is>
+          <t>Vinted, Espagne — non encaissé</t>
+        </is>
+      </c>
+      <c r="V25" s="13" t="inlineStr"/>
+      <c r="W25" s="13" t="inlineStr">
+        <is>
+          <t>VENDUE, en attente</t>
+        </is>
+      </c>
+      <c r="X25" s="13" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="Y25" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="Z25" s="8">
+      <c r="Z25" s="62">
         <f>IF($G25="","",$G25/$Y25)</f>
         <v/>
       </c>
-      <c r="AA25" s="4">
+      <c r="AA25" s="13">
         <f>IF($Z25="","",IF($Z25&gt;=25,"atteint",TEXT(25-$Z25,"0.00")&amp;" € manquants"))</f>
         <v/>
       </c>
@@ -2875,25 +2903,25 @@
           <t>GEOX baskets P.35 — neuves</t>
         </is>
       </c>
-      <c r="B26" s="5" t="n">
+      <c r="B26" s="54" t="n">
         <v>21.73</v>
       </c>
-      <c r="C26" s="6">
+      <c r="C26" s="55">
         <f>$B26+$Y26*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D26" s="7">
+      <c r="D26" s="56">
         <f>$C26/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E26" s="6">
+      <c r="E26" s="55">
         <f>CEILING($D26*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F26" s="8" t="n">
+      <c r="F26" s="57" t="n">
         <v>54</v>
       </c>
-      <c r="G26" s="8">
+      <c r="G26" s="57">
         <f>IF($F26="","",$F26-$C26-$M26-$N26)</f>
         <v/>
       </c>
@@ -2904,29 +2932,29 @@
       <c r="I26" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J26" s="6">
+      <c r="J26" s="55">
         <f>$C26/$I26</f>
         <v/>
       </c>
-      <c r="K26" s="6">
+      <c r="K26" s="55">
         <f>IF($F26="","",$F26/$I26)</f>
         <v/>
       </c>
-      <c r="L26" s="6">
+      <c r="L26" s="55">
         <f>IF($G26="","",$G26/$I26)</f>
         <v/>
       </c>
-      <c r="M26" s="7">
+      <c r="M26" s="56">
         <f>IF($F26="","",$F26*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N26" s="6" t="n">
+      <c r="N26" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O26" s="11" t="n">
+      <c r="O26" s="58" t="n">
         <v>17</v>
       </c>
-      <c r="P26" s="11" t="n">
+      <c r="P26" s="58" t="n">
         <v>4.42</v>
       </c>
       <c r="Q26" s="12" t="inlineStr">
@@ -2964,7 +2992,7 @@
       <c r="Y26" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z26" s="8">
+      <c r="Z26" s="57">
         <f>IF($G26="","",$G26/$Y26)</f>
         <v/>
       </c>
@@ -2979,25 +3007,25 @@
           <t>1 booster box Pokémon MEGA Nihil Zero (Munikis Zero) M3 — 30 boosters de 5 cartes — 2 lots de 15 à 49 €, blister à photographier avant ouverture</t>
         </is>
       </c>
-      <c r="B27" s="5" t="n">
+      <c r="B27" s="54" t="n">
         <v>69.23999999999999</v>
       </c>
-      <c r="C27" s="6">
+      <c r="C27" s="55">
         <f>$B27</f>
         <v/>
       </c>
-      <c r="D27" s="7">
+      <c r="D27" s="56">
         <f>$C27/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E27" s="6">
+      <c r="E27" s="55">
         <f>CEILING($D27*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F27" s="8" t="n">
+      <c r="F27" s="57" t="n">
         <v>98</v>
       </c>
-      <c r="G27" s="8">
+      <c r="G27" s="57">
         <f>IF($F27="","",$F27-$C27-$M27-$N27)</f>
         <v/>
       </c>
@@ -3008,23 +3036,23 @@
       <c r="I27" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="J27" s="6">
+      <c r="J27" s="55">
         <f>$C27/$I27</f>
         <v/>
       </c>
-      <c r="K27" s="6">
+      <c r="K27" s="55">
         <f>IF($F27="","",$F27/$I27)</f>
         <v/>
       </c>
-      <c r="L27" s="6">
+      <c r="L27" s="55">
         <f>IF($G27="","",$G27/$I27)</f>
         <v/>
       </c>
-      <c r="M27" s="7">
+      <c r="M27" s="56">
         <f>IF($F27="","",$F27*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N27" s="6" t="n">
+      <c r="N27" s="55" t="n">
         <v>0</v>
       </c>
       <c r="O27" s="31" t="n"/>
@@ -3064,7 +3092,7 @@
       <c r="Y27" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="Z27" s="8">
+      <c r="Z27" s="57">
         <f>IF($G27="","",$G27/$Y27)</f>
         <v/>
       </c>
@@ -3079,25 +3107,25 @@
           <t>Veste en jean ARMANI EXCHANGE T.S — neuve</t>
         </is>
       </c>
-      <c r="B28" s="14" t="n">
+      <c r="B28" s="59" t="n">
         <v>25.2</v>
       </c>
-      <c r="C28" s="15">
+      <c r="C28" s="60">
         <f>$B28+$Y28*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D28" s="16">
+      <c r="D28" s="61">
         <f>$C28/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E28" s="15">
+      <c r="E28" s="60">
         <f>CEILING($D28*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F28" s="17" t="n">
+      <c r="F28" s="62" t="n">
         <v>50</v>
       </c>
-      <c r="G28" s="17">
+      <c r="G28" s="62">
         <f>IF($F28="","",$F28-$C28-$M28-$N28)</f>
         <v/>
       </c>
@@ -3108,29 +3136,29 @@
       <c r="I28" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J28" s="15">
+      <c r="J28" s="60">
         <f>$C28/$I28</f>
         <v/>
       </c>
-      <c r="K28" s="15">
+      <c r="K28" s="60">
         <f>IF($F28="","",$F28/$I28)</f>
         <v/>
       </c>
-      <c r="L28" s="15">
+      <c r="L28" s="60">
         <f>IF($G28="","",$G28/$I28)</f>
         <v/>
       </c>
-      <c r="M28" s="16">
+      <c r="M28" s="61">
         <f>IF($F28="","",$F28*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N28" s="15" t="n">
+      <c r="N28" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="O28" s="20" t="n">
+      <c r="O28" s="63" t="n">
         <v>20</v>
       </c>
-      <c r="P28" s="20" t="n">
+      <c r="P28" s="63" t="n">
         <v>5.2</v>
       </c>
       <c r="Q28" s="21" t="inlineStr">
@@ -3172,7 +3200,7 @@
       <c r="Y28" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="Z28" s="17">
+      <c r="Z28" s="62">
         <f>IF($G28="","",$G28/$Y28)</f>
         <v/>
       </c>
@@ -3187,25 +3215,25 @@
           <t>Short BA&amp;SH Fegor T.34 — neuf</t>
         </is>
       </c>
-      <c r="B29" s="5" t="n">
+      <c r="B29" s="54" t="n">
         <v>50.4</v>
       </c>
-      <c r="C29" s="6">
+      <c r="C29" s="55">
         <f>$B29+$Y29*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D29" s="7">
+      <c r="D29" s="56">
         <f>$C29/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="E29" s="6">
+      <c r="E29" s="55">
         <f>CEILING($D29*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F29" s="8" t="n">
+      <c r="F29" s="57" t="n">
         <v>75</v>
       </c>
-      <c r="G29" s="8">
+      <c r="G29" s="57">
         <f>IF($F29="","",$F29-$C29-$M29-$N29)</f>
         <v/>
       </c>
@@ -3216,30 +3244,30 @@
       <c r="I29" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J29" s="6">
+      <c r="J29" s="55">
         <f>$C29/$I29</f>
         <v/>
       </c>
-      <c r="K29" s="6">
+      <c r="K29" s="55">
         <f>IF($F29="","",$F29/$I29)</f>
         <v/>
       </c>
-      <c r="L29" s="6">
+      <c r="L29" s="55">
         <f>IF($G29="","",$G29/$I29)</f>
         <v/>
       </c>
-      <c r="M29" s="7">
+      <c r="M29" s="56">
         <f>IF($F29="","",$F29*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N29" s="6">
+      <c r="N29" s="55">
         <f>IF($F29="","",$F29*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="O29" s="11" t="n">
+      <c r="O29" s="58" t="n">
         <v>40</v>
       </c>
-      <c r="P29" s="11" t="n">
+      <c r="P29" s="58" t="n">
         <v>10.4</v>
       </c>
       <c r="Q29" s="12" t="inlineStr">
@@ -3277,7 +3305,7 @@
       <c r="Y29" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z29" s="8">
+      <c r="Z29" s="57">
         <f>IF($G29="","",$G29/$Y29)</f>
         <v/>
       </c>
@@ -3292,25 +3320,25 @@
           <t>NEW BALANCE G19064IK Alkaline Green P.38½ — neuves avec boîte</t>
         </is>
       </c>
-      <c r="B30" s="5" t="n">
+      <c r="B30" s="54" t="n">
         <v>75.59999999999999</v>
       </c>
-      <c r="C30" s="6">
+      <c r="C30" s="55">
         <f>$B30+$Y30*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D30" s="7">
+      <c r="D30" s="56">
         <f>$C30/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E30" s="6">
+      <c r="E30" s="55">
         <f>CEILING($D30*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F30" s="8" t="n">
+      <c r="F30" s="57" t="n">
         <v>99</v>
       </c>
-      <c r="G30" s="8">
+      <c r="G30" s="57">
         <f>IF($F30="","",$F30-$C30-$M30-$N30)</f>
         <v/>
       </c>
@@ -3321,29 +3349,29 @@
       <c r="I30" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J30" s="6">
+      <c r="J30" s="55">
         <f>$C30/$I30</f>
         <v/>
       </c>
-      <c r="K30" s="6">
+      <c r="K30" s="55">
         <f>IF($F30="","",$F30/$I30)</f>
         <v/>
       </c>
-      <c r="L30" s="6">
+      <c r="L30" s="55">
         <f>IF($G30="","",$G30/$I30)</f>
         <v/>
       </c>
-      <c r="M30" s="7">
+      <c r="M30" s="56">
         <f>IF($F30="","",$F30*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N30" s="6" t="n">
+      <c r="N30" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O30" s="11" t="n">
+      <c r="O30" s="58" t="n">
         <v>60</v>
       </c>
-      <c r="P30" s="11" t="n">
+      <c r="P30" s="58" t="n">
         <v>15.6</v>
       </c>
       <c r="Q30" s="12" t="inlineStr">
@@ -3381,7 +3409,7 @@
       <c r="Y30" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z30" s="8">
+      <c r="Z30" s="57">
         <f>IF($G30="","",$G30/$Y30)</f>
         <v/>
       </c>
@@ -3396,25 +3424,25 @@
           <t>SALOMON X Ultra 5 Mid GTX P.44 — neuves</t>
         </is>
       </c>
-      <c r="B31" s="14" t="n">
+      <c r="B31" s="59" t="n">
         <v>76.68000000000001</v>
       </c>
-      <c r="C31" s="15">
+      <c r="C31" s="60">
         <f>$B31+$Y31*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D31" s="16">
+      <c r="D31" s="61">
         <f>$C31/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E31" s="15">
+      <c r="E31" s="60">
         <f>CEILING($D31*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F31" s="17" t="n">
+      <c r="F31" s="62" t="n">
         <v>100</v>
       </c>
-      <c r="G31" s="17">
+      <c r="G31" s="62">
         <f>IF($F31="","",$F31-$C31-$M31-$N31)</f>
         <v/>
       </c>
@@ -3425,29 +3453,29 @@
       <c r="I31" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J31" s="15">
+      <c r="J31" s="60">
         <f>$C31/$I31</f>
         <v/>
       </c>
-      <c r="K31" s="15">
+      <c r="K31" s="60">
         <f>IF($F31="","",$F31/$I31)</f>
         <v/>
       </c>
-      <c r="L31" s="15">
+      <c r="L31" s="60">
         <f>IF($G31="","",$G31/$I31)</f>
         <v/>
       </c>
-      <c r="M31" s="16">
+      <c r="M31" s="61">
         <f>IF($F31="","",$F31*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N31" s="15" t="n">
+      <c r="N31" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="O31" s="20" t="n">
+      <c r="O31" s="63" t="n">
         <v>60</v>
       </c>
-      <c r="P31" s="20" t="n">
+      <c r="P31" s="63" t="n">
         <v>15.6</v>
       </c>
       <c r="Q31" s="21" t="inlineStr">
@@ -3489,7 +3517,7 @@
       <c r="Y31" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="Z31" s="17">
+      <c r="Z31" s="62">
         <f>IF($G31="","",$G31/$Y31)</f>
         <v/>
       </c>
@@ -3504,25 +3532,25 @@
           <t>Sac demi-lune nylon noir KARL LAGERFELD JEANS — neuf avec étiquette</t>
         </is>
       </c>
-      <c r="B32" s="14" t="n">
+      <c r="B32" s="59" t="n">
         <v>50.4</v>
       </c>
-      <c r="C32" s="15">
+      <c r="C32" s="60">
         <f>$B32+$Y32*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D32" s="16">
+      <c r="D32" s="61">
         <f>$C32/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E32" s="15">
+      <c r="E32" s="60">
         <f>CEILING($D32*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F32" s="17" t="n">
+      <c r="F32" s="62" t="n">
         <v>70</v>
       </c>
-      <c r="G32" s="17">
+      <c r="G32" s="62">
         <f>IF($F32="","",$F32-$C32-$M32-$N32)</f>
         <v/>
       </c>
@@ -3533,29 +3561,29 @@
       <c r="I32" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J32" s="15">
+      <c r="J32" s="60">
         <f>$C32/$I32</f>
         <v/>
       </c>
-      <c r="K32" s="15">
+      <c r="K32" s="60">
         <f>IF($F32="","",$F32/$I32)</f>
         <v/>
       </c>
-      <c r="L32" s="15">
+      <c r="L32" s="60">
         <f>IF($G32="","",$G32/$I32)</f>
         <v/>
       </c>
-      <c r="M32" s="16">
+      <c r="M32" s="61">
         <f>IF($F32="","",$F32*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N32" s="15" t="n">
+      <c r="N32" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="O32" s="20" t="n">
+      <c r="O32" s="63" t="n">
         <v>40</v>
       </c>
-      <c r="P32" s="20" t="n">
+      <c r="P32" s="63" t="n">
         <v>10.4</v>
       </c>
       <c r="Q32" s="21" t="inlineStr">
@@ -3597,7 +3625,7 @@
       <c r="Y32" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="Z32" s="17">
+      <c r="Z32" s="62">
         <f>IF($G32="","",$G32/$Y32)</f>
         <v/>
       </c>
@@ -3612,25 +3640,25 @@
           <t>EMPORIO ARMANI baskets P.36 — neuves</t>
         </is>
       </c>
-      <c r="B33" s="5" t="n">
+      <c r="B33" s="54" t="n">
         <v>51.12</v>
       </c>
-      <c r="C33" s="6">
+      <c r="C33" s="55">
         <f>$B33+$Y33*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D33" s="7">
+      <c r="D33" s="56">
         <f>$C33/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E33" s="6">
+      <c r="E33" s="55">
         <f>CEILING($D33*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F33" s="8" t="n">
+      <c r="F33" s="57" t="n">
         <v>69</v>
       </c>
-      <c r="G33" s="8">
+      <c r="G33" s="57">
         <f>IF($F33="","",$F33-$C33-$M33-$N33)</f>
         <v/>
       </c>
@@ -3641,29 +3669,29 @@
       <c r="I33" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J33" s="6">
+      <c r="J33" s="55">
         <f>$C33/$I33</f>
         <v/>
       </c>
-      <c r="K33" s="6">
+      <c r="K33" s="55">
         <f>IF($F33="","",$F33/$I33)</f>
         <v/>
       </c>
-      <c r="L33" s="6">
+      <c r="L33" s="55">
         <f>IF($G33="","",$G33/$I33)</f>
         <v/>
       </c>
-      <c r="M33" s="7">
+      <c r="M33" s="56">
         <f>IF($F33="","",$F33*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N33" s="6" t="n">
+      <c r="N33" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O33" s="11" t="n">
+      <c r="O33" s="58" t="n">
         <v>40</v>
       </c>
-      <c r="P33" s="11" t="n">
+      <c r="P33" s="58" t="n">
         <v>10.4</v>
       </c>
       <c r="Q33" s="12" t="inlineStr">
@@ -3701,7 +3729,7 @@
       <c r="Y33" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z33" s="8">
+      <c r="Z33" s="57">
         <f>IF($G33="","",$G33/$Y33)</f>
         <v/>
       </c>
@@ -3716,25 +3744,25 @@
           <t>Lot de 4 toupies BEYBLADE HASBRO</t>
         </is>
       </c>
-      <c r="B34" s="23" t="n">
+      <c r="B34" s="64" t="n">
         <v>38.34</v>
       </c>
-      <c r="C34" s="24">
+      <c r="C34" s="65">
         <f>$B34+$Y34*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D34" s="25">
+      <c r="D34" s="66">
         <f>$C34/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E34" s="24">
+      <c r="E34" s="65">
         <f>CEILING($D34*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F34" s="26" t="n">
+      <c r="F34" s="67" t="n">
         <v>55</v>
       </c>
-      <c r="G34" s="26">
+      <c r="G34" s="67">
         <f>IF($F34="","",$F34-$C34-$M34-$N34)</f>
         <v/>
       </c>
@@ -3745,29 +3773,29 @@
       <c r="I34" s="28" t="n">
         <v>4</v>
       </c>
-      <c r="J34" s="24">
+      <c r="J34" s="65">
         <f>$C34/$I34</f>
         <v/>
       </c>
-      <c r="K34" s="24">
+      <c r="K34" s="65">
         <f>IF($F34="","",$F34/$I34)</f>
         <v/>
       </c>
-      <c r="L34" s="24">
+      <c r="L34" s="65">
         <f>IF($G34="","",$G34/$I34)</f>
         <v/>
       </c>
-      <c r="M34" s="25">
+      <c r="M34" s="66">
         <f>IF($F34="","",$F34*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N34" s="24" t="n">
+      <c r="N34" s="65" t="n">
         <v>0</v>
       </c>
-      <c r="O34" s="29" t="n">
+      <c r="O34" s="68" t="n">
         <v>30</v>
       </c>
-      <c r="P34" s="29" t="n">
+      <c r="P34" s="68" t="n">
         <v>7.8</v>
       </c>
       <c r="Q34" s="30" t="inlineStr">
@@ -3805,7 +3833,7 @@
       <c r="Y34" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="Z34" s="26">
+      <c r="Z34" s="67">
         <f>IF($G34="","",$G34/$Y34)</f>
         <v/>
       </c>
@@ -3820,25 +3848,25 @@
           <t>NEW BALANCE sneakers P.38 — neuves</t>
         </is>
       </c>
-      <c r="B35" s="5" t="n">
+      <c r="B35" s="54" t="n">
         <v>38.34</v>
       </c>
-      <c r="C35" s="6">
+      <c r="C35" s="55">
         <f>$B35+$Y35*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D35" s="7">
+      <c r="D35" s="56">
         <f>$C35/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E35" s="6">
+      <c r="E35" s="55">
         <f>CEILING($D35*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F35" s="8" t="n">
+      <c r="F35" s="57" t="n">
         <v>54</v>
       </c>
-      <c r="G35" s="8">
+      <c r="G35" s="57">
         <f>IF($F35="","",$F35-$C35-$M35-$N35)</f>
         <v/>
       </c>
@@ -3849,29 +3877,29 @@
       <c r="I35" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J35" s="6">
+      <c r="J35" s="55">
         <f>$C35/$I35</f>
         <v/>
       </c>
-      <c r="K35" s="6">
+      <c r="K35" s="55">
         <f>IF($F35="","",$F35/$I35)</f>
         <v/>
       </c>
-      <c r="L35" s="6">
+      <c r="L35" s="55">
         <f>IF($G35="","",$G35/$I35)</f>
         <v/>
       </c>
-      <c r="M35" s="7">
+      <c r="M35" s="56">
         <f>IF($F35="","",$F35*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N35" s="6" t="n">
+      <c r="N35" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O35" s="11" t="n">
+      <c r="O35" s="58" t="n">
         <v>30</v>
       </c>
-      <c r="P35" s="11" t="n">
+      <c r="P35" s="58" t="n">
         <v>7.8</v>
       </c>
       <c r="Q35" s="12" t="inlineStr">
@@ -3909,7 +3937,7 @@
       <c r="Y35" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z35" s="8">
+      <c r="Z35" s="57">
         <f>IF($G35="","",$G35/$Y35)</f>
         <v/>
       </c>
@@ -3924,25 +3952,25 @@
           <t>NEW BALANCE baskets montantes P.44 — neuves</t>
         </is>
       </c>
-      <c r="B36" s="5" t="n">
+      <c r="B36" s="54" t="n">
         <v>51.12</v>
       </c>
-      <c r="C36" s="6">
+      <c r="C36" s="55">
         <f>$B36+$Y36*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D36" s="7">
+      <c r="D36" s="56">
         <f>$C36/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E36" s="6">
+      <c r="E36" s="55">
         <f>CEILING($D36*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F36" s="8" t="n">
+      <c r="F36" s="57" t="n">
         <v>65</v>
       </c>
-      <c r="G36" s="8">
+      <c r="G36" s="57">
         <f>IF($F36="","",$F36-$C36-$M36-$N36)</f>
         <v/>
       </c>
@@ -3953,29 +3981,29 @@
       <c r="I36" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J36" s="6">
+      <c r="J36" s="55">
         <f>$C36/$I36</f>
         <v/>
       </c>
-      <c r="K36" s="6">
+      <c r="K36" s="55">
         <f>IF($F36="","",$F36/$I36)</f>
         <v/>
       </c>
-      <c r="L36" s="6">
+      <c r="L36" s="55">
         <f>IF($G36="","",$G36/$I36)</f>
         <v/>
       </c>
-      <c r="M36" s="7">
+      <c r="M36" s="56">
         <f>IF($F36="","",$F36*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N36" s="6" t="n">
+      <c r="N36" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O36" s="11" t="n">
+      <c r="O36" s="58" t="n">
         <v>40</v>
       </c>
-      <c r="P36" s="11" t="n">
+      <c r="P36" s="58" t="n">
         <v>10.4</v>
       </c>
       <c r="Q36" s="12" t="inlineStr">
@@ -4013,7 +4041,7 @@
       <c r="Y36" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z36" s="8">
+      <c r="Z36" s="57">
         <f>IF($G36="","",$G36/$Y36)</f>
         <v/>
       </c>
@@ -4028,25 +4056,25 @@
           <t>TOMMY JEANS baskets basses P.40 — neuves</t>
         </is>
       </c>
-      <c r="B37" s="5" t="n">
+      <c r="B37" s="54" t="n">
         <v>52.4</v>
       </c>
-      <c r="C37" s="6">
+      <c r="C37" s="55">
         <f>$B37+$Y37*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D37" s="7">
+      <c r="D37" s="56">
         <f>$C37/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E37" s="6">
+      <c r="E37" s="55">
         <f>CEILING($D37*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F37" s="8" t="n">
+      <c r="F37" s="57" t="n">
         <v>65</v>
       </c>
-      <c r="G37" s="8">
+      <c r="G37" s="57">
         <f>IF($F37="","",$F37-$C37-$M37-$N37)</f>
         <v/>
       </c>
@@ -4057,29 +4085,29 @@
       <c r="I37" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J37" s="6">
+      <c r="J37" s="55">
         <f>$C37/$I37</f>
         <v/>
       </c>
-      <c r="K37" s="6">
+      <c r="K37" s="55">
         <f>IF($F37="","",$F37/$I37)</f>
         <v/>
       </c>
-      <c r="L37" s="6">
+      <c r="L37" s="55">
         <f>IF($G37="","",$G37/$I37)</f>
         <v/>
       </c>
-      <c r="M37" s="7">
+      <c r="M37" s="56">
         <f>IF($F37="","",$F37*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N37" s="6" t="n">
+      <c r="N37" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O37" s="11" t="n">
+      <c r="O37" s="58" t="n">
         <v>41</v>
       </c>
-      <c r="P37" s="11" t="n">
+      <c r="P37" s="58" t="n">
         <v>10.66</v>
       </c>
       <c r="Q37" s="12" t="inlineStr">
@@ -4117,7 +4145,7 @@
       <c r="Y37" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z37" s="8">
+      <c r="Z37" s="57">
         <f>IF($G37="","",$G37/$Y37)</f>
         <v/>
       </c>
@@ -4132,25 +4160,25 @@
           <t>LACOSTE sneakers P.42 — neuves</t>
         </is>
       </c>
-      <c r="B38" s="14" t="n">
+      <c r="B38" s="59" t="n">
         <v>57.51</v>
       </c>
-      <c r="C38" s="15">
+      <c r="C38" s="60">
         <f>$B38+$Y38*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D38" s="16">
+      <c r="D38" s="61">
         <f>$C38/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E38" s="15">
+      <c r="E38" s="60">
         <f>CEILING($D38*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F38" s="17" t="n">
+      <c r="F38" s="62" t="n">
         <v>70</v>
       </c>
-      <c r="G38" s="17">
+      <c r="G38" s="62">
         <f>IF($F38="","",$F38-$C38-$M38-$N38)</f>
         <v/>
       </c>
@@ -4161,29 +4189,29 @@
       <c r="I38" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J38" s="15">
+      <c r="J38" s="60">
         <f>$C38/$I38</f>
         <v/>
       </c>
-      <c r="K38" s="15">
+      <c r="K38" s="60">
         <f>IF($F38="","",$F38/$I38)</f>
         <v/>
       </c>
-      <c r="L38" s="15">
+      <c r="L38" s="60">
         <f>IF($G38="","",$G38/$I38)</f>
         <v/>
       </c>
-      <c r="M38" s="16">
+      <c r="M38" s="61">
         <f>IF($F38="","",$F38*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N38" s="15" t="n">
+      <c r="N38" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="O38" s="20" t="n">
+      <c r="O38" s="63" t="n">
         <v>45</v>
       </c>
-      <c r="P38" s="20" t="n">
+      <c r="P38" s="63" t="n">
         <v>11.7</v>
       </c>
       <c r="Q38" s="21" t="inlineStr">
@@ -4225,7 +4253,7 @@
       <c r="Y38" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="Z38" s="17">
+      <c r="Z38" s="62">
         <f>IF($G38="","",$G38/$Y38)</f>
         <v/>
       </c>
@@ -4240,25 +4268,25 @@
           <t>Pompe immergée ROBBY VP550W noir et bleu — produit d'occasion</t>
         </is>
       </c>
-      <c r="B39" s="5" t="n">
+      <c r="B39" s="54" t="n">
         <v>35.9</v>
       </c>
-      <c r="C39" s="6">
+      <c r="C39" s="55">
         <f>$B39</f>
         <v/>
       </c>
-      <c r="D39" s="7">
+      <c r="D39" s="56">
         <f>$C39/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E39" s="6">
+      <c r="E39" s="55">
         <f>CEILING($D39*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F39" s="8" t="n">
+      <c r="F39" s="57" t="n">
         <v>45</v>
       </c>
-      <c r="G39" s="8">
+      <c r="G39" s="57">
         <f>IF($F39="","",$F39-$C39-$M39-$N39)</f>
         <v/>
       </c>
@@ -4269,23 +4297,23 @@
       <c r="I39" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J39" s="6">
+      <c r="J39" s="55">
         <f>$C39/$I39</f>
         <v/>
       </c>
-      <c r="K39" s="6">
+      <c r="K39" s="55">
         <f>IF($F39="","",$F39/$I39)</f>
         <v/>
       </c>
-      <c r="L39" s="6">
+      <c r="L39" s="55">
         <f>IF($G39="","",$G39/$I39)</f>
         <v/>
       </c>
-      <c r="M39" s="7">
+      <c r="M39" s="56">
         <f>IF($F39="","",$F39*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N39" s="6" t="n">
+      <c r="N39" s="55" t="n">
         <v>0</v>
       </c>
       <c r="O39" s="31" t="n"/>
@@ -4325,7 +4353,7 @@
       <c r="Y39" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z39" s="8">
+      <c r="Z39" s="57">
         <f>IF($G39="","",$G39/$Y39)</f>
         <v/>
       </c>
@@ -4340,25 +4368,25 @@
           <t>Pompe immergée ROBBY VP550W noir/gris — comme neuf, SOCLE CASSÉ</t>
         </is>
       </c>
-      <c r="B40" s="5" t="n">
+      <c r="B40" s="54" t="n">
         <v>28.29</v>
       </c>
-      <c r="C40" s="6">
+      <c r="C40" s="55">
         <f>$B40</f>
         <v/>
       </c>
-      <c r="D40" s="7">
+      <c r="D40" s="56">
         <f>$C40/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E40" s="6">
+      <c r="E40" s="55">
         <f>CEILING($D40*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F40" s="8" t="n">
+      <c r="F40" s="57" t="n">
         <v>35</v>
       </c>
-      <c r="G40" s="8">
+      <c r="G40" s="57">
         <f>IF($F40="","",$F40-$C40-$M40-$N40)</f>
         <v/>
       </c>
@@ -4369,23 +4397,23 @@
       <c r="I40" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J40" s="6">
+      <c r="J40" s="55">
         <f>$C40/$I40</f>
         <v/>
       </c>
-      <c r="K40" s="6">
+      <c r="K40" s="55">
         <f>IF($F40="","",$F40/$I40)</f>
         <v/>
       </c>
-      <c r="L40" s="6">
+      <c r="L40" s="55">
         <f>IF($G40="","",$G40/$I40)</f>
         <v/>
       </c>
-      <c r="M40" s="7">
+      <c r="M40" s="56">
         <f>IF($F40="","",$F40*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N40" s="6" t="n">
+      <c r="N40" s="55" t="n">
         <v>0</v>
       </c>
       <c r="O40" s="31" t="n"/>
@@ -4425,7 +4453,7 @@
       <c r="Y40" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z40" s="8">
+      <c r="Z40" s="57">
         <f>IF($G40="","",$G40/$Y40)</f>
         <v/>
       </c>
@@ -4440,25 +4468,25 @@
           <t>2 boosters Pokémon MEGA Storm Emeralda M6 — 5 cartes chacun — set sorti le 31/07/2026, publier vite</t>
         </is>
       </c>
-      <c r="B41" s="5" t="n">
+      <c r="B41" s="54" t="n">
         <v>12.74</v>
       </c>
-      <c r="C41" s="6">
+      <c r="C41" s="55">
         <f>$B41</f>
         <v/>
       </c>
-      <c r="D41" s="7">
+      <c r="D41" s="56">
         <f>$C41/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E41" s="6">
+      <c r="E41" s="55">
         <f>CEILING($D41*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F41" s="8" t="n">
+      <c r="F41" s="57" t="n">
         <v>19</v>
       </c>
-      <c r="G41" s="8">
+      <c r="G41" s="57">
         <f>IF($F41="","",$F41-$C41-$M41-$N41)</f>
         <v/>
       </c>
@@ -4469,23 +4497,23 @@
       <c r="I41" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J41" s="6">
+      <c r="J41" s="55">
         <f>$C41/$I41</f>
         <v/>
       </c>
-      <c r="K41" s="6">
+      <c r="K41" s="55">
         <f>IF($F41="","",$F41/$I41)</f>
         <v/>
       </c>
-      <c r="L41" s="6">
+      <c r="L41" s="55">
         <f>IF($G41="","",$G41/$I41)</f>
         <v/>
       </c>
-      <c r="M41" s="7">
+      <c r="M41" s="56">
         <f>IF($F41="","",$F41*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N41" s="6" t="n">
+      <c r="N41" s="55" t="n">
         <v>0</v>
       </c>
       <c r="O41" s="31" t="n"/>
@@ -4525,7 +4553,7 @@
       <c r="Y41" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z41" s="8">
+      <c r="Z41" s="57">
         <f>IF($G41="","",$G41/$Y41)</f>
         <v/>
       </c>
@@ -4540,23 +4568,23 @@
           <t>1 booster Pokémon High Class Pack MEGA Dream ex M2a — 10 cartes dans le booster</t>
         </is>
       </c>
-      <c r="B42" s="14" t="n">
+      <c r="B42" s="59" t="n">
         <v>12.95</v>
       </c>
-      <c r="C42" s="15">
+      <c r="C42" s="60">
         <f>$B42</f>
         <v/>
       </c>
-      <c r="D42" s="16">
+      <c r="D42" s="61">
         <f>$C42/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E42" s="15">
+      <c r="E42" s="60">
         <f>CEILING($D42*Paramètres!$B$24,1)</f>
         <v/>
       </c>
       <c r="F42" s="32" t="n"/>
-      <c r="G42" s="17">
+      <c r="G42" s="62">
         <f>IF($F42="","",$F42-$C42-$M42-$N42)</f>
         <v/>
       </c>
@@ -4567,23 +4595,23 @@
       <c r="I42" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J42" s="15">
+      <c r="J42" s="60">
         <f>$C42/$I42</f>
         <v/>
       </c>
-      <c r="K42" s="15">
+      <c r="K42" s="60">
         <f>IF($F42="","",$F42/$I42)</f>
         <v/>
       </c>
-      <c r="L42" s="15">
+      <c r="L42" s="60">
         <f>IF($G42="","",$G42/$I42)</f>
         <v/>
       </c>
-      <c r="M42" s="16">
+      <c r="M42" s="61">
         <f>IF($F42="","",$F42*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N42" s="15" t="n">
+      <c r="N42" s="60" t="n">
         <v>0</v>
       </c>
       <c r="O42" s="32" t="n"/>
@@ -4627,7 +4655,7 @@
       <c r="Y42" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="Z42" s="17">
+      <c r="Z42" s="62">
         <f>IF($G42="","",$G42/$Y42)</f>
         <v/>
       </c>
@@ -4642,23 +4670,23 @@
           <t>Pompe immergée ROBBY VP550W bleu et noir — occasion, NE MARCHE QU'EN MODE AUTO</t>
         </is>
       </c>
-      <c r="B43" s="14" t="n">
+      <c r="B43" s="59" t="n">
         <v>19.41</v>
       </c>
-      <c r="C43" s="15">
+      <c r="C43" s="60">
         <f>$B43</f>
         <v/>
       </c>
-      <c r="D43" s="16">
+      <c r="D43" s="61">
         <f>$C43/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E43" s="15">
+      <c r="E43" s="60">
         <f>CEILING($D43*Paramètres!$B$24,1)</f>
         <v/>
       </c>
       <c r="F43" s="32" t="n"/>
-      <c r="G43" s="17">
+      <c r="G43" s="62">
         <f>IF($F43="","",$F43-$C43-$M43-$N43)</f>
         <v/>
       </c>
@@ -4669,23 +4697,23 @@
       <c r="I43" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J43" s="15">
+      <c r="J43" s="60">
         <f>$C43/$I43</f>
         <v/>
       </c>
-      <c r="K43" s="15">
+      <c r="K43" s="60">
         <f>IF($F43="","",$F43/$I43)</f>
         <v/>
       </c>
-      <c r="L43" s="15">
+      <c r="L43" s="60">
         <f>IF($G43="","",$G43/$I43)</f>
         <v/>
       </c>
-      <c r="M43" s="16">
+      <c r="M43" s="61">
         <f>IF($F43="","",$F43*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N43" s="15" t="n">
+      <c r="N43" s="60" t="n">
         <v>0</v>
       </c>
       <c r="O43" s="32" t="n"/>
@@ -4729,7 +4757,7 @@
       <c r="Y43" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="Z43" s="17">
+      <c r="Z43" s="62">
         <f>IF($G43="","",$G43/$Y43)</f>
         <v/>
       </c>
@@ -4744,23 +4772,23 @@
           <t>Baskets NIKE Air Max Moto 2K P.44.5 — neuves</t>
         </is>
       </c>
-      <c r="B44" s="14" t="n">
+      <c r="B44" s="59" t="n">
         <v>50.4</v>
       </c>
-      <c r="C44" s="15">
+      <c r="C44" s="60">
         <f>$B44+$Y44*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D44" s="16">
+      <c r="D44" s="61">
         <f>$C44/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E44" s="15">
+      <c r="E44" s="60">
         <f>CEILING($D44*Paramètres!$B$24,1)</f>
         <v/>
       </c>
       <c r="F44" s="32" t="n"/>
-      <c r="G44" s="17">
+      <c r="G44" s="62">
         <f>IF($F44="","",$F44-$C44-$M44-$N44)</f>
         <v/>
       </c>
@@ -4771,29 +4799,29 @@
       <c r="I44" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J44" s="15">
+      <c r="J44" s="60">
         <f>$C44/$I44</f>
         <v/>
       </c>
-      <c r="K44" s="15">
+      <c r="K44" s="60">
         <f>IF($F44="","",$F44/$I44)</f>
         <v/>
       </c>
-      <c r="L44" s="15">
+      <c r="L44" s="60">
         <f>IF($G44="","",$G44/$I44)</f>
         <v/>
       </c>
-      <c r="M44" s="16">
+      <c r="M44" s="61">
         <f>IF($F44="","",$F44*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N44" s="15" t="n">
+      <c r="N44" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="O44" s="20" t="n">
+      <c r="O44" s="63" t="n">
         <v>40</v>
       </c>
-      <c r="P44" s="20" t="n">
+      <c r="P44" s="63" t="n">
         <v>10.4</v>
       </c>
       <c r="Q44" s="21" t="inlineStr">
@@ -4835,7 +4863,7 @@
       <c r="Y44" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="Z44" s="17">
+      <c r="Z44" s="62">
         <f>IF($G44="","",$G44/$Y44)</f>
         <v/>
       </c>
@@ -4850,23 +4878,23 @@
           <t>Baskets HOKA P.37 1/3 — neuves</t>
         </is>
       </c>
-      <c r="B45" s="14" t="n">
+      <c r="B45" s="59" t="n">
         <v>63</v>
       </c>
-      <c r="C45" s="15">
+      <c r="C45" s="60">
         <f>$B45+$Y45*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D45" s="16">
+      <c r="D45" s="61">
         <f>$C45/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E45" s="15">
+      <c r="E45" s="60">
         <f>CEILING($D45*Paramètres!$B$24,1)</f>
         <v/>
       </c>
       <c r="F45" s="32" t="n"/>
-      <c r="G45" s="17">
+      <c r="G45" s="62">
         <f>IF($F45="","",$F45-$C45-$M45-$N45)</f>
         <v/>
       </c>
@@ -4877,29 +4905,29 @@
       <c r="I45" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J45" s="15">
+      <c r="J45" s="60">
         <f>$C45/$I45</f>
         <v/>
       </c>
-      <c r="K45" s="15">
+      <c r="K45" s="60">
         <f>IF($F45="","",$F45/$I45)</f>
         <v/>
       </c>
-      <c r="L45" s="15">
+      <c r="L45" s="60">
         <f>IF($G45="","",$G45/$I45)</f>
         <v/>
       </c>
-      <c r="M45" s="16">
+      <c r="M45" s="61">
         <f>IF($F45="","",$F45*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N45" s="15" t="n">
+      <c r="N45" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="O45" s="20" t="n">
+      <c r="O45" s="63" t="n">
         <v>50</v>
       </c>
-      <c r="P45" s="20" t="n">
+      <c r="P45" s="63" t="n">
         <v>13</v>
       </c>
       <c r="Q45" s="21" t="inlineStr">
@@ -4941,7 +4969,7 @@
       <c r="Y45" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="Z45" s="17">
+      <c r="Z45" s="62">
         <f>IF($G45="","",$G45/$Y45)</f>
         <v/>
       </c>
@@ -4956,21 +4984,21 @@
           <t>TOTAL — 40 lots</t>
         </is>
       </c>
-      <c r="B46" s="34">
+      <c r="B46" s="69">
         <f>SUM(B6:B45)</f>
         <v/>
       </c>
-      <c r="C46" s="34">
+      <c r="C46" s="69">
         <f>SUM(C6:C45)</f>
         <v/>
       </c>
       <c r="D46" s="35" t="n"/>
       <c r="E46" s="35" t="n"/>
-      <c r="F46" s="34">
+      <c r="F46" s="69">
         <f>SUM(F6:F45)</f>
         <v/>
       </c>
-      <c r="G46" s="34">
+      <c r="G46" s="69">
         <f>SUM(G6:G45)</f>
         <v/>
       </c>
@@ -4978,18 +5006,18 @@
         <f>G46/C46</f>
         <v/>
       </c>
-      <c r="I46" s="37">
+      <c r="I46" s="70">
         <f>SUM(I6:I45)</f>
         <v/>
       </c>
       <c r="J46" s="35" t="n"/>
       <c r="K46" s="35" t="n"/>
       <c r="L46" s="35" t="n"/>
-      <c r="M46" s="34">
+      <c r="M46" s="69">
         <f>SUM(M6:M45)</f>
         <v/>
       </c>
-      <c r="N46" s="34">
+      <c r="N46" s="69">
         <f>SUM(N6:N45)</f>
         <v/>
       </c>
@@ -5004,7 +5032,7 @@
       <c r="W46" s="35" t="n"/>
       <c r="X46" s="35" t="n"/>
       <c r="Y46" s="35" t="n"/>
-      <c r="Z46" s="34">
+      <c r="Z46" s="69">
         <f>G46/SUM(Y6:Y45)</f>
         <v/>
       </c>
@@ -5063,7 +5091,7 @@
           <t>Marchandise ADN</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="55" t="n">
         <v>1637.35</v>
       </c>
     </row>
@@ -5073,7 +5101,7 @@
           <t>Livraison ADN</t>
         </is>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="55">
         <f>Paramètres!B11</f>
         <v/>
       </c>
@@ -5084,7 +5112,7 @@
           <t>Achats hors ADN (pompes, Pokémon)</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="55" t="n">
         <v>178.53</v>
       </c>
     </row>
@@ -5094,7 +5122,7 @@
           <t>TOTAL ENGAGÉ</t>
         </is>
       </c>
-      <c r="B7" s="34">
+      <c r="B7" s="69">
         <f>'Stock complet'!C46</f>
         <v/>
       </c>
@@ -5112,7 +5140,7 @@
           <t>Chiffre d'affaires attendu</t>
         </is>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="57">
         <f>'Stock complet'!F46</f>
         <v/>
       </c>
@@ -5128,7 +5156,7 @@
           <t>− URSSAF + CFP</t>
         </is>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="56">
         <f>-'Stock complet'!M46</f>
         <v/>
       </c>
@@ -5139,7 +5167,7 @@
           <t>− Commission carte</t>
         </is>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="55">
         <f>-'Stock complet'!N46</f>
         <v/>
       </c>
@@ -5149,7 +5177,7 @@
         <f> Marge brute</f>
         <v/>
       </c>
-      <c r="B13" s="34">
+      <c r="B13" s="69">
         <f>'Stock complet'!G46</f>
         <v/>
       </c>
@@ -5160,7 +5188,7 @@
           <t>− Emballage</t>
         </is>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="55">
         <f>-Paramètres!B20*Paramètres!B21</f>
         <v/>
       </c>
@@ -5171,7 +5199,7 @@
           <t>− Frais fixe carte</t>
         </is>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="55">
         <f>-Paramètres!B8*Paramètres!B21</f>
         <v/>
       </c>
@@ -5181,7 +5209,7 @@
         <f> Marge avant impôt</f>
         <v/>
       </c>
-      <c r="B16" s="34">
+      <c r="B16" s="69">
         <f>B13+B14+B15</f>
         <v/>
       </c>
@@ -5192,7 +5220,7 @@
           <t>Base imposable</t>
         </is>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="55">
         <f>B10*(1-Paramètres!B16)</f>
         <v/>
       </c>
@@ -5203,7 +5231,7 @@
           <t>− Impôt estimé</t>
         </is>
       </c>
-      <c r="B18" s="6">
+      <c r="B18" s="55">
         <f>-B17*Paramètres!B17</f>
         <v/>
       </c>
@@ -5213,7 +5241,7 @@
         <f> CE QUI RESTE</f>
         <v/>
       </c>
-      <c r="B19" s="41">
+      <c r="B19" s="71">
         <f>B16+B18</f>
         <v/>
       </c>
@@ -5231,7 +5259,7 @@
           <t>Marge nette / capital engagé</t>
         </is>
       </c>
-      <c r="B22" s="42">
+      <c r="B22" s="72">
         <f>B19/B7</f>
         <v/>
       </c>
@@ -5253,7 +5281,7 @@
           <t>Taux de marge nette sur le CA</t>
         </is>
       </c>
-      <c r="B24" s="42">
+      <c r="B24" s="72">
         <f>B19/B10</f>
         <v/>
       </c>
@@ -5276,7 +5304,7 @@
           <t>Shopify + Claude, aujourd'hui</t>
         </is>
       </c>
-      <c r="B27" s="6">
+      <c r="B27" s="55">
         <f>Paramètres!B30</f>
         <v/>
       </c>
@@ -5292,7 +5320,7 @@
           <t>Shopify + Claude, à partir du 11/11/2026</t>
         </is>
       </c>
-      <c r="B28" s="6">
+      <c r="B28" s="55">
         <f>Paramètres!B31</f>
         <v/>
       </c>
@@ -5308,7 +5336,7 @@
           <t>Soit par an, à partir de novembre</t>
         </is>
       </c>
-      <c r="B29" s="34">
+      <c r="B29" s="69">
         <f>Paramètres!B31*12</f>
         <v/>
       </c>
@@ -5319,7 +5347,7 @@
           <t>CA mensuel nécessaire pour les couvrir</t>
         </is>
       </c>
-      <c r="B30" s="41">
+      <c r="B30" s="71">
         <f>Paramètres!B31/B24</f>
         <v/>
       </c>
@@ -5335,7 +5363,7 @@
           <t>Marge du stock entier</t>
         </is>
       </c>
-      <c r="B31" s="6">
+      <c r="B31" s="55">
         <f>B19</f>
         <v/>
       </c>
@@ -5351,7 +5379,7 @@
           <t>Mois de charges couverts par tout le stock</t>
         </is>
       </c>
-      <c r="B32" s="44">
+      <c r="B32" s="73">
         <f>B19/Paramètres!B31</f>
         <v/>
       </c>
@@ -5479,7 +5507,7 @@
           <t>Cotisations URSSAF (achat-revente BIC)</t>
         </is>
       </c>
-      <c r="B5" s="46" t="n">
+      <c r="B5" s="74" t="n">
         <v>0.123</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -5494,7 +5522,7 @@
           <t>CFP — formation professionnelle</t>
         </is>
       </c>
-      <c r="B6" s="46" t="n">
+      <c r="B6" s="74" t="n">
         <v>0.001</v>
       </c>
     </row>
@@ -5504,7 +5532,7 @@
           <t>Commission carte Shopify Payments</t>
         </is>
       </c>
-      <c r="B7" s="46" t="n">
+      <c r="B7" s="74" t="n">
         <v>0.015</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -5519,7 +5547,7 @@
           <t>Frais fixe par transaction carte</t>
         </is>
       </c>
-      <c r="B8" s="47" t="n">
+      <c r="B8" s="75" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -5536,7 +5564,7 @@
           <t>Total des factures de livraison ADN</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="54" t="n">
         <v>127.8</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -5566,7 +5594,7 @@
           <t>Livraison par unité de vente</t>
         </is>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="55">
         <f>B11/B12</f>
         <v/>
       </c>
@@ -5589,7 +5617,7 @@
           <t>Abattement forfaitaire</t>
         </is>
       </c>
-      <c r="B16" s="46" t="n">
+      <c r="B16" s="74" t="n">
         <v>0.71</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -5604,7 +5632,7 @@
           <t>Tranche marginale du foyer</t>
         </is>
       </c>
-      <c r="B17" s="46" t="n">
+      <c r="B17" s="74" t="n">
         <v>0.11</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -5626,7 +5654,7 @@
           <t>Emballage par colis</t>
         </is>
       </c>
-      <c r="B20" s="47" t="n">
+      <c r="B20" s="75" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5675,7 +5703,7 @@
           <t>Abonnement Shopify — aujourd'hui</t>
         </is>
       </c>
-      <c r="B27" s="47" t="n">
+      <c r="B27" s="75" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -5690,7 +5718,7 @@
           <t>Abonnement Shopify — à partir du 11/11/2026</t>
         </is>
       </c>
-      <c r="B28" s="47" t="n">
+      <c r="B28" s="75" t="n">
         <v>36</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -5705,7 +5733,7 @@
           <t>Abonnement Claude</t>
         </is>
       </c>
-      <c r="B29" s="47" t="n">
+      <c r="B29" s="75" t="n">
         <v>22</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -5720,7 +5748,7 @@
           <t>Total mensuel aujourd'hui</t>
         </is>
       </c>
-      <c r="B30" s="50">
+      <c r="B30" s="76">
         <f>B27+B29</f>
         <v/>
       </c>
@@ -5731,7 +5759,7 @@
           <t>Total mensuel à partir du 11/11/2026</t>
         </is>
       </c>
-      <c r="B31" s="50">
+      <c r="B31" s="76">
         <f>B28+B29</f>
         <v/>
       </c>
@@ -5754,7 +5782,7 @@
           <t>CFE — cotisation foncière des entreprises</t>
         </is>
       </c>
-      <c r="B34" s="47" t="n">
+      <c r="B34" s="75" t="n">
         <v>0</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -5791,7 +5819,7 @@
           <t>Shopify Payments — frais fixe</t>
         </is>
       </c>
-      <c r="B38" s="47" t="n">
+      <c r="B38" s="75" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -5816,7 +5844,7 @@
           <t>PayPal — frais fixe</t>
         </is>
       </c>
-      <c r="B40" s="47" t="n">
+      <c r="B40" s="75" t="n">
         <v>0.35</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -5861,7 +5889,7 @@
           <t>Coefficient de marge — Shopify Payments</t>
         </is>
       </c>
-      <c r="B44" s="52">
+      <c r="B44" s="77">
         <f>1-B5-B6-B37</f>
         <v/>
       </c>
@@ -5877,7 +5905,7 @@
           <t>Coefficient de marge — PayPal</t>
         </is>
       </c>
-      <c r="B45" s="52">
+      <c r="B45" s="77">
         <f>1-B5-B6-B39</f>
         <v/>
       </c>
@@ -5893,7 +5921,7 @@
           <t>Coefficient de marge — hors carte</t>
         </is>
       </c>
-      <c r="B46" s="52">
+      <c r="B46" s="77">
         <f>1-B5-B6</f>
         <v/>
       </c>
@@ -5909,7 +5937,7 @@
           <t>Écart PayPal / Shopify Payments sur une vente à 89 €</t>
         </is>
       </c>
-      <c r="B47" s="6">
+      <c r="B47" s="55">
         <f>89*(B39-B37)+(B40-B38)</f>
         <v/>
       </c>
@@ -6042,16 +6070,16 @@
           <t>Lot de 12 paires de tongs HAVAIANAS fuchsia 35/36 — neuf</t>
         </is>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="G5" s="55" t="n">
         <v>80</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="H5" s="55" t="n">
         <v>20.8</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="I5" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="J5" s="55" t="n">
         <v>100.8</v>
       </c>
     </row>
@@ -6086,16 +6114,16 @@
           <t>Veste en jean ARMANI EXCHANGE T.S — neuve</t>
         </is>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="G6" s="55" t="n">
         <v>20</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="H6" s="55" t="n">
         <v>5.2</v>
       </c>
-      <c r="I6" s="6" t="n">
+      <c r="I6" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="J6" s="55" t="n">
         <v>25.2</v>
       </c>
     </row>
@@ -6130,16 +6158,16 @@
           <t>Lot de 4 gilets de flottaison MRS.ERTHA 3-6 ans — neuf</t>
         </is>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="G7" s="55" t="n">
         <v>30</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="H7" s="55" t="n">
         <v>7.8</v>
       </c>
-      <c r="I7" s="6" t="n">
+      <c r="I7" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="J7" s="55" t="n">
         <v>37.8</v>
       </c>
     </row>
@@ -6174,16 +6202,16 @@
           <t>Robe SANDRO T.40 — neuve</t>
         </is>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="G8" s="55" t="n">
         <v>30</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="H8" s="55" t="n">
         <v>7.8</v>
       </c>
-      <c r="I8" s="6" t="n">
+      <c r="I8" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="J8" s="55" t="n">
         <v>37.8</v>
       </c>
     </row>
@@ -6218,16 +6246,16 @@
           <t>Baskets HOKA P.37 1/3 — neuves</t>
         </is>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="G9" s="55" t="n">
         <v>50</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="H9" s="55" t="n">
         <v>13</v>
       </c>
-      <c r="I9" s="6" t="n">
+      <c r="I9" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="J9" s="55" t="n">
         <v>63</v>
       </c>
     </row>
@@ -6262,16 +6290,16 @@
           <t>Baskets NIKE Air Max Moto 2K P.44.5 — neuves</t>
         </is>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="G10" s="55" t="n">
         <v>40</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="H10" s="55" t="n">
         <v>10.4</v>
       </c>
-      <c r="I10" s="6" t="n">
+      <c r="I10" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="J10" s="55" t="n">
         <v>50.4</v>
       </c>
     </row>
@@ -6306,16 +6334,16 @@
           <t>Chaussures HOGAN P.36 — traces d'essayage</t>
         </is>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="G11" s="55" t="n">
         <v>10</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="H11" s="55" t="n">
         <v>2.6</v>
       </c>
-      <c r="I11" s="6" t="n">
+      <c r="I11" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="J11" s="55" t="n">
         <v>12.6</v>
       </c>
     </row>
@@ -6350,16 +6378,16 @@
           <t>NEW BALANCE G19064IK Alkaline Green P.38½ — neuves avec boîte</t>
         </is>
       </c>
-      <c r="G12" s="6" t="n">
+      <c r="G12" s="55" t="n">
         <v>60</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="H12" s="55" t="n">
         <v>15.6</v>
       </c>
-      <c r="I12" s="6" t="n">
+      <c r="I12" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="J12" s="55" t="n">
         <v>75.59999999999999</v>
       </c>
     </row>
@@ -6394,16 +6422,16 @@
           <t>Lot de 2 paires ADIDAS Predator Edge P.48 2/3 — neuves</t>
         </is>
       </c>
-      <c r="G13" s="6" t="n">
+      <c r="G13" s="55" t="n">
         <v>30</v>
       </c>
-      <c r="H13" s="6" t="n">
+      <c r="H13" s="55" t="n">
         <v>7.8</v>
       </c>
-      <c r="I13" s="6" t="n">
+      <c r="I13" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="6" t="n">
+      <c r="J13" s="55" t="n">
         <v>37.8</v>
       </c>
     </row>
@@ -6438,16 +6466,16 @@
           <t>Short BA&amp;SH Fegor T.34 — neuf</t>
         </is>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="G14" s="55" t="n">
         <v>40</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="H14" s="55" t="n">
         <v>10.4</v>
       </c>
-      <c r="I14" s="6" t="n">
+      <c r="I14" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J14" s="6" t="n">
+      <c r="J14" s="55" t="n">
         <v>50.4</v>
       </c>
     </row>
@@ -6482,16 +6510,16 @@
           <t>Jupe midi SONIA RYKIEL T.34 — neuve</t>
         </is>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="G15" s="55" t="n">
         <v>30</v>
       </c>
-      <c r="H15" s="6" t="n">
+      <c r="H15" s="55" t="n">
         <v>7.8</v>
       </c>
-      <c r="I15" s="6" t="n">
+      <c r="I15" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="J15" s="55" t="n">
         <v>37.8</v>
       </c>
     </row>
@@ -6526,16 +6554,16 @@
           <t>Sac demi-lune nylon noir KARL LAGERFELD JEANS — neuf avec étiquette</t>
         </is>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="G16" s="55" t="n">
         <v>40</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="H16" s="55" t="n">
         <v>10.4</v>
       </c>
-      <c r="I16" s="6" t="n">
+      <c r="I16" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="6" t="n">
+      <c r="J16" s="55" t="n">
         <v>50.4</v>
       </c>
     </row>
@@ -6570,16 +6598,16 @@
           <t>ADIDAS x STELLA McCARTNEY ASMC Ultraboost 21 P.36 — modèle d'exposition</t>
         </is>
       </c>
-      <c r="G17" s="6" t="n">
+      <c r="G17" s="55" t="n">
         <v>30</v>
       </c>
-      <c r="H17" s="6" t="n">
+      <c r="H17" s="55" t="n">
         <v>7.8</v>
       </c>
-      <c r="I17" s="6" t="n">
+      <c r="I17" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J17" s="6" t="n">
+      <c r="J17" s="55" t="n">
         <v>37.8</v>
       </c>
     </row>
@@ -6614,16 +6642,16 @@
           <t>Ballerines MASSIMO DUTTI P.41 — traces d'essayage</t>
         </is>
       </c>
-      <c r="G18" s="6" t="n">
+      <c r="G18" s="55" t="n">
         <v>20</v>
       </c>
-      <c r="H18" s="6" t="n">
+      <c r="H18" s="55" t="n">
         <v>5.2</v>
       </c>
-      <c r="I18" s="6" t="n">
+      <c r="I18" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J18" s="6" t="n">
+      <c r="J18" s="55" t="n">
         <v>25.2</v>
       </c>
     </row>
@@ -6658,16 +6686,16 @@
           <t>NEW BALANCE sneakers P.38 — neuves</t>
         </is>
       </c>
-      <c r="G19" s="6" t="n">
+      <c r="G19" s="55" t="n">
         <v>30</v>
       </c>
-      <c r="H19" s="6" t="n">
+      <c r="H19" s="55" t="n">
         <v>7.8</v>
       </c>
-      <c r="I19" s="6" t="n">
+      <c r="I19" s="55" t="n">
         <v>0.54</v>
       </c>
-      <c r="J19" s="6" t="n">
+      <c r="J19" s="55" t="n">
         <v>38.34</v>
       </c>
     </row>
@@ -6702,16 +6730,16 @@
           <t>LACOSTE sneakers P.42 — neuves</t>
         </is>
       </c>
-      <c r="G20" s="6" t="n">
+      <c r="G20" s="55" t="n">
         <v>45</v>
       </c>
-      <c r="H20" s="6" t="n">
+      <c r="H20" s="55" t="n">
         <v>11.7</v>
       </c>
-      <c r="I20" s="6" t="n">
+      <c r="I20" s="55" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="J20" s="6" t="n">
+      <c r="J20" s="55" t="n">
         <v>57.51</v>
       </c>
     </row>
@@ -6746,16 +6774,16 @@
           <t>EMPORIO ARMANI baskets P.36 — neuves</t>
         </is>
       </c>
-      <c r="G21" s="6" t="n">
+      <c r="G21" s="55" t="n">
         <v>40</v>
       </c>
-      <c r="H21" s="6" t="n">
+      <c r="H21" s="55" t="n">
         <v>10.4</v>
       </c>
-      <c r="I21" s="6" t="n">
+      <c r="I21" s="55" t="n">
         <v>0.72</v>
       </c>
-      <c r="J21" s="6" t="n">
+      <c r="J21" s="55" t="n">
         <v>51.12</v>
       </c>
     </row>
@@ -6790,16 +6818,16 @@
           <t>GEOX baskets P.35 — neuves</t>
         </is>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="G22" s="55" t="n">
         <v>17</v>
       </c>
-      <c r="H22" s="6" t="n">
+      <c r="H22" s="55" t="n">
         <v>4.42</v>
       </c>
-      <c r="I22" s="6" t="n">
+      <c r="I22" s="55" t="n">
         <v>0.31</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="J22" s="55" t="n">
         <v>21.73</v>
       </c>
     </row>
@@ -6834,16 +6862,16 @@
           <t>NEW BALANCE baskets montantes P.44 — neuves</t>
         </is>
       </c>
-      <c r="G23" s="6" t="n">
+      <c r="G23" s="55" t="n">
         <v>40</v>
       </c>
-      <c r="H23" s="6" t="n">
+      <c r="H23" s="55" t="n">
         <v>10.4</v>
       </c>
-      <c r="I23" s="6" t="n">
+      <c r="I23" s="55" t="n">
         <v>0.72</v>
       </c>
-      <c r="J23" s="6" t="n">
+      <c r="J23" s="55" t="n">
         <v>51.12</v>
       </c>
     </row>
@@ -6878,16 +6906,16 @@
           <t>TOMMY JEANS baskets basses P.40 — neuves</t>
         </is>
       </c>
-      <c r="G24" s="6" t="n">
+      <c r="G24" s="55" t="n">
         <v>41</v>
       </c>
-      <c r="H24" s="6" t="n">
+      <c r="H24" s="55" t="n">
         <v>10.66</v>
       </c>
-      <c r="I24" s="6" t="n">
+      <c r="I24" s="55" t="n">
         <v>0.74</v>
       </c>
-      <c r="J24" s="6" t="n">
+      <c r="J24" s="55" t="n">
         <v>52.4</v>
       </c>
     </row>
@@ -6922,16 +6950,16 @@
           <t>PHILIPP PLEIN SPORT baskets montantes P.40 — neuves</t>
         </is>
       </c>
-      <c r="G25" s="6" t="n">
+      <c r="G25" s="55" t="n">
         <v>45</v>
       </c>
-      <c r="H25" s="6" t="n">
+      <c r="H25" s="55" t="n">
         <v>11.7</v>
       </c>
-      <c r="I25" s="6" t="n">
+      <c r="I25" s="55" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="J25" s="6" t="n">
+      <c r="J25" s="55" t="n">
         <v>57.51</v>
       </c>
     </row>
@@ -6966,16 +6994,16 @@
           <t>PIER ANTONIO GASPARI robe droite bleu marine T.42 — neuve</t>
         </is>
       </c>
-      <c r="G26" s="6" t="n">
+      <c r="G26" s="55" t="n">
         <v>20</v>
       </c>
-      <c r="H26" s="6" t="n">
+      <c r="H26" s="55" t="n">
         <v>5.2</v>
       </c>
-      <c r="I26" s="6" t="n">
+      <c r="I26" s="55" t="n">
         <v>0.36</v>
       </c>
-      <c r="J26" s="6" t="n">
+      <c r="J26" s="55" t="n">
         <v>25.56</v>
       </c>
     </row>
@@ -7010,16 +7038,16 @@
           <t>ELISABETTA FRANCHI robe asymétrique viscose T.46 IT — neuve</t>
         </is>
       </c>
-      <c r="G27" s="6" t="n">
+      <c r="G27" s="55" t="n">
         <v>16</v>
       </c>
-      <c r="H27" s="6" t="n">
+      <c r="H27" s="55" t="n">
         <v>4.16</v>
       </c>
-      <c r="I27" s="6" t="n">
+      <c r="I27" s="55" t="n">
         <v>0.29</v>
       </c>
-      <c r="J27" s="6" t="n">
+      <c r="J27" s="55" t="n">
         <v>20.45</v>
       </c>
     </row>
@@ -7054,16 +7082,16 @@
           <t>CHIARA FERRAGNI robe bustier courte T.M — neuve</t>
         </is>
       </c>
-      <c r="G28" s="6" t="n">
+      <c r="G28" s="55" t="n">
         <v>25</v>
       </c>
-      <c r="H28" s="6" t="n">
+      <c r="H28" s="55" t="n">
         <v>6.5</v>
       </c>
-      <c r="I28" s="6" t="n">
+      <c r="I28" s="55" t="n">
         <v>0.45</v>
       </c>
-      <c r="J28" s="6" t="n">
+      <c r="J28" s="55" t="n">
         <v>31.95</v>
       </c>
     </row>
@@ -7098,16 +7126,16 @@
           <t>SALOMON X Ultra 5 Mid GTX P.44 — neuves</t>
         </is>
       </c>
-      <c r="G29" s="6" t="n">
+      <c r="G29" s="55" t="n">
         <v>60</v>
       </c>
-      <c r="H29" s="6" t="n">
+      <c r="H29" s="55" t="n">
         <v>15.6</v>
       </c>
-      <c r="I29" s="6" t="n">
+      <c r="I29" s="55" t="n">
         <v>1.08</v>
       </c>
-      <c r="J29" s="6" t="n">
+      <c r="J29" s="55" t="n">
         <v>76.68000000000001</v>
       </c>
     </row>
@@ -7142,16 +7170,16 @@
           <t>Lot de 4 toupies BEYBLADE HASBRO</t>
         </is>
       </c>
-      <c r="G30" s="6" t="n">
+      <c r="G30" s="55" t="n">
         <v>15</v>
       </c>
-      <c r="H30" s="6" t="n">
+      <c r="H30" s="55" t="n">
         <v>3.9</v>
       </c>
-      <c r="I30" s="6" t="n">
+      <c r="I30" s="55" t="n">
         <v>0.27</v>
       </c>
-      <c r="J30" s="6" t="n">
+      <c r="J30" s="55" t="n">
         <v>19.17</v>
       </c>
     </row>
@@ -7186,16 +7214,16 @@
           <t>Lot de 4 toupies BEYBLADE HASBRO</t>
         </is>
       </c>
-      <c r="G31" s="6" t="n">
+      <c r="G31" s="55" t="n">
         <v>30</v>
       </c>
-      <c r="H31" s="6" t="n">
+      <c r="H31" s="55" t="n">
         <v>7.8</v>
       </c>
-      <c r="I31" s="6" t="n">
+      <c r="I31" s="55" t="n">
         <v>0.54</v>
       </c>
-      <c r="J31" s="6" t="n">
+      <c r="J31" s="55" t="n">
         <v>38.34</v>
       </c>
     </row>
@@ -7230,16 +7258,16 @@
           <t>T-shirt BALENCIAGA T.2 — neuf</t>
         </is>
       </c>
-      <c r="G32" s="6" t="n">
+      <c r="G32" s="55" t="n">
         <v>90</v>
       </c>
-      <c r="H32" s="6" t="n">
+      <c r="H32" s="55" t="n">
         <v>23.4</v>
       </c>
-      <c r="I32" s="6" t="n">
+      <c r="I32" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J32" s="6" t="n">
+      <c r="J32" s="55" t="n">
         <v>113.4</v>
       </c>
     </row>
@@ -7274,16 +7302,16 @@
           <t>Blazer noir KARL LAGERFELD T.36 FR — neuf avec étiquette</t>
         </is>
       </c>
-      <c r="G33" s="6" t="n">
+      <c r="G33" s="55" t="n">
         <v>40</v>
       </c>
-      <c r="H33" s="6" t="n">
+      <c r="H33" s="55" t="n">
         <v>10.4</v>
       </c>
-      <c r="I33" s="6" t="n">
+      <c r="I33" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J33" s="6" t="n">
+      <c r="J33" s="55" t="n">
         <v>50.4</v>
       </c>
     </row>
@@ -7318,16 +7346,16 @@
           <t>ADIDAS Yeezy 700 V3 Mono Safflower T.38 — occasion</t>
         </is>
       </c>
-      <c r="G34" s="6" t="n">
+      <c r="G34" s="55" t="n">
         <v>50</v>
       </c>
-      <c r="H34" s="6" t="n">
+      <c r="H34" s="55" t="n">
         <v>13</v>
       </c>
-      <c r="I34" s="6" t="n">
+      <c r="I34" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J34" s="6" t="n">
+      <c r="J34" s="55" t="n">
         <v>63</v>
       </c>
     </row>
@@ -7362,16 +7390,16 @@
           <t>Lot de 6 vêtements femme MORGAN T.40 et L — neuf</t>
         </is>
       </c>
-      <c r="G35" s="6" t="n">
+      <c r="G35" s="55" t="n">
         <v>30</v>
       </c>
-      <c r="H35" s="6" t="n">
+      <c r="H35" s="55" t="n">
         <v>7.8</v>
       </c>
-      <c r="I35" s="6" t="n">
+      <c r="I35" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J35" s="6" t="n">
+      <c r="J35" s="55" t="n">
         <v>37.8</v>
       </c>
     </row>
@@ -7406,16 +7434,16 @@
           <t>Demi-bottes FORMA Legacy Waterproof T.45 noir — neuves</t>
         </is>
       </c>
-      <c r="G36" s="6" t="n">
+      <c r="G36" s="55" t="n">
         <v>50</v>
       </c>
-      <c r="H36" s="6" t="n">
+      <c r="H36" s="55" t="n">
         <v>13</v>
       </c>
-      <c r="I36" s="6" t="n">
+      <c r="I36" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J36" s="6" t="n">
+      <c r="J36" s="55" t="n">
         <v>63</v>
       </c>
     </row>
@@ -7450,16 +7478,16 @@
           <t>Combinaison de pluie BMW Overall ProRain unisexe XL — neuve</t>
         </is>
       </c>
-      <c r="G37" s="6" t="n">
+      <c r="G37" s="55" t="n">
         <v>60</v>
       </c>
-      <c r="H37" s="6" t="n">
+      <c r="H37" s="55" t="n">
         <v>8.57</v>
       </c>
-      <c r="I37" s="6" t="n">
+      <c r="I37" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J37" s="6" t="n">
+      <c r="J37" s="55" t="n">
         <v>68.56999999999999</v>
       </c>
     </row>
@@ -7494,16 +7522,16 @@
           <t>Lot de 20 paires de sandales et tongs RELIFE / TOMMY JEANS — neuf</t>
         </is>
       </c>
-      <c r="G38" s="6" t="n">
+      <c r="G38" s="55" t="n">
         <v>45</v>
       </c>
-      <c r="H38" s="6" t="n">
+      <c r="H38" s="55" t="n">
         <v>11.7</v>
       </c>
-      <c r="I38" s="6" t="n">
+      <c r="I38" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J38" s="6" t="n">
+      <c r="J38" s="55" t="n">
         <v>56.7</v>
       </c>
     </row>
@@ -7518,19 +7546,19 @@
           <t>TOTAL MARCHANDISE</t>
         </is>
       </c>
-      <c r="G39" s="34">
+      <c r="G39" s="69">
         <f>SUM(G5:G38)</f>
         <v/>
       </c>
-      <c r="H39" s="34">
+      <c r="H39" s="69">
         <f>SUM(H5:H38)</f>
         <v/>
       </c>
-      <c r="I39" s="34">
+      <c r="I39" s="69">
         <f>SUM(I5:I38)</f>
         <v/>
       </c>
-      <c r="J39" s="34">
+      <c r="J39" s="69">
         <f>SUM(J5:J38)</f>
         <v/>
       </c>
@@ -7600,7 +7628,7 @@
           <t>Colissimo Point Relais — assurance et signature</t>
         </is>
       </c>
-      <c r="F43" s="6" t="n">
+      <c r="F43" s="55" t="n">
         <v>19.9</v>
       </c>
     </row>
@@ -7630,7 +7658,7 @@
           <t>Colissimo Point Relais — assurance et signature</t>
         </is>
       </c>
-      <c r="F44" s="6" t="n">
+      <c r="F44" s="55" t="n">
         <v>18.22</v>
       </c>
     </row>
@@ -7660,7 +7688,7 @@
           <t>Colissimo Point Relais — assurance et signature</t>
         </is>
       </c>
-      <c r="F45" s="6" t="n">
+      <c r="F45" s="55" t="n">
         <v>29.94</v>
       </c>
     </row>
@@ -7690,7 +7718,7 @@
           <t>Colissimo Point Relais</t>
         </is>
       </c>
-      <c r="F46" s="6" t="n">
+      <c r="F46" s="55" t="n">
         <v>15.72</v>
       </c>
     </row>
@@ -7720,7 +7748,7 @@
           <t>Colissimo Point Relais — assurance et signature</t>
         </is>
       </c>
-      <c r="F47" s="6" t="n">
+      <c r="F47" s="55" t="n">
         <v>44.02</v>
       </c>
     </row>
@@ -7734,7 +7762,7 @@
           <t>TOTAL LIVRAISON</t>
         </is>
       </c>
-      <c r="F48" s="34">
+      <c r="F48" s="69">
         <f>SUM(F43:F47)</f>
         <v/>
       </c>

--- a/exports/maison-nsaia-stock.xlsx
+++ b/exports/maison-nsaia-stock.xlsx
@@ -2882,7 +2882,7 @@
       </c>
       <c r="X25" s="13" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>17/10/2026</t>
         </is>
       </c>
       <c r="Y25" s="13" t="n">

--- a/exports/maison-nsaia-stock.xlsx
+++ b/exports/maison-nsaia-stock.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Stock complet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Synthèse" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Paramètres" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Factures" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stock complet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Synthèse" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paramètres" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Factures" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stock complet'!$A$5:$AA$45</definedName>
@@ -22,11 +22,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00 &quot;€&quot;"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
-    <numFmt numFmtId="167" formatCode="#,##0 &quot;art.&quot;"/>
-    <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00 &quot;€&quot;"/>
+    <numFmt numFmtId="165" formatCode="#,##0 &quot;art.&quot;"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="168" formatCode="0.000"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -142,7 +142,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -150,57 +150,81 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="9" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -778,25 +802,25 @@
           <t>Lot de 20 paires de sandales et tongs RELIFE / TOMMY JEANS — neuf</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="54" t="n">
         <v>56.7</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="55">
         <f>$B6+$Y6*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="56">
         <f>$C6/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="55">
         <f>CEILING($D6*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F6" s="8" t="n">
+      <c r="F6" s="57" t="n">
         <v>199</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="57">
         <f>IF($F6="","",$F6-$C6-$M6-$N6)</f>
         <v/>
       </c>
@@ -807,29 +831,29 @@
       <c r="I6" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="55">
         <f>$C6/$I6</f>
         <v/>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="55">
         <f>IF($F6="","",$F6/$I6)</f>
         <v/>
       </c>
-      <c r="L6" s="6">
+      <c r="L6" s="55">
         <f>IF($G6="","",$G6/$I6)</f>
         <v/>
       </c>
-      <c r="M6" s="7">
+      <c r="M6" s="56">
         <f>IF($F6="","",$F6*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N6" s="6" t="n">
+      <c r="N6" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O6" s="11" t="n">
+      <c r="O6" s="58" t="n">
         <v>45</v>
       </c>
-      <c r="P6" s="11" t="n">
+      <c r="P6" s="58" t="n">
         <v>11.7</v>
       </c>
       <c r="Q6" s="12" t="inlineStr">
@@ -867,7 +891,7 @@
       <c r="Y6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z6" s="8">
+      <c r="Z6" s="57">
         <f>IF($G6="","",$G6/$Y6)</f>
         <v/>
       </c>
@@ -882,25 +906,25 @@
           <t>Lot de 2 paires ADIDAS Predator Edge P.48 2/3 — neuves</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="54" t="n">
         <v>37.8</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="55">
         <f>$B7+$Y7*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="56">
         <f>$C7/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="55">
         <f>CEILING($D7*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F7" s="8" t="n">
+      <c r="F7" s="57" t="n">
         <v>178</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="57">
         <f>IF($F7="","",$F7-$C7-$M7-$N7)</f>
         <v/>
       </c>
@@ -911,29 +935,29 @@
       <c r="I7" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="J7" s="6">
+      <c r="J7" s="55">
         <f>$C7/$I7</f>
         <v/>
       </c>
-      <c r="K7" s="6">
+      <c r="K7" s="55">
         <f>IF($F7="","",$F7/$I7)</f>
         <v/>
       </c>
-      <c r="L7" s="6">
+      <c r="L7" s="55">
         <f>IF($G7="","",$G7/$I7)</f>
         <v/>
       </c>
-      <c r="M7" s="7">
+      <c r="M7" s="56">
         <f>IF($F7="","",$F7*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N7" s="6" t="n">
+      <c r="N7" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O7" s="11" t="n">
+      <c r="O7" s="58" t="n">
         <v>30</v>
       </c>
-      <c r="P7" s="11" t="n">
+      <c r="P7" s="58" t="n">
         <v>7.8</v>
       </c>
       <c r="Q7" s="12" t="inlineStr">
@@ -971,7 +995,7 @@
       <c r="Y7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="Z7" s="8">
+      <c r="Z7" s="57">
         <f>IF($G7="","",$G7/$Y7)</f>
         <v/>
       </c>
@@ -986,25 +1010,25 @@
           <t>Demi-bottes FORMA Legacy Waterproof T.45 noir — neuves</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="54" t="n">
         <v>63</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="55">
         <f>$B8+$Y8*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="56">
         <f>$C8/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="55">
         <f>CEILING($D8*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F8" s="8" t="n">
+      <c r="F8" s="57" t="n">
         <v>159</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="57">
         <f>IF($F8="","",$F8-$C8-$M8-$N8)</f>
         <v/>
       </c>
@@ -1015,30 +1039,30 @@
       <c r="I8" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J8" s="6">
+      <c r="J8" s="55">
         <f>$C8/$I8</f>
         <v/>
       </c>
-      <c r="K8" s="6">
+      <c r="K8" s="55">
         <f>IF($F8="","",$F8/$I8)</f>
         <v/>
       </c>
-      <c r="L8" s="6">
+      <c r="L8" s="55">
         <f>IF($G8="","",$G8/$I8)</f>
         <v/>
       </c>
-      <c r="M8" s="7">
+      <c r="M8" s="56">
         <f>IF($F8="","",$F8*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N8" s="6">
+      <c r="N8" s="55">
         <f>IF($F8="","",$F8*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="O8" s="11" t="n">
+      <c r="O8" s="58" t="n">
         <v>50</v>
       </c>
-      <c r="P8" s="11" t="n">
+      <c r="P8" s="58" t="n">
         <v>13</v>
       </c>
       <c r="Q8" s="12" t="inlineStr">
@@ -1076,7 +1100,7 @@
       <c r="Y8" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z8" s="8">
+      <c r="Z8" s="57">
         <f>IF($G8="","",$G8/$Y8)</f>
         <v/>
       </c>
@@ -1091,25 +1115,25 @@
           <t>Lot de 4 gilets de flottaison MRS.ERTHA 3-6 ans — neuf</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="54" t="n">
         <v>37.8</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="55">
         <f>$B9+$Y9*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="56">
         <f>$C9/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="55">
         <f>CEILING($D9*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F9" s="8" t="n">
+      <c r="F9" s="57" t="n">
         <v>136</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="57">
         <f>IF($F9="","",$F9-$C9-$M9-$N9)</f>
         <v/>
       </c>
@@ -1120,29 +1144,29 @@
       <c r="I9" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="J9" s="6">
+      <c r="J9" s="55">
         <f>$C9/$I9</f>
         <v/>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="55">
         <f>IF($F9="","",$F9/$I9)</f>
         <v/>
       </c>
-      <c r="L9" s="6">
+      <c r="L9" s="55">
         <f>IF($G9="","",$G9/$I9)</f>
         <v/>
       </c>
-      <c r="M9" s="7">
+      <c r="M9" s="56">
         <f>IF($F9="","",$F9*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N9" s="6" t="n">
+      <c r="N9" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O9" s="11" t="n">
+      <c r="O9" s="58" t="n">
         <v>30</v>
       </c>
-      <c r="P9" s="11" t="n">
+      <c r="P9" s="58" t="n">
         <v>7.8</v>
       </c>
       <c r="Q9" s="12" t="inlineStr">
@@ -1180,7 +1204,7 @@
       <c r="Y9" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="Z9" s="8">
+      <c r="Z9" s="57">
         <f>IF($G9="","",$G9/$Y9)</f>
         <v/>
       </c>
@@ -1195,25 +1219,25 @@
           <t>Lot de 12 paires de tongs HAVAIANAS fuchsia 35/36 — neuf</t>
         </is>
       </c>
-      <c r="B10" s="14" t="n">
+      <c r="B10" s="59" t="n">
         <v>100.8</v>
       </c>
-      <c r="C10" s="15">
+      <c r="C10" s="60">
         <f>$B10+$Y10*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D10" s="16">
+      <c r="D10" s="61">
         <f>$C10/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E10" s="15">
+      <c r="E10" s="60">
         <f>CEILING($D10*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F10" s="17" t="n">
+      <c r="F10" s="62" t="n">
         <v>208</v>
       </c>
-      <c r="G10" s="17">
+      <c r="G10" s="62">
         <f>IF($F10="","",$F10-$C10-$M10-$N10)</f>
         <v/>
       </c>
@@ -1224,29 +1248,29 @@
       <c r="I10" s="19" t="n">
         <v>12</v>
       </c>
-      <c r="J10" s="15">
+      <c r="J10" s="60">
         <f>$C10/$I10</f>
         <v/>
       </c>
-      <c r="K10" s="15">
+      <c r="K10" s="60">
         <f>IF($F10="","",$F10/$I10)</f>
         <v/>
       </c>
-      <c r="L10" s="15">
+      <c r="L10" s="60">
         <f>IF($G10="","",$G10/$I10)</f>
         <v/>
       </c>
-      <c r="M10" s="16">
+      <c r="M10" s="61">
         <f>IF($F10="","",$F10*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N10" s="15" t="n">
+      <c r="N10" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="O10" s="20" t="n">
+      <c r="O10" s="63" t="n">
         <v>80</v>
       </c>
-      <c r="P10" s="20" t="n">
+      <c r="P10" s="63" t="n">
         <v>20.8</v>
       </c>
       <c r="Q10" s="21" t="inlineStr">
@@ -1277,18 +1301,18 @@
       <c r="V10" s="13" t="inlineStr"/>
       <c r="W10" s="13" t="inlineStr">
         <is>
-          <t>URGENT — 10 restent, monter à 18 €</t>
+          <t>URGENT — 9 restent, monter à 18 €</t>
         </is>
       </c>
       <c r="X10" s="13" t="inlineStr">
         <is>
-          <t>2 vendues à 14 € le 10/08</t>
+          <t>2 vendues à 14 € le 10/08 · 1 vendue à 15 € (encaissée le 10/09)</t>
         </is>
       </c>
       <c r="Y10" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" s="17">
+      <c r="Z10" s="62">
         <f>IF($G10="","",$G10/$Y10)</f>
         <v/>
       </c>
@@ -1303,25 +1327,25 @@
           <t>ELISABETTA FRANCHI robe asymétrique viscose T.46 IT — neuve</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="54" t="n">
         <v>20.45</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="55">
         <f>$B11+$Y11*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="56">
         <f>$C11/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="55">
         <f>CEILING($D11*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F11" s="8" t="n">
+      <c r="F11" s="57" t="n">
         <v>99</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="57">
         <f>IF($F11="","",$F11-$C11-$M11-$N11)</f>
         <v/>
       </c>
@@ -1332,30 +1356,30 @@
       <c r="I11" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J11" s="6">
+      <c r="J11" s="55">
         <f>$C11/$I11</f>
         <v/>
       </c>
-      <c r="K11" s="6">
+      <c r="K11" s="55">
         <f>IF($F11="","",$F11/$I11)</f>
         <v/>
       </c>
-      <c r="L11" s="6">
+      <c r="L11" s="55">
         <f>IF($G11="","",$G11/$I11)</f>
         <v/>
       </c>
-      <c r="M11" s="7">
+      <c r="M11" s="56">
         <f>IF($F11="","",$F11*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N11" s="6">
+      <c r="N11" s="55">
         <f>IF($F11="","",$F11*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="O11" s="11" t="n">
+      <c r="O11" s="58" t="n">
         <v>16</v>
       </c>
-      <c r="P11" s="11" t="n">
+      <c r="P11" s="58" t="n">
         <v>4.16</v>
       </c>
       <c r="Q11" s="12" t="inlineStr">
@@ -1393,7 +1417,7 @@
       <c r="Y11" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z11" s="8">
+      <c r="Z11" s="57">
         <f>IF($G11="","",$G11/$Y11)</f>
         <v/>
       </c>
@@ -1408,25 +1432,25 @@
           <t>Combinaison de pluie BMW Overall ProRain unisexe XL — neuve</t>
         </is>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="54" t="n">
         <v>68.56999999999999</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="55">
         <f>$B12+$Y12*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="56">
         <f>$C12/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="55">
         <f>CEILING($D12*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F12" s="8" t="n">
+      <c r="F12" s="57" t="n">
         <v>139</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G12" s="57">
         <f>IF($F12="","",$F12-$C12-$M12-$N12)</f>
         <v/>
       </c>
@@ -1437,29 +1461,29 @@
       <c r="I12" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J12" s="6">
+      <c r="J12" s="55">
         <f>$C12/$I12</f>
         <v/>
       </c>
-      <c r="K12" s="6">
+      <c r="K12" s="55">
         <f>IF($F12="","",$F12/$I12)</f>
         <v/>
       </c>
-      <c r="L12" s="6">
+      <c r="L12" s="55">
         <f>IF($G12="","",$G12/$I12)</f>
         <v/>
       </c>
-      <c r="M12" s="7">
+      <c r="M12" s="56">
         <f>IF($F12="","",$F12*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N12" s="6" t="n">
+      <c r="N12" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O12" s="11" t="n">
+      <c r="O12" s="58" t="n">
         <v>60</v>
       </c>
-      <c r="P12" s="11" t="n">
+      <c r="P12" s="58" t="n">
         <v>8.57</v>
       </c>
       <c r="Q12" s="12" t="inlineStr">
@@ -1497,7 +1521,7 @@
       <c r="Y12" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z12" s="8">
+      <c r="Z12" s="57">
         <f>IF($G12="","",$G12/$Y12)</f>
         <v/>
       </c>
@@ -1512,25 +1536,25 @@
           <t>Chaussures HOGAN P.36 — traces d'essayage</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="54" t="n">
         <v>12.6</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="55">
         <f>$B13+$Y13*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="56">
         <f>$C13/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="55">
         <f>CEILING($D13*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F13" s="8" t="n">
+      <c r="F13" s="57" t="n">
         <v>79</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G13" s="57">
         <f>IF($F13="","",$F13-$C13-$M13-$N13)</f>
         <v/>
       </c>
@@ -1541,30 +1565,30 @@
       <c r="I13" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J13" s="6">
+      <c r="J13" s="55">
         <f>$C13/$I13</f>
         <v/>
       </c>
-      <c r="K13" s="6">
+      <c r="K13" s="55">
         <f>IF($F13="","",$F13/$I13)</f>
         <v/>
       </c>
-      <c r="L13" s="6">
+      <c r="L13" s="55">
         <f>IF($G13="","",$G13/$I13)</f>
         <v/>
       </c>
-      <c r="M13" s="7">
+      <c r="M13" s="56">
         <f>IF($F13="","",$F13*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N13" s="6">
+      <c r="N13" s="55">
         <f>IF($F13="","",$F13*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="O13" s="11" t="n">
+      <c r="O13" s="58" t="n">
         <v>10</v>
       </c>
-      <c r="P13" s="11" t="n">
+      <c r="P13" s="58" t="n">
         <v>2.6</v>
       </c>
       <c r="Q13" s="12" t="inlineStr">
@@ -1602,7 +1626,7 @@
       <c r="Y13" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z13" s="8">
+      <c r="Z13" s="57">
         <f>IF($G13="","",$G13/$Y13)</f>
         <v/>
       </c>
@@ -1617,25 +1641,25 @@
           <t>Jupe midi SONIA RYKIEL T.34 — neuve</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B14" s="54" t="n">
         <v>37.8</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="55">
         <f>$B14+$Y14*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="56">
         <f>$C14/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="55">
         <f>CEILING($D14*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F14" s="8" t="n">
+      <c r="F14" s="57" t="n">
         <v>99</v>
       </c>
-      <c r="G14" s="8">
+      <c r="G14" s="57">
         <f>IF($F14="","",$F14-$C14-$M14-$N14)</f>
         <v/>
       </c>
@@ -1646,30 +1670,30 @@
       <c r="I14" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J14" s="6">
+      <c r="J14" s="55">
         <f>$C14/$I14</f>
         <v/>
       </c>
-      <c r="K14" s="6">
+      <c r="K14" s="55">
         <f>IF($F14="","",$F14/$I14)</f>
         <v/>
       </c>
-      <c r="L14" s="6">
+      <c r="L14" s="55">
         <f>IF($G14="","",$G14/$I14)</f>
         <v/>
       </c>
-      <c r="M14" s="7">
+      <c r="M14" s="56">
         <f>IF($F14="","",$F14*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N14" s="6">
+      <c r="N14" s="55">
         <f>IF($F14="","",$F14*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="O14" s="11" t="n">
+      <c r="O14" s="58" t="n">
         <v>30</v>
       </c>
-      <c r="P14" s="11" t="n">
+      <c r="P14" s="58" t="n">
         <v>7.8</v>
       </c>
       <c r="Q14" s="12" t="inlineStr">
@@ -1707,7 +1731,7 @@
       <c r="Y14" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z14" s="8">
+      <c r="Z14" s="57">
         <f>IF($G14="","",$G14/$Y14)</f>
         <v/>
       </c>
@@ -1722,25 +1746,25 @@
           <t>Robe SANDRO T.40 — neuve</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="54" t="n">
         <v>37.8</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="55">
         <f>$B15+$Y15*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="56">
         <f>$C15/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="55">
         <f>CEILING($D15*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F15" s="8" t="n">
+      <c r="F15" s="57" t="n">
         <v>89</v>
       </c>
-      <c r="G15" s="8">
+      <c r="G15" s="57">
         <f>IF($F15="","",$F15-$C15-$M15-$N15)</f>
         <v/>
       </c>
@@ -1751,30 +1775,30 @@
       <c r="I15" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J15" s="6">
+      <c r="J15" s="55">
         <f>$C15/$I15</f>
         <v/>
       </c>
-      <c r="K15" s="6">
+      <c r="K15" s="55">
         <f>IF($F15="","",$F15/$I15)</f>
         <v/>
       </c>
-      <c r="L15" s="6">
+      <c r="L15" s="55">
         <f>IF($G15="","",$G15/$I15)</f>
         <v/>
       </c>
-      <c r="M15" s="7">
+      <c r="M15" s="56">
         <f>IF($F15="","",$F15*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N15" s="6">
+      <c r="N15" s="55">
         <f>IF($F15="","",$F15*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="O15" s="11" t="n">
+      <c r="O15" s="58" t="n">
         <v>30</v>
       </c>
-      <c r="P15" s="11" t="n">
+      <c r="P15" s="58" t="n">
         <v>7.8</v>
       </c>
       <c r="Q15" s="12" t="inlineStr">
@@ -1812,7 +1836,7 @@
       <c r="Y15" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z15" s="8">
+      <c r="Z15" s="57">
         <f>IF($G15="","",$G15/$Y15)</f>
         <v/>
       </c>
@@ -1827,25 +1851,25 @@
           <t>Lot de 6 vêtements femme MORGAN T.40 et L — neuf</t>
         </is>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B16" s="54" t="n">
         <v>37.8</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="55">
         <f>$B16+$Y16*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="56">
         <f>$C16/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E16" s="6">
+      <c r="E16" s="55">
         <f>CEILING($D16*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F16" s="8" t="n">
+      <c r="F16" s="57" t="n">
         <v>98</v>
       </c>
-      <c r="G16" s="8">
+      <c r="G16" s="57">
         <f>IF($F16="","",$F16-$C16-$M16-$N16)</f>
         <v/>
       </c>
@@ -1856,29 +1880,29 @@
       <c r="I16" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="J16" s="6">
+      <c r="J16" s="55">
         <f>$C16/$I16</f>
         <v/>
       </c>
-      <c r="K16" s="6">
+      <c r="K16" s="55">
         <f>IF($F16="","",$F16/$I16)</f>
         <v/>
       </c>
-      <c r="L16" s="6">
+      <c r="L16" s="55">
         <f>IF($G16="","",$G16/$I16)</f>
         <v/>
       </c>
-      <c r="M16" s="7">
+      <c r="M16" s="56">
         <f>IF($F16="","",$F16*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N16" s="6" t="n">
+      <c r="N16" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O16" s="11" t="n">
+      <c r="O16" s="58" t="n">
         <v>30</v>
       </c>
-      <c r="P16" s="11" t="n">
+      <c r="P16" s="58" t="n">
         <v>7.8</v>
       </c>
       <c r="Q16" s="12" t="inlineStr">
@@ -1916,7 +1940,7 @@
       <c r="Y16" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="Z16" s="8">
+      <c r="Z16" s="57">
         <f>IF($G16="","",$G16/$Y16)</f>
         <v/>
       </c>
@@ -1931,25 +1955,25 @@
           <t>ADIDAS Yeezy 700 V3 Mono Safflower T.38 — occasion</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n">
+      <c r="B17" s="54" t="n">
         <v>63</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="55">
         <f>$B17+$Y17*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="56">
         <f>$C17/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E17" s="6">
+      <c r="E17" s="55">
         <f>CEILING($D17*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F17" s="8" t="n">
+      <c r="F17" s="57" t="n">
         <v>105</v>
       </c>
-      <c r="G17" s="8">
+      <c r="G17" s="57">
         <f>IF($F17="","",$F17-$C17-$M17-$N17)</f>
         <v/>
       </c>
@@ -1960,29 +1984,29 @@
       <c r="I17" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J17" s="6">
+      <c r="J17" s="55">
         <f>$C17/$I17</f>
         <v/>
       </c>
-      <c r="K17" s="6">
+      <c r="K17" s="55">
         <f>IF($F17="","",$F17/$I17)</f>
         <v/>
       </c>
-      <c r="L17" s="6">
+      <c r="L17" s="55">
         <f>IF($G17="","",$G17/$I17)</f>
         <v/>
       </c>
-      <c r="M17" s="7">
+      <c r="M17" s="56">
         <f>IF($F17="","",$F17*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N17" s="6" t="n">
+      <c r="N17" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O17" s="11" t="n">
+      <c r="O17" s="58" t="n">
         <v>50</v>
       </c>
-      <c r="P17" s="11" t="n">
+      <c r="P17" s="58" t="n">
         <v>13</v>
       </c>
       <c r="Q17" s="12" t="inlineStr">
@@ -2020,7 +2044,7 @@
       <c r="Y17" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z17" s="8">
+      <c r="Z17" s="57">
         <f>IF($G17="","",$G17/$Y17)</f>
         <v/>
       </c>
@@ -2035,25 +2059,25 @@
           <t>T-shirt BALENCIAGA T.2 — neuf</t>
         </is>
       </c>
-      <c r="B18" s="14" t="n">
+      <c r="B18" s="59" t="n">
         <v>113.4</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="60">
         <f>$B18+$Y18*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D18" s="16">
+      <c r="D18" s="61">
         <f>$C18/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E18" s="15">
+      <c r="E18" s="60">
         <f>CEILING($D18*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F18" s="17" t="n">
+      <c r="F18" s="62" t="n">
         <v>155</v>
       </c>
-      <c r="G18" s="17">
+      <c r="G18" s="62">
         <f>IF($F18="","",$F18-$C18-$M18-$N18)</f>
         <v/>
       </c>
@@ -2064,29 +2088,29 @@
       <c r="I18" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J18" s="15">
+      <c r="J18" s="60">
         <f>$C18/$I18</f>
         <v/>
       </c>
-      <c r="K18" s="15">
+      <c r="K18" s="60">
         <f>IF($F18="","",$F18/$I18)</f>
         <v/>
       </c>
-      <c r="L18" s="15">
+      <c r="L18" s="60">
         <f>IF($G18="","",$G18/$I18)</f>
         <v/>
       </c>
-      <c r="M18" s="16">
+      <c r="M18" s="61">
         <f>IF($F18="","",$F18*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N18" s="15" t="n">
+      <c r="N18" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="O18" s="20" t="n">
+      <c r="O18" s="63" t="n">
         <v>90</v>
       </c>
-      <c r="P18" s="20" t="n">
+      <c r="P18" s="63" t="n">
         <v>23.4</v>
       </c>
       <c r="Q18" s="21" t="inlineStr">
@@ -2128,7 +2152,7 @@
       <c r="Y18" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="Z18" s="17">
+      <c r="Z18" s="62">
         <f>IF($G18="","",$G18/$Y18)</f>
         <v/>
       </c>
@@ -2143,25 +2167,25 @@
           <t>ADIDAS x STELLA McCARTNEY ASMC Ultraboost 21 P.36 — modèle d'exposition</t>
         </is>
       </c>
-      <c r="B19" s="5" t="n">
+      <c r="B19" s="54" t="n">
         <v>37.8</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="55">
         <f>$B19+$Y19*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D19" s="7">
+      <c r="D19" s="56">
         <f>$C19/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="E19" s="6">
+      <c r="E19" s="55">
         <f>CEILING($D19*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F19" s="8" t="n">
+      <c r="F19" s="57" t="n">
         <v>79</v>
       </c>
-      <c r="G19" s="8">
+      <c r="G19" s="57">
         <f>IF($F19="","",$F19-$C19-$M19-$N19)</f>
         <v/>
       </c>
@@ -2172,30 +2196,30 @@
       <c r="I19" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J19" s="6">
+      <c r="J19" s="55">
         <f>$C19/$I19</f>
         <v/>
       </c>
-      <c r="K19" s="6">
+      <c r="K19" s="55">
         <f>IF($F19="","",$F19/$I19)</f>
         <v/>
       </c>
-      <c r="L19" s="6">
+      <c r="L19" s="55">
         <f>IF($G19="","",$G19/$I19)</f>
         <v/>
       </c>
-      <c r="M19" s="7">
+      <c r="M19" s="56">
         <f>IF($F19="","",$F19*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N19" s="6">
+      <c r="N19" s="55">
         <f>IF($F19="","",$F19*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="O19" s="11" t="n">
+      <c r="O19" s="58" t="n">
         <v>30</v>
       </c>
-      <c r="P19" s="11" t="n">
+      <c r="P19" s="58" t="n">
         <v>7.8</v>
       </c>
       <c r="Q19" s="12" t="inlineStr">
@@ -2233,7 +2257,7 @@
       <c r="Y19" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z19" s="8">
+      <c r="Z19" s="57">
         <f>IF($G19="","",$G19/$Y19)</f>
         <v/>
       </c>
@@ -2248,25 +2272,25 @@
           <t>Blazer noir KARL LAGERFELD T.36 FR — neuf avec étiquette</t>
         </is>
       </c>
-      <c r="B20" s="5" t="n">
+      <c r="B20" s="54" t="n">
         <v>50.4</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="55">
         <f>$B20+$Y20*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D20" s="7">
+      <c r="D20" s="56">
         <f>$C20/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="E20" s="6">
+      <c r="E20" s="55">
         <f>CEILING($D20*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F20" s="8" t="n">
+      <c r="F20" s="57" t="n">
         <v>91</v>
       </c>
-      <c r="G20" s="8">
+      <c r="G20" s="57">
         <f>IF($F20="","",$F20-$C20-$M20-$N20)</f>
         <v/>
       </c>
@@ -2277,30 +2301,30 @@
       <c r="I20" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J20" s="6">
+      <c r="J20" s="55">
         <f>$C20/$I20</f>
         <v/>
       </c>
-      <c r="K20" s="6">
+      <c r="K20" s="55">
         <f>IF($F20="","",$F20/$I20)</f>
         <v/>
       </c>
-      <c r="L20" s="6">
+      <c r="L20" s="55">
         <f>IF($G20="","",$G20/$I20)</f>
         <v/>
       </c>
-      <c r="M20" s="7">
+      <c r="M20" s="56">
         <f>IF($F20="","",$F20*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N20" s="6">
+      <c r="N20" s="55">
         <f>IF($F20="","",$F20*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="O20" s="11" t="n">
+      <c r="O20" s="58" t="n">
         <v>40</v>
       </c>
-      <c r="P20" s="11" t="n">
+      <c r="P20" s="58" t="n">
         <v>10.4</v>
       </c>
       <c r="Q20" s="12" t="inlineStr">
@@ -2338,7 +2362,7 @@
       <c r="Y20" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z20" s="8">
+      <c r="Z20" s="57">
         <f>IF($G20="","",$G20/$Y20)</f>
         <v/>
       </c>
@@ -2353,25 +2377,25 @@
           <t>PHILIPP PLEIN SPORT baskets montantes P.40 — neuves</t>
         </is>
       </c>
-      <c r="B21" s="5" t="n">
+      <c r="B21" s="54" t="n">
         <v>57.51</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C21" s="55">
         <f>$B21+$Y21*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D21" s="7">
+      <c r="D21" s="56">
         <f>$C21/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E21" s="6">
+      <c r="E21" s="55">
         <f>CEILING($D21*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F21" s="8" t="n">
+      <c r="F21" s="57" t="n">
         <v>95</v>
       </c>
-      <c r="G21" s="8">
+      <c r="G21" s="57">
         <f>IF($F21="","",$F21-$C21-$M21-$N21)</f>
         <v/>
       </c>
@@ -2382,29 +2406,29 @@
       <c r="I21" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J21" s="6">
+      <c r="J21" s="55">
         <f>$C21/$I21</f>
         <v/>
       </c>
-      <c r="K21" s="6">
+      <c r="K21" s="55">
         <f>IF($F21="","",$F21/$I21)</f>
         <v/>
       </c>
-      <c r="L21" s="6">
+      <c r="L21" s="55">
         <f>IF($G21="","",$G21/$I21)</f>
         <v/>
       </c>
-      <c r="M21" s="7">
+      <c r="M21" s="56">
         <f>IF($F21="","",$F21*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N21" s="6" t="n">
+      <c r="N21" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O21" s="11" t="n">
+      <c r="O21" s="58" t="n">
         <v>45</v>
       </c>
-      <c r="P21" s="11" t="n">
+      <c r="P21" s="58" t="n">
         <v>11.7</v>
       </c>
       <c r="Q21" s="12" t="inlineStr">
@@ -2442,7 +2466,7 @@
       <c r="Y21" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z21" s="8">
+      <c r="Z21" s="57">
         <f>IF($G21="","",$G21/$Y21)</f>
         <v/>
       </c>
@@ -2457,25 +2481,25 @@
           <t>CHIARA FERRAGNI robe bustier courte T.M — neuve</t>
         </is>
       </c>
-      <c r="B22" s="5" t="n">
+      <c r="B22" s="54" t="n">
         <v>31.95</v>
       </c>
-      <c r="C22" s="6">
+      <c r="C22" s="55">
         <f>$B22+$Y22*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D22" s="7">
+      <c r="D22" s="56">
         <f>$C22/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="E22" s="6">
+      <c r="E22" s="55">
         <f>CEILING($D22*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F22" s="8" t="n">
+      <c r="F22" s="57" t="n">
         <v>69</v>
       </c>
-      <c r="G22" s="8">
+      <c r="G22" s="57">
         <f>IF($F22="","",$F22-$C22-$M22-$N22)</f>
         <v/>
       </c>
@@ -2486,30 +2510,30 @@
       <c r="I22" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J22" s="6">
+      <c r="J22" s="55">
         <f>$C22/$I22</f>
         <v/>
       </c>
-      <c r="K22" s="6">
+      <c r="K22" s="55">
         <f>IF($F22="","",$F22/$I22)</f>
         <v/>
       </c>
-      <c r="L22" s="6">
+      <c r="L22" s="55">
         <f>IF($G22="","",$G22/$I22)</f>
         <v/>
       </c>
-      <c r="M22" s="7">
+      <c r="M22" s="56">
         <f>IF($F22="","",$F22*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N22" s="6">
+      <c r="N22" s="55">
         <f>IF($F22="","",$F22*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="O22" s="11" t="n">
+      <c r="O22" s="58" t="n">
         <v>25</v>
       </c>
-      <c r="P22" s="11" t="n">
+      <c r="P22" s="58" t="n">
         <v>6.5</v>
       </c>
       <c r="Q22" s="12" t="inlineStr">
@@ -2547,7 +2571,7 @@
       <c r="Y22" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z22" s="8">
+      <c r="Z22" s="57">
         <f>IF($G22="","",$G22/$Y22)</f>
         <v/>
       </c>
@@ -2562,25 +2586,25 @@
           <t>PIER ANTONIO GASPARI robe droite bleu marine T.42 — neuve</t>
         </is>
       </c>
-      <c r="B23" s="5" t="n">
+      <c r="B23" s="54" t="n">
         <v>25.56</v>
       </c>
-      <c r="C23" s="6">
+      <c r="C23" s="55">
         <f>$B23+$Y23*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D23" s="7">
+      <c r="D23" s="56">
         <f>$C23/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="E23" s="6">
+      <c r="E23" s="55">
         <f>CEILING($D23*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F23" s="8" t="n">
+      <c r="F23" s="57" t="n">
         <v>62</v>
       </c>
-      <c r="G23" s="8">
+      <c r="G23" s="57">
         <f>IF($F23="","",$F23-$C23-$M23-$N23)</f>
         <v/>
       </c>
@@ -2591,30 +2615,30 @@
       <c r="I23" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J23" s="6">
+      <c r="J23" s="55">
         <f>$C23/$I23</f>
         <v/>
       </c>
-      <c r="K23" s="6">
+      <c r="K23" s="55">
         <f>IF($F23="","",$F23/$I23)</f>
         <v/>
       </c>
-      <c r="L23" s="6">
+      <c r="L23" s="55">
         <f>IF($G23="","",$G23/$I23)</f>
         <v/>
       </c>
-      <c r="M23" s="7">
+      <c r="M23" s="56">
         <f>IF($F23="","",$F23*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N23" s="6">
+      <c r="N23" s="55">
         <f>IF($F23="","",$F23*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="O23" s="11" t="n">
+      <c r="O23" s="58" t="n">
         <v>20</v>
       </c>
-      <c r="P23" s="11" t="n">
+      <c r="P23" s="58" t="n">
         <v>5.2</v>
       </c>
       <c r="Q23" s="12" t="inlineStr">
@@ -2652,7 +2676,7 @@
       <c r="Y23" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z23" s="8">
+      <c r="Z23" s="57">
         <f>IF($G23="","",$G23/$Y23)</f>
         <v/>
       </c>
@@ -2667,25 +2691,25 @@
           <t>Lot de 4 toupies BEYBLADE HASBRO</t>
         </is>
       </c>
-      <c r="B24" s="23" t="n">
+      <c r="B24" s="64" t="n">
         <v>19.17</v>
       </c>
-      <c r="C24" s="24">
+      <c r="C24" s="65">
         <f>$B24+$Y24*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D24" s="25">
+      <c r="D24" s="66">
         <f>$C24/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E24" s="24">
+      <c r="E24" s="65">
         <f>CEILING($D24*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F24" s="26" t="n">
+      <c r="F24" s="67" t="n">
         <v>55</v>
       </c>
-      <c r="G24" s="26">
+      <c r="G24" s="67">
         <f>IF($F24="","",$F24-$C24-$M24-$N24)</f>
         <v/>
       </c>
@@ -2696,29 +2720,29 @@
       <c r="I24" s="28" t="n">
         <v>4</v>
       </c>
-      <c r="J24" s="24">
+      <c r="J24" s="65">
         <f>$C24/$I24</f>
         <v/>
       </c>
-      <c r="K24" s="24">
+      <c r="K24" s="65">
         <f>IF($F24="","",$F24/$I24)</f>
         <v/>
       </c>
-      <c r="L24" s="24">
+      <c r="L24" s="65">
         <f>IF($G24="","",$G24/$I24)</f>
         <v/>
       </c>
-      <c r="M24" s="25">
+      <c r="M24" s="66">
         <f>IF($F24="","",$F24*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N24" s="24" t="n">
+      <c r="N24" s="65" t="n">
         <v>0</v>
       </c>
-      <c r="O24" s="29" t="n">
+      <c r="O24" s="68" t="n">
         <v>15</v>
       </c>
-      <c r="P24" s="29" t="n">
+      <c r="P24" s="68" t="n">
         <v>3.9</v>
       </c>
       <c r="Q24" s="30" t="inlineStr">
@@ -2756,7 +2780,7 @@
       <c r="Y24" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="Z24" s="26">
+      <c r="Z24" s="67">
         <f>IF($G24="","",$G24/$Y24)</f>
         <v/>
       </c>
@@ -2771,25 +2795,25 @@
           <t>Ballerines MASSIMO DUTTI P.41 — traces d'essayage</t>
         </is>
       </c>
-      <c r="B25" s="5" t="n">
+      <c r="B25" s="54" t="n">
         <v>25.2</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C25" s="55">
         <f>$B25+$Y25*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D25" s="7">
+      <c r="D25" s="56">
         <f>$C25/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E25" s="6">
+      <c r="E25" s="55">
         <f>CEILING($D25*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F25" s="8" t="n">
+      <c r="F25" s="57" t="n">
         <v>61</v>
       </c>
-      <c r="G25" s="8">
+      <c r="G25" s="57">
         <f>IF($F25="","",$F25-$C25-$M25-$N25)</f>
         <v/>
       </c>
@@ -2800,29 +2824,29 @@
       <c r="I25" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J25" s="6">
+      <c r="J25" s="55">
         <f>$C25/$I25</f>
         <v/>
       </c>
-      <c r="K25" s="6">
+      <c r="K25" s="55">
         <f>IF($F25="","",$F25/$I25)</f>
         <v/>
       </c>
-      <c r="L25" s="6">
+      <c r="L25" s="55">
         <f>IF($G25="","",$G25/$I25)</f>
         <v/>
       </c>
-      <c r="M25" s="7">
+      <c r="M25" s="56">
         <f>IF($F25="","",$F25*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N25" s="6" t="n">
+      <c r="N25" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O25" s="11" t="n">
+      <c r="O25" s="58" t="n">
         <v>20</v>
       </c>
-      <c r="P25" s="11" t="n">
+      <c r="P25" s="58" t="n">
         <v>5.2</v>
       </c>
       <c r="Q25" s="12" t="inlineStr">
@@ -2860,7 +2884,7 @@
       <c r="Y25" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z25" s="8">
+      <c r="Z25" s="57">
         <f>IF($G25="","",$G25/$Y25)</f>
         <v/>
       </c>
@@ -2875,25 +2899,25 @@
           <t>GEOX baskets P.35 — neuves</t>
         </is>
       </c>
-      <c r="B26" s="5" t="n">
+      <c r="B26" s="54" t="n">
         <v>21.73</v>
       </c>
-      <c r="C26" s="6">
+      <c r="C26" s="55">
         <f>$B26+$Y26*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D26" s="7">
+      <c r="D26" s="56">
         <f>$C26/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E26" s="6">
+      <c r="E26" s="55">
         <f>CEILING($D26*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F26" s="8" t="n">
+      <c r="F26" s="57" t="n">
         <v>54</v>
       </c>
-      <c r="G26" s="8">
+      <c r="G26" s="57">
         <f>IF($F26="","",$F26-$C26-$M26-$N26)</f>
         <v/>
       </c>
@@ -2904,29 +2928,29 @@
       <c r="I26" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J26" s="6">
+      <c r="J26" s="55">
         <f>$C26/$I26</f>
         <v/>
       </c>
-      <c r="K26" s="6">
+      <c r="K26" s="55">
         <f>IF($F26="","",$F26/$I26)</f>
         <v/>
       </c>
-      <c r="L26" s="6">
+      <c r="L26" s="55">
         <f>IF($G26="","",$G26/$I26)</f>
         <v/>
       </c>
-      <c r="M26" s="7">
+      <c r="M26" s="56">
         <f>IF($F26="","",$F26*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N26" s="6" t="n">
+      <c r="N26" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O26" s="11" t="n">
+      <c r="O26" s="58" t="n">
         <v>17</v>
       </c>
-      <c r="P26" s="11" t="n">
+      <c r="P26" s="58" t="n">
         <v>4.42</v>
       </c>
       <c r="Q26" s="12" t="inlineStr">
@@ -2964,7 +2988,7 @@
       <c r="Y26" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z26" s="8">
+      <c r="Z26" s="57">
         <f>IF($G26="","",$G26/$Y26)</f>
         <v/>
       </c>
@@ -2979,25 +3003,25 @@
           <t>1 booster box Pokémon MEGA Nihil Zero (Munikis Zero) M3 — 30 boosters de 5 cartes — 2 lots de 15 à 49 €, blister à photographier avant ouverture</t>
         </is>
       </c>
-      <c r="B27" s="5" t="n">
+      <c r="B27" s="54" t="n">
         <v>69.23999999999999</v>
       </c>
-      <c r="C27" s="6">
+      <c r="C27" s="55">
         <f>$B27</f>
         <v/>
       </c>
-      <c r="D27" s="7">
+      <c r="D27" s="56">
         <f>$C27/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E27" s="6">
+      <c r="E27" s="55">
         <f>CEILING($D27*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F27" s="8" t="n">
+      <c r="F27" s="57" t="n">
         <v>98</v>
       </c>
-      <c r="G27" s="8">
+      <c r="G27" s="57">
         <f>IF($F27="","",$F27-$C27-$M27-$N27)</f>
         <v/>
       </c>
@@ -3008,23 +3032,23 @@
       <c r="I27" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="J27" s="6">
+      <c r="J27" s="55">
         <f>$C27/$I27</f>
         <v/>
       </c>
-      <c r="K27" s="6">
+      <c r="K27" s="55">
         <f>IF($F27="","",$F27/$I27)</f>
         <v/>
       </c>
-      <c r="L27" s="6">
+      <c r="L27" s="55">
         <f>IF($G27="","",$G27/$I27)</f>
         <v/>
       </c>
-      <c r="M27" s="7">
+      <c r="M27" s="56">
         <f>IF($F27="","",$F27*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N27" s="6" t="n">
+      <c r="N27" s="55" t="n">
         <v>0</v>
       </c>
       <c r="O27" s="31" t="n"/>
@@ -3064,7 +3088,7 @@
       <c r="Y27" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="Z27" s="8">
+      <c r="Z27" s="57">
         <f>IF($G27="","",$G27/$Y27)</f>
         <v/>
       </c>
@@ -3079,25 +3103,25 @@
           <t>Veste en jean ARMANI EXCHANGE T.S — neuve</t>
         </is>
       </c>
-      <c r="B28" s="14" t="n">
+      <c r="B28" s="59" t="n">
         <v>25.2</v>
       </c>
-      <c r="C28" s="15">
+      <c r="C28" s="60">
         <f>$B28+$Y28*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D28" s="16">
+      <c r="D28" s="61">
         <f>$C28/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E28" s="15">
+      <c r="E28" s="60">
         <f>CEILING($D28*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F28" s="17" t="n">
+      <c r="F28" s="62" t="n">
         <v>50</v>
       </c>
-      <c r="G28" s="17">
+      <c r="G28" s="62">
         <f>IF($F28="","",$F28-$C28-$M28-$N28)</f>
         <v/>
       </c>
@@ -3108,29 +3132,29 @@
       <c r="I28" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J28" s="15">
+      <c r="J28" s="60">
         <f>$C28/$I28</f>
         <v/>
       </c>
-      <c r="K28" s="15">
+      <c r="K28" s="60">
         <f>IF($F28="","",$F28/$I28)</f>
         <v/>
       </c>
-      <c r="L28" s="15">
+      <c r="L28" s="60">
         <f>IF($G28="","",$G28/$I28)</f>
         <v/>
       </c>
-      <c r="M28" s="16">
+      <c r="M28" s="61">
         <f>IF($F28="","",$F28*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N28" s="15" t="n">
+      <c r="N28" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="O28" s="20" t="n">
+      <c r="O28" s="63" t="n">
         <v>20</v>
       </c>
-      <c r="P28" s="20" t="n">
+      <c r="P28" s="63" t="n">
         <v>5.2</v>
       </c>
       <c r="Q28" s="21" t="inlineStr">
@@ -3172,7 +3196,7 @@
       <c r="Y28" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="Z28" s="17">
+      <c r="Z28" s="62">
         <f>IF($G28="","",$G28/$Y28)</f>
         <v/>
       </c>
@@ -3187,25 +3211,25 @@
           <t>Short BA&amp;SH Fegor T.34 — neuf</t>
         </is>
       </c>
-      <c r="B29" s="5" t="n">
+      <c r="B29" s="54" t="n">
         <v>50.4</v>
       </c>
-      <c r="C29" s="6">
+      <c r="C29" s="55">
         <f>$B29+$Y29*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D29" s="7">
+      <c r="D29" s="56">
         <f>$C29/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="E29" s="6">
+      <c r="E29" s="55">
         <f>CEILING($D29*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F29" s="8" t="n">
+      <c r="F29" s="57" t="n">
         <v>75</v>
       </c>
-      <c r="G29" s="8">
+      <c r="G29" s="57">
         <f>IF($F29="","",$F29-$C29-$M29-$N29)</f>
         <v/>
       </c>
@@ -3216,30 +3240,30 @@
       <c r="I29" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J29" s="6">
+      <c r="J29" s="55">
         <f>$C29/$I29</f>
         <v/>
       </c>
-      <c r="K29" s="6">
+      <c r="K29" s="55">
         <f>IF($F29="","",$F29/$I29)</f>
         <v/>
       </c>
-      <c r="L29" s="6">
+      <c r="L29" s="55">
         <f>IF($G29="","",$G29/$I29)</f>
         <v/>
       </c>
-      <c r="M29" s="7">
+      <c r="M29" s="56">
         <f>IF($F29="","",$F29*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N29" s="6">
+      <c r="N29" s="55">
         <f>IF($F29="","",$F29*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="O29" s="11" t="n">
+      <c r="O29" s="58" t="n">
         <v>40</v>
       </c>
-      <c r="P29" s="11" t="n">
+      <c r="P29" s="58" t="n">
         <v>10.4</v>
       </c>
       <c r="Q29" s="12" t="inlineStr">
@@ -3277,7 +3301,7 @@
       <c r="Y29" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z29" s="8">
+      <c r="Z29" s="57">
         <f>IF($G29="","",$G29/$Y29)</f>
         <v/>
       </c>
@@ -3287,105 +3311,109 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="13" t="inlineStr">
         <is>
           <t>NEW BALANCE G19064IK Alkaline Green P.38½ — neuves avec boîte</t>
         </is>
       </c>
-      <c r="B30" s="5" t="n">
+      <c r="B30" s="59" t="n">
         <v>75.59999999999999</v>
       </c>
-      <c r="C30" s="6">
+      <c r="C30" s="60">
         <f>$B30+$Y30*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D30" s="7">
+      <c r="D30" s="61">
         <f>$C30/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E30" s="6">
+      <c r="E30" s="60">
         <f>CEILING($D30*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F30" s="8" t="n">
+      <c r="F30" s="62" t="n">
         <v>99</v>
       </c>
-      <c r="G30" s="8">
+      <c r="G30" s="62">
         <f>IF($F30="","",$F30-$C30-$M30-$N30)</f>
         <v/>
       </c>
-      <c r="H30" s="9">
+      <c r="H30" s="18">
         <f>IF($G30="","",$G30/$C30)</f>
         <v/>
       </c>
-      <c r="I30" s="10" t="n">
+      <c r="I30" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J30" s="6">
+      <c r="J30" s="60">
         <f>$C30/$I30</f>
         <v/>
       </c>
-      <c r="K30" s="6">
+      <c r="K30" s="60">
         <f>IF($F30="","",$F30/$I30)</f>
         <v/>
       </c>
-      <c r="L30" s="6">
+      <c r="L30" s="60">
         <f>IF($G30="","",$G30/$I30)</f>
         <v/>
       </c>
-      <c r="M30" s="7">
+      <c r="M30" s="61">
         <f>IF($F30="","",$F30*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N30" s="6" t="n">
+      <c r="N30" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="O30" s="11" t="n">
+      <c r="O30" s="63" t="n">
         <v>60</v>
       </c>
-      <c r="P30" s="11" t="n">
+      <c r="P30" s="63" t="n">
         <v>15.6</v>
       </c>
-      <c r="Q30" s="12" t="inlineStr">
+      <c r="Q30" s="21" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="R30" s="12" t="inlineStr">
+      <c r="R30" s="21" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="S30" s="12" t="inlineStr">
+      <c r="S30" s="21" t="inlineStr">
         <is>
           <t>FB2026-43716</t>
         </is>
       </c>
-      <c r="T30" s="12" t="inlineStr">
+      <c r="T30" s="21" t="inlineStr">
         <is>
           <t>199</t>
         </is>
       </c>
-      <c r="U30" s="4" t="inlineStr">
-        <is>
-          <t>Leboncoin</t>
-        </is>
-      </c>
-      <c r="V30" s="4" t="inlineStr"/>
-      <c r="W30" s="4" t="inlineStr">
-        <is>
-          <t>Liquider</t>
-        </is>
-      </c>
-      <c r="X30" s="4" t="inlineStr"/>
-      <c r="Y30" s="4" t="n">
+      <c r="U30" s="13" t="inlineStr">
+        <is>
+          <t>Vinted</t>
+        </is>
+      </c>
+      <c r="V30" s="13" t="inlineStr"/>
+      <c r="W30" s="13" t="inlineStr">
+        <is>
+          <t>VENDUE 99 €, encaissée le 10/09</t>
+        </is>
+      </c>
+      <c r="X30" s="13" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="Y30" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="Z30" s="8">
+      <c r="Z30" s="62">
         <f>IF($G30="","",$G30/$Y30)</f>
         <v/>
       </c>
-      <c r="AA30" s="4">
+      <c r="AA30" s="13">
         <f>IF($Z30="","",IF($Z30&gt;=25,"atteint",TEXT(25-$Z30,"0.00")&amp;" € manquants"))</f>
         <v/>
       </c>
@@ -3396,25 +3424,25 @@
           <t>SALOMON X Ultra 5 Mid GTX P.44 — neuves</t>
         </is>
       </c>
-      <c r="B31" s="14" t="n">
+      <c r="B31" s="59" t="n">
         <v>76.68000000000001</v>
       </c>
-      <c r="C31" s="15">
+      <c r="C31" s="60">
         <f>$B31+$Y31*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D31" s="16">
+      <c r="D31" s="61">
         <f>$C31/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E31" s="15">
+      <c r="E31" s="60">
         <f>CEILING($D31*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F31" s="17" t="n">
+      <c r="F31" s="62" t="n">
         <v>100</v>
       </c>
-      <c r="G31" s="17">
+      <c r="G31" s="62">
         <f>IF($F31="","",$F31-$C31-$M31-$N31)</f>
         <v/>
       </c>
@@ -3425,29 +3453,29 @@
       <c r="I31" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J31" s="15">
+      <c r="J31" s="60">
         <f>$C31/$I31</f>
         <v/>
       </c>
-      <c r="K31" s="15">
+      <c r="K31" s="60">
         <f>IF($F31="","",$F31/$I31)</f>
         <v/>
       </c>
-      <c r="L31" s="15">
+      <c r="L31" s="60">
         <f>IF($G31="","",$G31/$I31)</f>
         <v/>
       </c>
-      <c r="M31" s="16">
+      <c r="M31" s="61">
         <f>IF($F31="","",$F31*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N31" s="15" t="n">
+      <c r="N31" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="O31" s="20" t="n">
+      <c r="O31" s="63" t="n">
         <v>60</v>
       </c>
-      <c r="P31" s="20" t="n">
+      <c r="P31" s="63" t="n">
         <v>15.6</v>
       </c>
       <c r="Q31" s="21" t="inlineStr">
@@ -3472,13 +3500,13 @@
       </c>
       <c r="U31" s="13" t="inlineStr">
         <is>
-          <t>Vinted, Italie — non encaissé</t>
+          <t>Vinted, Italie — encaissé le 21/08</t>
         </is>
       </c>
       <c r="V31" s="13" t="inlineStr"/>
       <c r="W31" s="13" t="inlineStr">
         <is>
-          <t>VENDUE, en attente</t>
+          <t>VENDUE</t>
         </is>
       </c>
       <c r="X31" s="13" t="inlineStr">
@@ -3489,7 +3517,7 @@
       <c r="Y31" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="Z31" s="17">
+      <c r="Z31" s="62">
         <f>IF($G31="","",$G31/$Y31)</f>
         <v/>
       </c>
@@ -3504,25 +3532,25 @@
           <t>Sac demi-lune nylon noir KARL LAGERFELD JEANS — neuf avec étiquette</t>
         </is>
       </c>
-      <c r="B32" s="14" t="n">
+      <c r="B32" s="59" t="n">
         <v>50.4</v>
       </c>
-      <c r="C32" s="15">
+      <c r="C32" s="60">
         <f>$B32+$Y32*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D32" s="16">
+      <c r="D32" s="61">
         <f>$C32/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E32" s="15">
+      <c r="E32" s="60">
         <f>CEILING($D32*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F32" s="17" t="n">
+      <c r="F32" s="62" t="n">
         <v>70</v>
       </c>
-      <c r="G32" s="17">
+      <c r="G32" s="62">
         <f>IF($F32="","",$F32-$C32-$M32-$N32)</f>
         <v/>
       </c>
@@ -3533,29 +3561,29 @@
       <c r="I32" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J32" s="15">
+      <c r="J32" s="60">
         <f>$C32/$I32</f>
         <v/>
       </c>
-      <c r="K32" s="15">
+      <c r="K32" s="60">
         <f>IF($F32="","",$F32/$I32)</f>
         <v/>
       </c>
-      <c r="L32" s="15">
+      <c r="L32" s="60">
         <f>IF($G32="","",$G32/$I32)</f>
         <v/>
       </c>
-      <c r="M32" s="16">
+      <c r="M32" s="61">
         <f>IF($F32="","",$F32*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N32" s="15" t="n">
+      <c r="N32" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="O32" s="20" t="n">
+      <c r="O32" s="63" t="n">
         <v>40</v>
       </c>
-      <c r="P32" s="20" t="n">
+      <c r="P32" s="63" t="n">
         <v>10.4</v>
       </c>
       <c r="Q32" s="21" t="inlineStr">
@@ -3597,7 +3625,7 @@
       <c r="Y32" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="Z32" s="17">
+      <c r="Z32" s="62">
         <f>IF($G32="","",$G32/$Y32)</f>
         <v/>
       </c>
@@ -3612,25 +3640,25 @@
           <t>EMPORIO ARMANI baskets P.36 — neuves</t>
         </is>
       </c>
-      <c r="B33" s="5" t="n">
+      <c r="B33" s="54" t="n">
         <v>51.12</v>
       </c>
-      <c r="C33" s="6">
+      <c r="C33" s="55">
         <f>$B33+$Y33*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D33" s="7">
+      <c r="D33" s="56">
         <f>$C33/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E33" s="6">
+      <c r="E33" s="55">
         <f>CEILING($D33*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F33" s="8" t="n">
+      <c r="F33" s="57" t="n">
         <v>69</v>
       </c>
-      <c r="G33" s="8">
+      <c r="G33" s="57">
         <f>IF($F33="","",$F33-$C33-$M33-$N33)</f>
         <v/>
       </c>
@@ -3641,29 +3669,29 @@
       <c r="I33" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J33" s="6">
+      <c r="J33" s="55">
         <f>$C33/$I33</f>
         <v/>
       </c>
-      <c r="K33" s="6">
+      <c r="K33" s="55">
         <f>IF($F33="","",$F33/$I33)</f>
         <v/>
       </c>
-      <c r="L33" s="6">
+      <c r="L33" s="55">
         <f>IF($G33="","",$G33/$I33)</f>
         <v/>
       </c>
-      <c r="M33" s="7">
+      <c r="M33" s="56">
         <f>IF($F33="","",$F33*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N33" s="6" t="n">
+      <c r="N33" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O33" s="11" t="n">
+      <c r="O33" s="58" t="n">
         <v>40</v>
       </c>
-      <c r="P33" s="11" t="n">
+      <c r="P33" s="58" t="n">
         <v>10.4</v>
       </c>
       <c r="Q33" s="12" t="inlineStr">
@@ -3701,7 +3729,7 @@
       <c r="Y33" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z33" s="8">
+      <c r="Z33" s="57">
         <f>IF($G33="","",$G33/$Y33)</f>
         <v/>
       </c>
@@ -3716,25 +3744,25 @@
           <t>Lot de 4 toupies BEYBLADE HASBRO</t>
         </is>
       </c>
-      <c r="B34" s="23" t="n">
+      <c r="B34" s="64" t="n">
         <v>38.34</v>
       </c>
-      <c r="C34" s="24">
+      <c r="C34" s="65">
         <f>$B34+$Y34*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D34" s="25">
+      <c r="D34" s="66">
         <f>$C34/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E34" s="24">
+      <c r="E34" s="65">
         <f>CEILING($D34*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F34" s="26" t="n">
+      <c r="F34" s="67" t="n">
         <v>55</v>
       </c>
-      <c r="G34" s="26">
+      <c r="G34" s="67">
         <f>IF($F34="","",$F34-$C34-$M34-$N34)</f>
         <v/>
       </c>
@@ -3745,29 +3773,29 @@
       <c r="I34" s="28" t="n">
         <v>4</v>
       </c>
-      <c r="J34" s="24">
+      <c r="J34" s="65">
         <f>$C34/$I34</f>
         <v/>
       </c>
-      <c r="K34" s="24">
+      <c r="K34" s="65">
         <f>IF($F34="","",$F34/$I34)</f>
         <v/>
       </c>
-      <c r="L34" s="24">
+      <c r="L34" s="65">
         <f>IF($G34="","",$G34/$I34)</f>
         <v/>
       </c>
-      <c r="M34" s="25">
+      <c r="M34" s="66">
         <f>IF($F34="","",$F34*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N34" s="24" t="n">
+      <c r="N34" s="65" t="n">
         <v>0</v>
       </c>
-      <c r="O34" s="29" t="n">
+      <c r="O34" s="68" t="n">
         <v>30</v>
       </c>
-      <c r="P34" s="29" t="n">
+      <c r="P34" s="68" t="n">
         <v>7.8</v>
       </c>
       <c r="Q34" s="30" t="inlineStr">
@@ -3805,7 +3833,7 @@
       <c r="Y34" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="Z34" s="26">
+      <c r="Z34" s="67">
         <f>IF($G34="","",$G34/$Y34)</f>
         <v/>
       </c>
@@ -3820,25 +3848,25 @@
           <t>NEW BALANCE sneakers P.38 — neuves</t>
         </is>
       </c>
-      <c r="B35" s="5" t="n">
+      <c r="B35" s="54" t="n">
         <v>38.34</v>
       </c>
-      <c r="C35" s="6">
+      <c r="C35" s="55">
         <f>$B35+$Y35*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D35" s="7">
+      <c r="D35" s="56">
         <f>$C35/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E35" s="6">
+      <c r="E35" s="55">
         <f>CEILING($D35*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F35" s="8" t="n">
+      <c r="F35" s="57" t="n">
         <v>54</v>
       </c>
-      <c r="G35" s="8">
+      <c r="G35" s="57">
         <f>IF($F35="","",$F35-$C35-$M35-$N35)</f>
         <v/>
       </c>
@@ -3849,29 +3877,29 @@
       <c r="I35" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J35" s="6">
+      <c r="J35" s="55">
         <f>$C35/$I35</f>
         <v/>
       </c>
-      <c r="K35" s="6">
+      <c r="K35" s="55">
         <f>IF($F35="","",$F35/$I35)</f>
         <v/>
       </c>
-      <c r="L35" s="6">
+      <c r="L35" s="55">
         <f>IF($G35="","",$G35/$I35)</f>
         <v/>
       </c>
-      <c r="M35" s="7">
+      <c r="M35" s="56">
         <f>IF($F35="","",$F35*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N35" s="6" t="n">
+      <c r="N35" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O35" s="11" t="n">
+      <c r="O35" s="58" t="n">
         <v>30</v>
       </c>
-      <c r="P35" s="11" t="n">
+      <c r="P35" s="58" t="n">
         <v>7.8</v>
       </c>
       <c r="Q35" s="12" t="inlineStr">
@@ -3909,7 +3937,7 @@
       <c r="Y35" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z35" s="8">
+      <c r="Z35" s="57">
         <f>IF($G35="","",$G35/$Y35)</f>
         <v/>
       </c>
@@ -3924,25 +3952,25 @@
           <t>NEW BALANCE baskets montantes P.44 — neuves</t>
         </is>
       </c>
-      <c r="B36" s="5" t="n">
+      <c r="B36" s="54" t="n">
         <v>51.12</v>
       </c>
-      <c r="C36" s="6">
+      <c r="C36" s="55">
         <f>$B36+$Y36*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D36" s="7">
+      <c r="D36" s="56">
         <f>$C36/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E36" s="6">
+      <c r="E36" s="55">
         <f>CEILING($D36*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F36" s="8" t="n">
+      <c r="F36" s="57" t="n">
         <v>65</v>
       </c>
-      <c r="G36" s="8">
+      <c r="G36" s="57">
         <f>IF($F36="","",$F36-$C36-$M36-$N36)</f>
         <v/>
       </c>
@@ -3953,29 +3981,29 @@
       <c r="I36" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J36" s="6">
+      <c r="J36" s="55">
         <f>$C36/$I36</f>
         <v/>
       </c>
-      <c r="K36" s="6">
+      <c r="K36" s="55">
         <f>IF($F36="","",$F36/$I36)</f>
         <v/>
       </c>
-      <c r="L36" s="6">
+      <c r="L36" s="55">
         <f>IF($G36="","",$G36/$I36)</f>
         <v/>
       </c>
-      <c r="M36" s="7">
+      <c r="M36" s="56">
         <f>IF($F36="","",$F36*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N36" s="6" t="n">
+      <c r="N36" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O36" s="11" t="n">
+      <c r="O36" s="58" t="n">
         <v>40</v>
       </c>
-      <c r="P36" s="11" t="n">
+      <c r="P36" s="58" t="n">
         <v>10.4</v>
       </c>
       <c r="Q36" s="12" t="inlineStr">
@@ -4013,7 +4041,7 @@
       <c r="Y36" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z36" s="8">
+      <c r="Z36" s="57">
         <f>IF($G36="","",$G36/$Y36)</f>
         <v/>
       </c>
@@ -4028,25 +4056,25 @@
           <t>TOMMY JEANS baskets basses P.40 — neuves</t>
         </is>
       </c>
-      <c r="B37" s="5" t="n">
+      <c r="B37" s="54" t="n">
         <v>52.4</v>
       </c>
-      <c r="C37" s="6">
+      <c r="C37" s="55">
         <f>$B37+$Y37*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D37" s="7">
+      <c r="D37" s="56">
         <f>$C37/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E37" s="6">
+      <c r="E37" s="55">
         <f>CEILING($D37*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F37" s="8" t="n">
+      <c r="F37" s="57" t="n">
         <v>65</v>
       </c>
-      <c r="G37" s="8">
+      <c r="G37" s="57">
         <f>IF($F37="","",$F37-$C37-$M37-$N37)</f>
         <v/>
       </c>
@@ -4057,29 +4085,29 @@
       <c r="I37" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J37" s="6">
+      <c r="J37" s="55">
         <f>$C37/$I37</f>
         <v/>
       </c>
-      <c r="K37" s="6">
+      <c r="K37" s="55">
         <f>IF($F37="","",$F37/$I37)</f>
         <v/>
       </c>
-      <c r="L37" s="6">
+      <c r="L37" s="55">
         <f>IF($G37="","",$G37/$I37)</f>
         <v/>
       </c>
-      <c r="M37" s="7">
+      <c r="M37" s="56">
         <f>IF($F37="","",$F37*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N37" s="6" t="n">
+      <c r="N37" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O37" s="11" t="n">
+      <c r="O37" s="58" t="n">
         <v>41</v>
       </c>
-      <c r="P37" s="11" t="n">
+      <c r="P37" s="58" t="n">
         <v>10.66</v>
       </c>
       <c r="Q37" s="12" t="inlineStr">
@@ -4117,7 +4145,7 @@
       <c r="Y37" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z37" s="8">
+      <c r="Z37" s="57">
         <f>IF($G37="","",$G37/$Y37)</f>
         <v/>
       </c>
@@ -4132,25 +4160,25 @@
           <t>LACOSTE sneakers P.42 — neuves</t>
         </is>
       </c>
-      <c r="B38" s="14" t="n">
+      <c r="B38" s="59" t="n">
         <v>57.51</v>
       </c>
-      <c r="C38" s="15">
+      <c r="C38" s="60">
         <f>$B38+$Y38*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D38" s="16">
+      <c r="D38" s="61">
         <f>$C38/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E38" s="15">
+      <c r="E38" s="60">
         <f>CEILING($D38*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F38" s="17" t="n">
+      <c r="F38" s="62" t="n">
         <v>70</v>
       </c>
-      <c r="G38" s="17">
+      <c r="G38" s="62">
         <f>IF($F38="","",$F38-$C38-$M38-$N38)</f>
         <v/>
       </c>
@@ -4161,29 +4189,29 @@
       <c r="I38" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J38" s="15">
+      <c r="J38" s="60">
         <f>$C38/$I38</f>
         <v/>
       </c>
-      <c r="K38" s="15">
+      <c r="K38" s="60">
         <f>IF($F38="","",$F38/$I38)</f>
         <v/>
       </c>
-      <c r="L38" s="15">
+      <c r="L38" s="60">
         <f>IF($G38="","",$G38/$I38)</f>
         <v/>
       </c>
-      <c r="M38" s="16">
+      <c r="M38" s="61">
         <f>IF($F38="","",$F38*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N38" s="15" t="n">
+      <c r="N38" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="O38" s="20" t="n">
+      <c r="O38" s="63" t="n">
         <v>45</v>
       </c>
-      <c r="P38" s="20" t="n">
+      <c r="P38" s="63" t="n">
         <v>11.7</v>
       </c>
       <c r="Q38" s="21" t="inlineStr">
@@ -4225,7 +4253,7 @@
       <c r="Y38" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="Z38" s="17">
+      <c r="Z38" s="62">
         <f>IF($G38="","",$G38/$Y38)</f>
         <v/>
       </c>
@@ -4240,25 +4268,25 @@
           <t>Pompe immergée ROBBY VP550W noir et bleu — produit d'occasion</t>
         </is>
       </c>
-      <c r="B39" s="5" t="n">
+      <c r="B39" s="54" t="n">
         <v>35.9</v>
       </c>
-      <c r="C39" s="6">
+      <c r="C39" s="55">
         <f>$B39</f>
         <v/>
       </c>
-      <c r="D39" s="7">
+      <c r="D39" s="56">
         <f>$C39/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E39" s="6">
+      <c r="E39" s="55">
         <f>CEILING($D39*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F39" s="8" t="n">
+      <c r="F39" s="57" t="n">
         <v>45</v>
       </c>
-      <c r="G39" s="8">
+      <c r="G39" s="57">
         <f>IF($F39="","",$F39-$C39-$M39-$N39)</f>
         <v/>
       </c>
@@ -4269,23 +4297,23 @@
       <c r="I39" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J39" s="6">
+      <c r="J39" s="55">
         <f>$C39/$I39</f>
         <v/>
       </c>
-      <c r="K39" s="6">
+      <c r="K39" s="55">
         <f>IF($F39="","",$F39/$I39)</f>
         <v/>
       </c>
-      <c r="L39" s="6">
+      <c r="L39" s="55">
         <f>IF($G39="","",$G39/$I39)</f>
         <v/>
       </c>
-      <c r="M39" s="7">
+      <c r="M39" s="56">
         <f>IF($F39="","",$F39*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N39" s="6" t="n">
+      <c r="N39" s="55" t="n">
         <v>0</v>
       </c>
       <c r="O39" s="31" t="n"/>
@@ -4325,7 +4353,7 @@
       <c r="Y39" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z39" s="8">
+      <c r="Z39" s="57">
         <f>IF($G39="","",$G39/$Y39)</f>
         <v/>
       </c>
@@ -4340,25 +4368,25 @@
           <t>Pompe immergée ROBBY VP550W noir/gris — comme neuf, SOCLE CASSÉ</t>
         </is>
       </c>
-      <c r="B40" s="5" t="n">
+      <c r="B40" s="54" t="n">
         <v>28.29</v>
       </c>
-      <c r="C40" s="6">
+      <c r="C40" s="55">
         <f>$B40</f>
         <v/>
       </c>
-      <c r="D40" s="7">
+      <c r="D40" s="56">
         <f>$C40/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E40" s="6">
+      <c r="E40" s="55">
         <f>CEILING($D40*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F40" s="8" t="n">
+      <c r="F40" s="57" t="n">
         <v>35</v>
       </c>
-      <c r="G40" s="8">
+      <c r="G40" s="57">
         <f>IF($F40="","",$F40-$C40-$M40-$N40)</f>
         <v/>
       </c>
@@ -4369,23 +4397,23 @@
       <c r="I40" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J40" s="6">
+      <c r="J40" s="55">
         <f>$C40/$I40</f>
         <v/>
       </c>
-      <c r="K40" s="6">
+      <c r="K40" s="55">
         <f>IF($F40="","",$F40/$I40)</f>
         <v/>
       </c>
-      <c r="L40" s="6">
+      <c r="L40" s="55">
         <f>IF($G40="","",$G40/$I40)</f>
         <v/>
       </c>
-      <c r="M40" s="7">
+      <c r="M40" s="56">
         <f>IF($F40="","",$F40*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N40" s="6" t="n">
+      <c r="N40" s="55" t="n">
         <v>0</v>
       </c>
       <c r="O40" s="31" t="n"/>
@@ -4425,7 +4453,7 @@
       <c r="Y40" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z40" s="8">
+      <c r="Z40" s="57">
         <f>IF($G40="","",$G40/$Y40)</f>
         <v/>
       </c>
@@ -4440,25 +4468,25 @@
           <t>2 boosters Pokémon MEGA Storm Emeralda M6 — 5 cartes chacun — set sorti le 31/07/2026, publier vite</t>
         </is>
       </c>
-      <c r="B41" s="5" t="n">
+      <c r="B41" s="54" t="n">
         <v>12.74</v>
       </c>
-      <c r="C41" s="6">
+      <c r="C41" s="55">
         <f>$B41</f>
         <v/>
       </c>
-      <c r="D41" s="7">
+      <c r="D41" s="56">
         <f>$C41/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E41" s="6">
+      <c r="E41" s="55">
         <f>CEILING($D41*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F41" s="8" t="n">
+      <c r="F41" s="57" t="n">
         <v>19</v>
       </c>
-      <c r="G41" s="8">
+      <c r="G41" s="57">
         <f>IF($F41="","",$F41-$C41-$M41-$N41)</f>
         <v/>
       </c>
@@ -4469,23 +4497,23 @@
       <c r="I41" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J41" s="6">
+      <c r="J41" s="55">
         <f>$C41/$I41</f>
         <v/>
       </c>
-      <c r="K41" s="6">
+      <c r="K41" s="55">
         <f>IF($F41="","",$F41/$I41)</f>
         <v/>
       </c>
-      <c r="L41" s="6">
+      <c r="L41" s="55">
         <f>IF($G41="","",$G41/$I41)</f>
         <v/>
       </c>
-      <c r="M41" s="7">
+      <c r="M41" s="56">
         <f>IF($F41="","",$F41*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N41" s="6" t="n">
+      <c r="N41" s="55" t="n">
         <v>0</v>
       </c>
       <c r="O41" s="31" t="n"/>
@@ -4525,7 +4553,7 @@
       <c r="Y41" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z41" s="8">
+      <c r="Z41" s="57">
         <f>IF($G41="","",$G41/$Y41)</f>
         <v/>
       </c>
@@ -4540,23 +4568,23 @@
           <t>1 booster Pokémon High Class Pack MEGA Dream ex M2a — 10 cartes dans le booster</t>
         </is>
       </c>
-      <c r="B42" s="14" t="n">
+      <c r="B42" s="59" t="n">
         <v>12.95</v>
       </c>
-      <c r="C42" s="15">
+      <c r="C42" s="60">
         <f>$B42</f>
         <v/>
       </c>
-      <c r="D42" s="16">
+      <c r="D42" s="61">
         <f>$C42/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E42" s="15">
+      <c r="E42" s="60">
         <f>CEILING($D42*Paramètres!$B$24,1)</f>
         <v/>
       </c>
       <c r="F42" s="32" t="n"/>
-      <c r="G42" s="17">
+      <c r="G42" s="62">
         <f>IF($F42="","",$F42-$C42-$M42-$N42)</f>
         <v/>
       </c>
@@ -4567,23 +4595,23 @@
       <c r="I42" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J42" s="15">
+      <c r="J42" s="60">
         <f>$C42/$I42</f>
         <v/>
       </c>
-      <c r="K42" s="15">
+      <c r="K42" s="60">
         <f>IF($F42="","",$F42/$I42)</f>
         <v/>
       </c>
-      <c r="L42" s="15">
+      <c r="L42" s="60">
         <f>IF($G42="","",$G42/$I42)</f>
         <v/>
       </c>
-      <c r="M42" s="16">
+      <c r="M42" s="61">
         <f>IF($F42="","",$F42*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N42" s="15" t="n">
+      <c r="N42" s="60" t="n">
         <v>0</v>
       </c>
       <c r="O42" s="32" t="n"/>
@@ -4627,7 +4655,7 @@
       <c r="Y42" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="Z42" s="17">
+      <c r="Z42" s="62">
         <f>IF($G42="","",$G42/$Y42)</f>
         <v/>
       </c>
@@ -4642,23 +4670,23 @@
           <t>Pompe immergée ROBBY VP550W bleu et noir — occasion, NE MARCHE QU'EN MODE AUTO</t>
         </is>
       </c>
-      <c r="B43" s="14" t="n">
+      <c r="B43" s="59" t="n">
         <v>19.41</v>
       </c>
-      <c r="C43" s="15">
+      <c r="C43" s="60">
         <f>$B43</f>
         <v/>
       </c>
-      <c r="D43" s="16">
+      <c r="D43" s="61">
         <f>$C43/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E43" s="15">
+      <c r="E43" s="60">
         <f>CEILING($D43*Paramètres!$B$24,1)</f>
         <v/>
       </c>
       <c r="F43" s="32" t="n"/>
-      <c r="G43" s="17">
+      <c r="G43" s="62">
         <f>IF($F43="","",$F43-$C43-$M43-$N43)</f>
         <v/>
       </c>
@@ -4669,23 +4697,23 @@
       <c r="I43" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J43" s="15">
+      <c r="J43" s="60">
         <f>$C43/$I43</f>
         <v/>
       </c>
-      <c r="K43" s="15">
+      <c r="K43" s="60">
         <f>IF($F43="","",$F43/$I43)</f>
         <v/>
       </c>
-      <c r="L43" s="15">
+      <c r="L43" s="60">
         <f>IF($G43="","",$G43/$I43)</f>
         <v/>
       </c>
-      <c r="M43" s="16">
+      <c r="M43" s="61">
         <f>IF($F43="","",$F43*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N43" s="15" t="n">
+      <c r="N43" s="60" t="n">
         <v>0</v>
       </c>
       <c r="O43" s="32" t="n"/>
@@ -4729,7 +4757,7 @@
       <c r="Y43" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="Z43" s="17">
+      <c r="Z43" s="62">
         <f>IF($G43="","",$G43/$Y43)</f>
         <v/>
       </c>
@@ -4744,23 +4772,23 @@
           <t>Baskets NIKE Air Max Moto 2K P.44.5 — neuves</t>
         </is>
       </c>
-      <c r="B44" s="14" t="n">
+      <c r="B44" s="59" t="n">
         <v>50.4</v>
       </c>
-      <c r="C44" s="15">
+      <c r="C44" s="60">
         <f>$B44+$Y44*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D44" s="16">
+      <c r="D44" s="61">
         <f>$C44/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E44" s="15">
+      <c r="E44" s="60">
         <f>CEILING($D44*Paramètres!$B$24,1)</f>
         <v/>
       </c>
       <c r="F44" s="32" t="n"/>
-      <c r="G44" s="17">
+      <c r="G44" s="62">
         <f>IF($F44="","",$F44-$C44-$M44-$N44)</f>
         <v/>
       </c>
@@ -4771,29 +4799,29 @@
       <c r="I44" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J44" s="15">
+      <c r="J44" s="60">
         <f>$C44/$I44</f>
         <v/>
       </c>
-      <c r="K44" s="15">
+      <c r="K44" s="60">
         <f>IF($F44="","",$F44/$I44)</f>
         <v/>
       </c>
-      <c r="L44" s="15">
+      <c r="L44" s="60">
         <f>IF($G44="","",$G44/$I44)</f>
         <v/>
       </c>
-      <c r="M44" s="16">
+      <c r="M44" s="61">
         <f>IF($F44="","",$F44*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N44" s="15" t="n">
+      <c r="N44" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="O44" s="20" t="n">
+      <c r="O44" s="63" t="n">
         <v>40</v>
       </c>
-      <c r="P44" s="20" t="n">
+      <c r="P44" s="63" t="n">
         <v>10.4</v>
       </c>
       <c r="Q44" s="21" t="inlineStr">
@@ -4835,7 +4863,7 @@
       <c r="Y44" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="Z44" s="17">
+      <c r="Z44" s="62">
         <f>IF($G44="","",$G44/$Y44)</f>
         <v/>
       </c>
@@ -4850,23 +4878,23 @@
           <t>Baskets HOKA P.37 1/3 — neuves</t>
         </is>
       </c>
-      <c r="B45" s="14" t="n">
+      <c r="B45" s="59" t="n">
         <v>63</v>
       </c>
-      <c r="C45" s="15">
+      <c r="C45" s="60">
         <f>$B45+$Y45*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D45" s="16">
+      <c r="D45" s="61">
         <f>$C45/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E45" s="15">
+      <c r="E45" s="60">
         <f>CEILING($D45*Paramètres!$B$24,1)</f>
         <v/>
       </c>
       <c r="F45" s="32" t="n"/>
-      <c r="G45" s="17">
+      <c r="G45" s="62">
         <f>IF($F45="","",$F45-$C45-$M45-$N45)</f>
         <v/>
       </c>
@@ -4877,29 +4905,29 @@
       <c r="I45" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J45" s="15">
+      <c r="J45" s="60">
         <f>$C45/$I45</f>
         <v/>
       </c>
-      <c r="K45" s="15">
+      <c r="K45" s="60">
         <f>IF($F45="","",$F45/$I45)</f>
         <v/>
       </c>
-      <c r="L45" s="15">
+      <c r="L45" s="60">
         <f>IF($G45="","",$G45/$I45)</f>
         <v/>
       </c>
-      <c r="M45" s="16">
+      <c r="M45" s="61">
         <f>IF($F45="","",$F45*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N45" s="15" t="n">
+      <c r="N45" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="O45" s="20" t="n">
+      <c r="O45" s="63" t="n">
         <v>50</v>
       </c>
-      <c r="P45" s="20" t="n">
+      <c r="P45" s="63" t="n">
         <v>13</v>
       </c>
       <c r="Q45" s="21" t="inlineStr">
@@ -4941,7 +4969,7 @@
       <c r="Y45" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="Z45" s="17">
+      <c r="Z45" s="62">
         <f>IF($G45="","",$G45/$Y45)</f>
         <v/>
       </c>
@@ -4956,21 +4984,21 @@
           <t>TOTAL — 40 lots</t>
         </is>
       </c>
-      <c r="B46" s="34">
+      <c r="B46" s="69">
         <f>SUM(B6:B45)</f>
         <v/>
       </c>
-      <c r="C46" s="34">
+      <c r="C46" s="69">
         <f>SUM(C6:C45)</f>
         <v/>
       </c>
       <c r="D46" s="35" t="n"/>
       <c r="E46" s="35" t="n"/>
-      <c r="F46" s="34">
+      <c r="F46" s="69">
         <f>SUM(F6:F45)</f>
         <v/>
       </c>
-      <c r="G46" s="34">
+      <c r="G46" s="69">
         <f>SUM(G6:G45)</f>
         <v/>
       </c>
@@ -4978,18 +5006,18 @@
         <f>G46/C46</f>
         <v/>
       </c>
-      <c r="I46" s="37">
+      <c r="I46" s="70">
         <f>SUM(I6:I45)</f>
         <v/>
       </c>
       <c r="J46" s="35" t="n"/>
       <c r="K46" s="35" t="n"/>
       <c r="L46" s="35" t="n"/>
-      <c r="M46" s="34">
+      <c r="M46" s="69">
         <f>SUM(M6:M45)</f>
         <v/>
       </c>
-      <c r="N46" s="34">
+      <c r="N46" s="69">
         <f>SUM(N6:N45)</f>
         <v/>
       </c>
@@ -5004,7 +5032,7 @@
       <c r="W46" s="35" t="n"/>
       <c r="X46" s="35" t="n"/>
       <c r="Y46" s="35" t="n"/>
-      <c r="Z46" s="34">
+      <c r="Z46" s="69">
         <f>G46/SUM(Y6:Y45)</f>
         <v/>
       </c>
@@ -5063,7 +5091,7 @@
           <t>Marchandise ADN</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="55" t="n">
         <v>1637.35</v>
       </c>
     </row>
@@ -5073,7 +5101,7 @@
           <t>Livraison ADN</t>
         </is>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="55">
         <f>Paramètres!B11</f>
         <v/>
       </c>
@@ -5084,7 +5112,7 @@
           <t>Achats hors ADN (pompes, Pokémon)</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="55" t="n">
         <v>178.53</v>
       </c>
     </row>
@@ -5094,7 +5122,7 @@
           <t>TOTAL ENGAGÉ</t>
         </is>
       </c>
-      <c r="B7" s="34">
+      <c r="B7" s="69">
         <f>'Stock complet'!C46</f>
         <v/>
       </c>
@@ -5112,7 +5140,7 @@
           <t>Chiffre d'affaires attendu</t>
         </is>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="57">
         <f>'Stock complet'!F46</f>
         <v/>
       </c>
@@ -5128,7 +5156,7 @@
           <t>− URSSAF + CFP</t>
         </is>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="56">
         <f>-'Stock complet'!M46</f>
         <v/>
       </c>
@@ -5139,7 +5167,7 @@
           <t>− Commission carte</t>
         </is>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="55">
         <f>-'Stock complet'!N46</f>
         <v/>
       </c>
@@ -5149,7 +5177,7 @@
         <f> Marge brute</f>
         <v/>
       </c>
-      <c r="B13" s="34">
+      <c r="B13" s="69">
         <f>'Stock complet'!G46</f>
         <v/>
       </c>
@@ -5160,7 +5188,7 @@
           <t>− Emballage</t>
         </is>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="55">
         <f>-Paramètres!B20*Paramètres!B21</f>
         <v/>
       </c>
@@ -5171,7 +5199,7 @@
           <t>− Frais fixe carte</t>
         </is>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="55">
         <f>-Paramètres!B8*Paramètres!B21</f>
         <v/>
       </c>
@@ -5181,7 +5209,7 @@
         <f> Marge avant impôt</f>
         <v/>
       </c>
-      <c r="B16" s="34">
+      <c r="B16" s="69">
         <f>B13+B14+B15</f>
         <v/>
       </c>
@@ -5192,7 +5220,7 @@
           <t>Base imposable</t>
         </is>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="55">
         <f>B10*(1-Paramètres!B16)</f>
         <v/>
       </c>
@@ -5203,7 +5231,7 @@
           <t>− Impôt estimé</t>
         </is>
       </c>
-      <c r="B18" s="6">
+      <c r="B18" s="55">
         <f>-B17*Paramètres!B17</f>
         <v/>
       </c>
@@ -5213,7 +5241,7 @@
         <f> CE QUI RESTE</f>
         <v/>
       </c>
-      <c r="B19" s="41">
+      <c r="B19" s="71">
         <f>B16+B18</f>
         <v/>
       </c>
@@ -5231,7 +5259,7 @@
           <t>Marge nette / capital engagé</t>
         </is>
       </c>
-      <c r="B22" s="42">
+      <c r="B22" s="72">
         <f>B19/B7</f>
         <v/>
       </c>
@@ -5253,7 +5281,7 @@
           <t>Taux de marge nette sur le CA</t>
         </is>
       </c>
-      <c r="B24" s="42">
+      <c r="B24" s="72">
         <f>B19/B10</f>
         <v/>
       </c>
@@ -5276,7 +5304,7 @@
           <t>Shopify + Claude, aujourd'hui</t>
         </is>
       </c>
-      <c r="B27" s="6">
+      <c r="B27" s="55">
         <f>Paramètres!B30</f>
         <v/>
       </c>
@@ -5292,7 +5320,7 @@
           <t>Shopify + Claude, à partir du 11/11/2026</t>
         </is>
       </c>
-      <c r="B28" s="6">
+      <c r="B28" s="55">
         <f>Paramètres!B31</f>
         <v/>
       </c>
@@ -5308,7 +5336,7 @@
           <t>Soit par an, à partir de novembre</t>
         </is>
       </c>
-      <c r="B29" s="34">
+      <c r="B29" s="69">
         <f>Paramètres!B31*12</f>
         <v/>
       </c>
@@ -5319,7 +5347,7 @@
           <t>CA mensuel nécessaire pour les couvrir</t>
         </is>
       </c>
-      <c r="B30" s="41">
+      <c r="B30" s="71">
         <f>Paramètres!B31/B24</f>
         <v/>
       </c>
@@ -5335,7 +5363,7 @@
           <t>Marge du stock entier</t>
         </is>
       </c>
-      <c r="B31" s="6">
+      <c r="B31" s="55">
         <f>B19</f>
         <v/>
       </c>
@@ -5351,7 +5379,7 @@
           <t>Mois de charges couverts par tout le stock</t>
         </is>
       </c>
-      <c r="B32" s="44">
+      <c r="B32" s="73">
         <f>B19/Paramètres!B31</f>
         <v/>
       </c>
@@ -5479,7 +5507,7 @@
           <t>Cotisations URSSAF (achat-revente BIC)</t>
         </is>
       </c>
-      <c r="B5" s="46" t="n">
+      <c r="B5" s="74" t="n">
         <v>0.123</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -5494,7 +5522,7 @@
           <t>CFP — formation professionnelle</t>
         </is>
       </c>
-      <c r="B6" s="46" t="n">
+      <c r="B6" s="74" t="n">
         <v>0.001</v>
       </c>
     </row>
@@ -5504,7 +5532,7 @@
           <t>Commission carte Shopify Payments</t>
         </is>
       </c>
-      <c r="B7" s="46" t="n">
+      <c r="B7" s="74" t="n">
         <v>0.015</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -5519,7 +5547,7 @@
           <t>Frais fixe par transaction carte</t>
         </is>
       </c>
-      <c r="B8" s="47" t="n">
+      <c r="B8" s="75" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -5536,7 +5564,7 @@
           <t>Total des factures de livraison ADN</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="54" t="n">
         <v>127.8</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -5566,7 +5594,7 @@
           <t>Livraison par unité de vente</t>
         </is>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="55">
         <f>B11/B12</f>
         <v/>
       </c>
@@ -5589,7 +5617,7 @@
           <t>Abattement forfaitaire</t>
         </is>
       </c>
-      <c r="B16" s="46" t="n">
+      <c r="B16" s="74" t="n">
         <v>0.71</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -5604,7 +5632,7 @@
           <t>Tranche marginale du foyer</t>
         </is>
       </c>
-      <c r="B17" s="46" t="n">
+      <c r="B17" s="74" t="n">
         <v>0.11</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -5626,7 +5654,7 @@
           <t>Emballage par colis</t>
         </is>
       </c>
-      <c r="B20" s="47" t="n">
+      <c r="B20" s="75" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5675,7 +5703,7 @@
           <t>Abonnement Shopify — aujourd'hui</t>
         </is>
       </c>
-      <c r="B27" s="47" t="n">
+      <c r="B27" s="75" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -5690,7 +5718,7 @@
           <t>Abonnement Shopify — à partir du 11/11/2026</t>
         </is>
       </c>
-      <c r="B28" s="47" t="n">
+      <c r="B28" s="75" t="n">
         <v>36</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -5705,7 +5733,7 @@
           <t>Abonnement Claude</t>
         </is>
       </c>
-      <c r="B29" s="47" t="n">
+      <c r="B29" s="75" t="n">
         <v>22</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -5720,7 +5748,7 @@
           <t>Total mensuel aujourd'hui</t>
         </is>
       </c>
-      <c r="B30" s="50">
+      <c r="B30" s="76">
         <f>B27+B29</f>
         <v/>
       </c>
@@ -5731,7 +5759,7 @@
           <t>Total mensuel à partir du 11/11/2026</t>
         </is>
       </c>
-      <c r="B31" s="50">
+      <c r="B31" s="76">
         <f>B28+B29</f>
         <v/>
       </c>
@@ -5754,7 +5782,7 @@
           <t>CFE — cotisation foncière des entreprises</t>
         </is>
       </c>
-      <c r="B34" s="47" t="n">
+      <c r="B34" s="75" t="n">
         <v>0</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -5791,7 +5819,7 @@
           <t>Shopify Payments — frais fixe</t>
         </is>
       </c>
-      <c r="B38" s="47" t="n">
+      <c r="B38" s="75" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -5816,7 +5844,7 @@
           <t>PayPal — frais fixe</t>
         </is>
       </c>
-      <c r="B40" s="47" t="n">
+      <c r="B40" s="75" t="n">
         <v>0.35</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -5861,7 +5889,7 @@
           <t>Coefficient de marge — Shopify Payments</t>
         </is>
       </c>
-      <c r="B44" s="52">
+      <c r="B44" s="77">
         <f>1-B5-B6-B37</f>
         <v/>
       </c>
@@ -5877,7 +5905,7 @@
           <t>Coefficient de marge — PayPal</t>
         </is>
       </c>
-      <c r="B45" s="52">
+      <c r="B45" s="77">
         <f>1-B5-B6-B39</f>
         <v/>
       </c>
@@ -5893,7 +5921,7 @@
           <t>Coefficient de marge — hors carte</t>
         </is>
       </c>
-      <c r="B46" s="52">
+      <c r="B46" s="77">
         <f>1-B5-B6</f>
         <v/>
       </c>
@@ -5909,7 +5937,7 @@
           <t>Écart PayPal / Shopify Payments sur une vente à 89 €</t>
         </is>
       </c>
-      <c r="B47" s="6">
+      <c r="B47" s="55">
         <f>89*(B39-B37)+(B40-B38)</f>
         <v/>
       </c>
@@ -6042,16 +6070,16 @@
           <t>Lot de 12 paires de tongs HAVAIANAS fuchsia 35/36 — neuf</t>
         </is>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="G5" s="55" t="n">
         <v>80</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="H5" s="55" t="n">
         <v>20.8</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="I5" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="J5" s="55" t="n">
         <v>100.8</v>
       </c>
     </row>
@@ -6086,16 +6114,16 @@
           <t>Veste en jean ARMANI EXCHANGE T.S — neuve</t>
         </is>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="G6" s="55" t="n">
         <v>20</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="H6" s="55" t="n">
         <v>5.2</v>
       </c>
-      <c r="I6" s="6" t="n">
+      <c r="I6" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="J6" s="55" t="n">
         <v>25.2</v>
       </c>
     </row>
@@ -6130,16 +6158,16 @@
           <t>Lot de 4 gilets de flottaison MRS.ERTHA 3-6 ans — neuf</t>
         </is>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="G7" s="55" t="n">
         <v>30</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="H7" s="55" t="n">
         <v>7.8</v>
       </c>
-      <c r="I7" s="6" t="n">
+      <c r="I7" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="J7" s="55" t="n">
         <v>37.8</v>
       </c>
     </row>
@@ -6174,16 +6202,16 @@
           <t>Robe SANDRO T.40 — neuve</t>
         </is>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="G8" s="55" t="n">
         <v>30</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="H8" s="55" t="n">
         <v>7.8</v>
       </c>
-      <c r="I8" s="6" t="n">
+      <c r="I8" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="J8" s="55" t="n">
         <v>37.8</v>
       </c>
     </row>
@@ -6218,16 +6246,16 @@
           <t>Baskets HOKA P.37 1/3 — neuves</t>
         </is>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="G9" s="55" t="n">
         <v>50</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="H9" s="55" t="n">
         <v>13</v>
       </c>
-      <c r="I9" s="6" t="n">
+      <c r="I9" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="J9" s="55" t="n">
         <v>63</v>
       </c>
     </row>
@@ -6262,16 +6290,16 @@
           <t>Baskets NIKE Air Max Moto 2K P.44.5 — neuves</t>
         </is>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="G10" s="55" t="n">
         <v>40</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="H10" s="55" t="n">
         <v>10.4</v>
       </c>
-      <c r="I10" s="6" t="n">
+      <c r="I10" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="J10" s="55" t="n">
         <v>50.4</v>
       </c>
     </row>
@@ -6306,16 +6334,16 @@
           <t>Chaussures HOGAN P.36 — traces d'essayage</t>
         </is>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="G11" s="55" t="n">
         <v>10</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="H11" s="55" t="n">
         <v>2.6</v>
       </c>
-      <c r="I11" s="6" t="n">
+      <c r="I11" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="J11" s="55" t="n">
         <v>12.6</v>
       </c>
     </row>
@@ -6350,16 +6378,16 @@
           <t>NEW BALANCE G19064IK Alkaline Green P.38½ — neuves avec boîte</t>
         </is>
       </c>
-      <c r="G12" s="6" t="n">
+      <c r="G12" s="55" t="n">
         <v>60</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="H12" s="55" t="n">
         <v>15.6</v>
       </c>
-      <c r="I12" s="6" t="n">
+      <c r="I12" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="J12" s="55" t="n">
         <v>75.59999999999999</v>
       </c>
     </row>
@@ -6394,16 +6422,16 @@
           <t>Lot de 2 paires ADIDAS Predator Edge P.48 2/3 — neuves</t>
         </is>
       </c>
-      <c r="G13" s="6" t="n">
+      <c r="G13" s="55" t="n">
         <v>30</v>
       </c>
-      <c r="H13" s="6" t="n">
+      <c r="H13" s="55" t="n">
         <v>7.8</v>
       </c>
-      <c r="I13" s="6" t="n">
+      <c r="I13" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="6" t="n">
+      <c r="J13" s="55" t="n">
         <v>37.8</v>
       </c>
     </row>
@@ -6438,16 +6466,16 @@
           <t>Short BA&amp;SH Fegor T.34 — neuf</t>
         </is>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="G14" s="55" t="n">
         <v>40</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="H14" s="55" t="n">
         <v>10.4</v>
       </c>
-      <c r="I14" s="6" t="n">
+      <c r="I14" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J14" s="6" t="n">
+      <c r="J14" s="55" t="n">
         <v>50.4</v>
       </c>
     </row>
@@ -6482,16 +6510,16 @@
           <t>Jupe midi SONIA RYKIEL T.34 — neuve</t>
         </is>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="G15" s="55" t="n">
         <v>30</v>
       </c>
-      <c r="H15" s="6" t="n">
+      <c r="H15" s="55" t="n">
         <v>7.8</v>
       </c>
-      <c r="I15" s="6" t="n">
+      <c r="I15" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="J15" s="55" t="n">
         <v>37.8</v>
       </c>
     </row>
@@ -6526,16 +6554,16 @@
           <t>Sac demi-lune nylon noir KARL LAGERFELD JEANS — neuf avec étiquette</t>
         </is>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="G16" s="55" t="n">
         <v>40</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="H16" s="55" t="n">
         <v>10.4</v>
       </c>
-      <c r="I16" s="6" t="n">
+      <c r="I16" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="6" t="n">
+      <c r="J16" s="55" t="n">
         <v>50.4</v>
       </c>
     </row>
@@ -6570,16 +6598,16 @@
           <t>ADIDAS x STELLA McCARTNEY ASMC Ultraboost 21 P.36 — modèle d'exposition</t>
         </is>
       </c>
-      <c r="G17" s="6" t="n">
+      <c r="G17" s="55" t="n">
         <v>30</v>
       </c>
-      <c r="H17" s="6" t="n">
+      <c r="H17" s="55" t="n">
         <v>7.8</v>
       </c>
-      <c r="I17" s="6" t="n">
+      <c r="I17" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J17" s="6" t="n">
+      <c r="J17" s="55" t="n">
         <v>37.8</v>
       </c>
     </row>
@@ -6614,16 +6642,16 @@
           <t>Ballerines MASSIMO DUTTI P.41 — traces d'essayage</t>
         </is>
       </c>
-      <c r="G18" s="6" t="n">
+      <c r="G18" s="55" t="n">
         <v>20</v>
       </c>
-      <c r="H18" s="6" t="n">
+      <c r="H18" s="55" t="n">
         <v>5.2</v>
       </c>
-      <c r="I18" s="6" t="n">
+      <c r="I18" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J18" s="6" t="n">
+      <c r="J18" s="55" t="n">
         <v>25.2</v>
       </c>
     </row>
@@ -6658,16 +6686,16 @@
           <t>NEW BALANCE sneakers P.38 — neuves</t>
         </is>
       </c>
-      <c r="G19" s="6" t="n">
+      <c r="G19" s="55" t="n">
         <v>30</v>
       </c>
-      <c r="H19" s="6" t="n">
+      <c r="H19" s="55" t="n">
         <v>7.8</v>
       </c>
-      <c r="I19" s="6" t="n">
+      <c r="I19" s="55" t="n">
         <v>0.54</v>
       </c>
-      <c r="J19" s="6" t="n">
+      <c r="J19" s="55" t="n">
         <v>38.34</v>
       </c>
     </row>
@@ -6702,16 +6730,16 @@
           <t>LACOSTE sneakers P.42 — neuves</t>
         </is>
       </c>
-      <c r="G20" s="6" t="n">
+      <c r="G20" s="55" t="n">
         <v>45</v>
       </c>
-      <c r="H20" s="6" t="n">
+      <c r="H20" s="55" t="n">
         <v>11.7</v>
       </c>
-      <c r="I20" s="6" t="n">
+      <c r="I20" s="55" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="J20" s="6" t="n">
+      <c r="J20" s="55" t="n">
         <v>57.51</v>
       </c>
     </row>
@@ -6746,16 +6774,16 @@
           <t>EMPORIO ARMANI baskets P.36 — neuves</t>
         </is>
       </c>
-      <c r="G21" s="6" t="n">
+      <c r="G21" s="55" t="n">
         <v>40</v>
       </c>
-      <c r="H21" s="6" t="n">
+      <c r="H21" s="55" t="n">
         <v>10.4</v>
       </c>
-      <c r="I21" s="6" t="n">
+      <c r="I21" s="55" t="n">
         <v>0.72</v>
       </c>
-      <c r="J21" s="6" t="n">
+      <c r="J21" s="55" t="n">
         <v>51.12</v>
       </c>
     </row>
@@ -6790,16 +6818,16 @@
           <t>GEOX baskets P.35 — neuves</t>
         </is>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="G22" s="55" t="n">
         <v>17</v>
       </c>
-      <c r="H22" s="6" t="n">
+      <c r="H22" s="55" t="n">
         <v>4.42</v>
       </c>
-      <c r="I22" s="6" t="n">
+      <c r="I22" s="55" t="n">
         <v>0.31</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="J22" s="55" t="n">
         <v>21.73</v>
       </c>
     </row>
@@ -6834,16 +6862,16 @@
           <t>NEW BALANCE baskets montantes P.44 — neuves</t>
         </is>
       </c>
-      <c r="G23" s="6" t="n">
+      <c r="G23" s="55" t="n">
         <v>40</v>
       </c>
-      <c r="H23" s="6" t="n">
+      <c r="H23" s="55" t="n">
         <v>10.4</v>
       </c>
-      <c r="I23" s="6" t="n">
+      <c r="I23" s="55" t="n">
         <v>0.72</v>
       </c>
-      <c r="J23" s="6" t="n">
+      <c r="J23" s="55" t="n">
         <v>51.12</v>
       </c>
     </row>
@@ -6878,16 +6906,16 @@
           <t>TOMMY JEANS baskets basses P.40 — neuves</t>
         </is>
       </c>
-      <c r="G24" s="6" t="n">
+      <c r="G24" s="55" t="n">
         <v>41</v>
       </c>
-      <c r="H24" s="6" t="n">
+      <c r="H24" s="55" t="n">
         <v>10.66</v>
       </c>
-      <c r="I24" s="6" t="n">
+      <c r="I24" s="55" t="n">
         <v>0.74</v>
       </c>
-      <c r="J24" s="6" t="n">
+      <c r="J24" s="55" t="n">
         <v>52.4</v>
       </c>
     </row>
@@ -6922,16 +6950,16 @@
           <t>PHILIPP PLEIN SPORT baskets montantes P.40 — neuves</t>
         </is>
       </c>
-      <c r="G25" s="6" t="n">
+      <c r="G25" s="55" t="n">
         <v>45</v>
       </c>
-      <c r="H25" s="6" t="n">
+      <c r="H25" s="55" t="n">
         <v>11.7</v>
       </c>
-      <c r="I25" s="6" t="n">
+      <c r="I25" s="55" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="J25" s="6" t="n">
+      <c r="J25" s="55" t="n">
         <v>57.51</v>
       </c>
     </row>
@@ -6966,16 +6994,16 @@
           <t>PIER ANTONIO GASPARI robe droite bleu marine T.42 — neuve</t>
         </is>
       </c>
-      <c r="G26" s="6" t="n">
+      <c r="G26" s="55" t="n">
         <v>20</v>
       </c>
-      <c r="H26" s="6" t="n">
+      <c r="H26" s="55" t="n">
         <v>5.2</v>
       </c>
-      <c r="I26" s="6" t="n">
+      <c r="I26" s="55" t="n">
         <v>0.36</v>
       </c>
-      <c r="J26" s="6" t="n">
+      <c r="J26" s="55" t="n">
         <v>25.56</v>
       </c>
     </row>
@@ -7010,16 +7038,16 @@
           <t>ELISABETTA FRANCHI robe asymétrique viscose T.46 IT — neuve</t>
         </is>
       </c>
-      <c r="G27" s="6" t="n">
+      <c r="G27" s="55" t="n">
         <v>16</v>
       </c>
-      <c r="H27" s="6" t="n">
+      <c r="H27" s="55" t="n">
         <v>4.16</v>
       </c>
-      <c r="I27" s="6" t="n">
+      <c r="I27" s="55" t="n">
         <v>0.29</v>
       </c>
-      <c r="J27" s="6" t="n">
+      <c r="J27" s="55" t="n">
         <v>20.45</v>
       </c>
     </row>
@@ -7054,16 +7082,16 @@
           <t>CHIARA FERRAGNI robe bustier courte T.M — neuve</t>
         </is>
       </c>
-      <c r="G28" s="6" t="n">
+      <c r="G28" s="55" t="n">
         <v>25</v>
       </c>
-      <c r="H28" s="6" t="n">
+      <c r="H28" s="55" t="n">
         <v>6.5</v>
       </c>
-      <c r="I28" s="6" t="n">
+      <c r="I28" s="55" t="n">
         <v>0.45</v>
       </c>
-      <c r="J28" s="6" t="n">
+      <c r="J28" s="55" t="n">
         <v>31.95</v>
       </c>
     </row>
@@ -7098,16 +7126,16 @@
           <t>SALOMON X Ultra 5 Mid GTX P.44 — neuves</t>
         </is>
       </c>
-      <c r="G29" s="6" t="n">
+      <c r="G29" s="55" t="n">
         <v>60</v>
       </c>
-      <c r="H29" s="6" t="n">
+      <c r="H29" s="55" t="n">
         <v>15.6</v>
       </c>
-      <c r="I29" s="6" t="n">
+      <c r="I29" s="55" t="n">
         <v>1.08</v>
       </c>
-      <c r="J29" s="6" t="n">
+      <c r="J29" s="55" t="n">
         <v>76.68000000000001</v>
       </c>
     </row>
@@ -7142,16 +7170,16 @@
           <t>Lot de 4 toupies BEYBLADE HASBRO</t>
         </is>
       </c>
-      <c r="G30" s="6" t="n">
+      <c r="G30" s="55" t="n">
         <v>15</v>
       </c>
-      <c r="H30" s="6" t="n">
+      <c r="H30" s="55" t="n">
         <v>3.9</v>
       </c>
-      <c r="I30" s="6" t="n">
+      <c r="I30" s="55" t="n">
         <v>0.27</v>
       </c>
-      <c r="J30" s="6" t="n">
+      <c r="J30" s="55" t="n">
         <v>19.17</v>
       </c>
     </row>
@@ -7186,16 +7214,16 @@
           <t>Lot de 4 toupies BEYBLADE HASBRO</t>
         </is>
       </c>
-      <c r="G31" s="6" t="n">
+      <c r="G31" s="55" t="n">
         <v>30</v>
       </c>
-      <c r="H31" s="6" t="n">
+      <c r="H31" s="55" t="n">
         <v>7.8</v>
       </c>
-      <c r="I31" s="6" t="n">
+      <c r="I31" s="55" t="n">
         <v>0.54</v>
       </c>
-      <c r="J31" s="6" t="n">
+      <c r="J31" s="55" t="n">
         <v>38.34</v>
       </c>
     </row>
@@ -7230,16 +7258,16 @@
           <t>T-shirt BALENCIAGA T.2 — neuf</t>
         </is>
       </c>
-      <c r="G32" s="6" t="n">
+      <c r="G32" s="55" t="n">
         <v>90</v>
       </c>
-      <c r="H32" s="6" t="n">
+      <c r="H32" s="55" t="n">
         <v>23.4</v>
       </c>
-      <c r="I32" s="6" t="n">
+      <c r="I32" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J32" s="6" t="n">
+      <c r="J32" s="55" t="n">
         <v>113.4</v>
       </c>
     </row>
@@ -7274,16 +7302,16 @@
           <t>Blazer noir KARL LAGERFELD T.36 FR — neuf avec étiquette</t>
         </is>
       </c>
-      <c r="G33" s="6" t="n">
+      <c r="G33" s="55" t="n">
         <v>40</v>
       </c>
-      <c r="H33" s="6" t="n">
+      <c r="H33" s="55" t="n">
         <v>10.4</v>
       </c>
-      <c r="I33" s="6" t="n">
+      <c r="I33" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J33" s="6" t="n">
+      <c r="J33" s="55" t="n">
         <v>50.4</v>
       </c>
     </row>
@@ -7318,16 +7346,16 @@
           <t>ADIDAS Yeezy 700 V3 Mono Safflower T.38 — occasion</t>
         </is>
       </c>
-      <c r="G34" s="6" t="n">
+      <c r="G34" s="55" t="n">
         <v>50</v>
       </c>
-      <c r="H34" s="6" t="n">
+      <c r="H34" s="55" t="n">
         <v>13</v>
       </c>
-      <c r="I34" s="6" t="n">
+      <c r="I34" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J34" s="6" t="n">
+      <c r="J34" s="55" t="n">
         <v>63</v>
       </c>
     </row>
@@ -7362,16 +7390,16 @@
           <t>Lot de 6 vêtements femme MORGAN T.40 et L — neuf</t>
         </is>
       </c>
-      <c r="G35" s="6" t="n">
+      <c r="G35" s="55" t="n">
         <v>30</v>
       </c>
-      <c r="H35" s="6" t="n">
+      <c r="H35" s="55" t="n">
         <v>7.8</v>
       </c>
-      <c r="I35" s="6" t="n">
+      <c r="I35" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J35" s="6" t="n">
+      <c r="J35" s="55" t="n">
         <v>37.8</v>
       </c>
     </row>
@@ -7406,16 +7434,16 @@
           <t>Demi-bottes FORMA Legacy Waterproof T.45 noir — neuves</t>
         </is>
       </c>
-      <c r="G36" s="6" t="n">
+      <c r="G36" s="55" t="n">
         <v>50</v>
       </c>
-      <c r="H36" s="6" t="n">
+      <c r="H36" s="55" t="n">
         <v>13</v>
       </c>
-      <c r="I36" s="6" t="n">
+      <c r="I36" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J36" s="6" t="n">
+      <c r="J36" s="55" t="n">
         <v>63</v>
       </c>
     </row>
@@ -7450,16 +7478,16 @@
           <t>Combinaison de pluie BMW Overall ProRain unisexe XL — neuve</t>
         </is>
       </c>
-      <c r="G37" s="6" t="n">
+      <c r="G37" s="55" t="n">
         <v>60</v>
       </c>
-      <c r="H37" s="6" t="n">
+      <c r="H37" s="55" t="n">
         <v>8.57</v>
       </c>
-      <c r="I37" s="6" t="n">
+      <c r="I37" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J37" s="6" t="n">
+      <c r="J37" s="55" t="n">
         <v>68.56999999999999</v>
       </c>
     </row>
@@ -7494,16 +7522,16 @@
           <t>Lot de 20 paires de sandales et tongs RELIFE / TOMMY JEANS — neuf</t>
         </is>
       </c>
-      <c r="G38" s="6" t="n">
+      <c r="G38" s="55" t="n">
         <v>45</v>
       </c>
-      <c r="H38" s="6" t="n">
+      <c r="H38" s="55" t="n">
         <v>11.7</v>
       </c>
-      <c r="I38" s="6" t="n">
+      <c r="I38" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J38" s="6" t="n">
+      <c r="J38" s="55" t="n">
         <v>56.7</v>
       </c>
     </row>
@@ -7518,19 +7546,19 @@
           <t>TOTAL MARCHANDISE</t>
         </is>
       </c>
-      <c r="G39" s="34">
+      <c r="G39" s="69">
         <f>SUM(G5:G38)</f>
         <v/>
       </c>
-      <c r="H39" s="34">
+      <c r="H39" s="69">
         <f>SUM(H5:H38)</f>
         <v/>
       </c>
-      <c r="I39" s="34">
+      <c r="I39" s="69">
         <f>SUM(I5:I38)</f>
         <v/>
       </c>
-      <c r="J39" s="34">
+      <c r="J39" s="69">
         <f>SUM(J5:J38)</f>
         <v/>
       </c>
@@ -7600,7 +7628,7 @@
           <t>Colissimo Point Relais — assurance et signature</t>
         </is>
       </c>
-      <c r="F43" s="6" t="n">
+      <c r="F43" s="55" t="n">
         <v>19.9</v>
       </c>
     </row>
@@ -7630,7 +7658,7 @@
           <t>Colissimo Point Relais — assurance et signature</t>
         </is>
       </c>
-      <c r="F44" s="6" t="n">
+      <c r="F44" s="55" t="n">
         <v>18.22</v>
       </c>
     </row>
@@ -7660,7 +7688,7 @@
           <t>Colissimo Point Relais — assurance et signature</t>
         </is>
       </c>
-      <c r="F45" s="6" t="n">
+      <c r="F45" s="55" t="n">
         <v>29.94</v>
       </c>
     </row>
@@ -7690,7 +7718,7 @@
           <t>Colissimo Point Relais</t>
         </is>
       </c>
-      <c r="F46" s="6" t="n">
+      <c r="F46" s="55" t="n">
         <v>15.72</v>
       </c>
     </row>
@@ -7720,7 +7748,7 @@
           <t>Colissimo Point Relais — assurance et signature</t>
         </is>
       </c>
-      <c r="F47" s="6" t="n">
+      <c r="F47" s="55" t="n">
         <v>44.02</v>
       </c>
     </row>
@@ -7734,7 +7762,7 @@
           <t>TOTAL LIVRAISON</t>
         </is>
       </c>
-      <c r="F48" s="34">
+      <c r="F48" s="69">
         <f>SUM(F43:F47)</f>
         <v/>
       </c>

--- a/exports/maison-nsaia-stock.xlsx
+++ b/exports/maison-nsaia-stock.xlsx
@@ -2790,105 +2790,109 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>Ballerines MASSIMO DUTTI P.41 — traces d'essayage</t>
         </is>
       </c>
-      <c r="B25" s="54" t="n">
+      <c r="B25" s="59" t="n">
         <v>25.2</v>
       </c>
-      <c r="C25" s="55">
+      <c r="C25" s="60">
         <f>$B25+$Y25*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D25" s="56">
+      <c r="D25" s="61">
         <f>$C25/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E25" s="55">
+      <c r="E25" s="60">
         <f>CEILING($D25*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F25" s="57" t="n">
-        <v>61</v>
-      </c>
-      <c r="G25" s="57">
+      <c r="F25" s="62" t="n">
+        <v>50</v>
+      </c>
+      <c r="G25" s="62">
         <f>IF($F25="","",$F25-$C25-$M25-$N25)</f>
         <v/>
       </c>
-      <c r="H25" s="9">
+      <c r="H25" s="18">
         <f>IF($G25="","",$G25/$C25)</f>
         <v/>
       </c>
-      <c r="I25" s="10" t="n">
+      <c r="I25" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J25" s="55">
+      <c r="J25" s="60">
         <f>$C25/$I25</f>
         <v/>
       </c>
-      <c r="K25" s="55">
+      <c r="K25" s="60">
         <f>IF($F25="","",$F25/$I25)</f>
         <v/>
       </c>
-      <c r="L25" s="55">
+      <c r="L25" s="60">
         <f>IF($G25="","",$G25/$I25)</f>
         <v/>
       </c>
-      <c r="M25" s="56">
+      <c r="M25" s="61">
         <f>IF($F25="","",$F25*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N25" s="55" t="n">
+      <c r="N25" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="O25" s="58" t="n">
+      <c r="O25" s="63" t="n">
         <v>20</v>
       </c>
-      <c r="P25" s="58" t="n">
+      <c r="P25" s="63" t="n">
         <v>5.2</v>
       </c>
-      <c r="Q25" s="12" t="inlineStr">
+      <c r="Q25" s="21" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="R25" s="12" t="inlineStr">
+      <c r="R25" s="21" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="S25" s="12" t="inlineStr">
+      <c r="S25" s="21" t="inlineStr">
         <is>
           <t>FB2026-43716</t>
         </is>
       </c>
-      <c r="T25" s="12" t="inlineStr">
+      <c r="T25" s="21" t="inlineStr">
         <is>
           <t>439</t>
         </is>
       </c>
-      <c r="U25" s="4" t="inlineStr">
-        <is>
-          <t>Leboncoin + eBay</t>
-        </is>
-      </c>
-      <c r="V25" s="4" t="inlineStr"/>
-      <c r="W25" s="4" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="X25" s="4" t="inlineStr"/>
-      <c r="Y25" s="4" t="n">
+      <c r="U25" s="13" t="inlineStr">
+        <is>
+          <t>Vinted — non encaissé</t>
+        </is>
+      </c>
+      <c r="V25" s="13" t="inlineStr"/>
+      <c r="W25" s="13" t="inlineStr">
+        <is>
+          <t>VENDUE, en attente</t>
+        </is>
+      </c>
+      <c r="X25" s="13" t="inlineStr">
+        <is>
+          <t>17/10/2026</t>
+        </is>
+      </c>
+      <c r="Y25" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="Z25" s="57">
+      <c r="Z25" s="62">
         <f>IF($G25="","",$G25/$Y25)</f>
         <v/>
       </c>
-      <c r="AA25" s="4">
+      <c r="AA25" s="13">
         <f>IF($Z25="","",IF($Z25&gt;=25,"atteint",TEXT(25-$Z25,"0.00")&amp;" € manquants"))</f>
         <v/>
       </c>
